--- a/VerveStacks_EST/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_Base_VS.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_EST\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F0B9889-38CD-44A4-A2E0-8342AB30B7FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A137AE38-A6B2-4249-B163-6EA6F1A2042D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Veda" sheetId="1" r:id="rId1"/>
-    <sheet name="buildrates" sheetId="4" r:id="rId2"/>
-    <sheet name="historical_data_long" sheetId="3" r:id="rId3"/>
+    <sheet name="re_targets" sheetId="5" r:id="rId1"/>
+    <sheet name="Veda" sheetId="1" r:id="rId2"/>
+    <sheet name="buildrates" sheetId="4" r:id="rId3"/>
+    <sheet name="historical_data_long" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -123,7 +124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1534" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1666" uniqueCount="118">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -400,6 +401,87 @@
   <si>
     <t>EST</t>
   </si>
+  <si>
+    <t>RE Targets from EMBER</t>
+  </si>
+  <si>
+    <t>TARGET_YEAR</t>
+  </si>
+  <si>
+    <t>FUEL_CATEGORY</t>
+  </si>
+  <si>
+    <t>METRIC</t>
+  </si>
+  <si>
+    <t>VALUE</t>
+  </si>
+  <si>
+    <t>SOURCE_TYPE</t>
+  </si>
+  <si>
+    <t>SOURCE_NAME</t>
+  </si>
+  <si>
+    <t>PUBLISHER</t>
+  </si>
+  <si>
+    <t>ANNOUNCEMENT_DATE</t>
+  </si>
+  <si>
+    <t>LINK</t>
+  </si>
+  <si>
+    <t>SOURCE_SUMMARY</t>
+  </si>
+  <si>
+    <t>NOTES</t>
+  </si>
+  <si>
+    <t>Bioenergy</t>
+  </si>
+  <si>
+    <t>capacity_total_gw</t>
+  </si>
+  <si>
+    <t>Undergoing legislative process</t>
+  </si>
+  <si>
+    <t>Estonia Draft update of the national energy and climate plan</t>
+  </si>
+  <si>
+    <t>Directorate-General for Communication</t>
+  </si>
+  <si>
+    <t>https://commission.europa.eu/publications/estonia-draft-updated-necp-2021-2030_en</t>
+  </si>
+  <si>
+    <t>Under the EU Regulation on the governance of energy union and climate action (EU 2018/21999), adopted in 2019 as part of the Clean Energy for All Europeans Package, all EU countries must submit 10-year national energy and climate plans (NECPs) to outline how they intend to meet the EU energy and climate targets for 2030. In line with Article 14 of the Governance Regulation, EU member countries were required to submit their draft updated NECPS to the EU Commission. 
+Estonia has set an ambitious goal of reaching 100% renewable electricity by 2030, which it aims to meet through the increase in production volumes in wind (both onshore and offshore) solar, in addition to energy storage through pump hydroelectric power stations and batteries. Estonia’s updated NECP provides a breakdown of each renewable technology up to 2030 with explicit targets.</t>
+  </si>
+  <si>
+    <t>Section 3.1.2.1. AE sectoral share curves for 2021-2030
+p. 153, Figure 48 - share of renewables to reach 67% by 2030
+Table 2.4, p29</t>
+  </si>
+  <si>
+    <t>Hydro</t>
+  </si>
+  <si>
+    <t>Offshore Wind</t>
+  </si>
+  <si>
+    <t>Onshore Wind</t>
+  </si>
+  <si>
+    <t>Solar</t>
+  </si>
+  <si>
+    <t>generation_twh</t>
+  </si>
+  <si>
+    <t>share_of_generation_pct</t>
+  </si>
 </sst>
 </file>
 
@@ -534,7 +616,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -547,6 +629,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="4"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Heading 3" xfId="2" builtinId="18"/>
@@ -884,42 +971,627 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9293F70F-DBAF-4231-9F91-306A64614683}">
+  <dimension ref="B9:L25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B9" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="12"/>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B10" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="K10" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="L10" s="12" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="B11" s="12">
+        <v>2030</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="E11" s="12">
+        <v>0.36699999999999999</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="I11" s="13">
+        <v>45155</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="L11" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="B12" s="12">
+        <v>2030</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="E12" s="12">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="I12" s="13">
+        <v>45155</v>
+      </c>
+      <c r="J12" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="K12" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="L12" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="B13" s="12">
+        <v>2030</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="E13" s="12">
+        <v>1</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="I13" s="13">
+        <v>45155</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="L13" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="B14" s="12">
+        <v>2030</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="E14" s="12">
+        <v>1.31</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="I14" s="13">
+        <v>45155</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="K14" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="L14" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="B15" s="12">
+        <v>2030</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="E15" s="12">
+        <v>1.2</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="I15" s="13">
+        <v>45155</v>
+      </c>
+      <c r="J15" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="K15" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="L15" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="B16" s="12">
+        <v>2030</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="E16" s="12">
+        <v>1.54</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="I16" s="13">
+        <v>45155</v>
+      </c>
+      <c r="J16" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="K16" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="L16" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="B17" s="12">
+        <v>2030</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="E17" s="12">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="I17" s="13">
+        <v>45155</v>
+      </c>
+      <c r="J17" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="K17" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="L17" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="B18" s="12">
+        <v>2030</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="E18" s="12">
+        <v>3.7149999999999999</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="I18" s="13">
+        <v>45155</v>
+      </c>
+      <c r="J18" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="K18" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="L18" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="B19" s="12">
+        <v>2030</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="E19" s="12">
+        <v>3.1240000000000001</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="H19" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="I19" s="13">
+        <v>45155</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="K19" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="L19" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="B20" s="12">
+        <v>2030</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="E20" s="12">
+        <v>1</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="I20" s="13">
+        <v>45155</v>
+      </c>
+      <c r="J20" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="K20" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="L20" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="B21" s="12">
+        <v>2030</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="E21" s="12">
+        <v>16.376000000000001</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="G21" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="I21" s="13">
+        <v>45155</v>
+      </c>
+      <c r="J21" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="K21" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="L21" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="B22" s="12">
+        <v>2030</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="E22" s="12">
+        <v>0.26600000000000001</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="G22" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="H22" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="I22" s="13">
+        <v>45155</v>
+      </c>
+      <c r="J22" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="K22" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="L22" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="B23" s="12">
+        <v>2030</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="E23" s="12">
+        <v>39.503999999999998</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="G23" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="H23" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="I23" s="13">
+        <v>45155</v>
+      </c>
+      <c r="J23" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="K23" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="L23" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="B24" s="12">
+        <v>2030</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="E24" s="12">
+        <v>33.22</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="H24" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="I24" s="13">
+        <v>45155</v>
+      </c>
+      <c r="J24" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="K24" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="L24" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="B25" s="12">
+        <v>2030</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="E25" s="12">
+        <v>10.634</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="H25" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="I25" s="13">
+        <v>45155</v>
+      </c>
+      <c r="J25" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="K25" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="L25" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AL40"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="10.9296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.59765625" customWidth="1"/>
-    <col min="5" max="5" width="9.53125" customWidth="1"/>
-    <col min="6" max="6" width="9.73046875" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.265625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.06640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="4.19921875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.73046875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.19921875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.6328125" customWidth="1"/>
+    <col min="5" max="5" width="9.54296875" customWidth="1"/>
+    <col min="6" max="6" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.90625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.08984375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.1796875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.7265625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.1796875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.7265625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="24" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.06640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.36328125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.08984375" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="7" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="7.1328125" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="4.73046875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="9.19921875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.19921875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="23.73046875" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="7.08984375" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="4.7265625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="23.7265625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="6.36328125" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="7" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="7.86328125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="4.73046875" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="9.19921875" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="4.7265625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="11.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.35">
       <c r="AB1">
         <v>1.1000000000000001</v>
       </c>
@@ -927,7 +1599,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.35">
       <c r="F2" s="6" t="s">
         <v>50</v>
       </c>
@@ -944,7 +1616,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>0</v>
       </c>
@@ -967,7 +1639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>48</v>
       </c>
@@ -992,7 +1664,7 @@
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>87</v>
       </c>
@@ -1012,7 +1684,7 @@
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>0.28000000000000003</v>
       </c>
@@ -1048,7 +1720,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>83</v>
       </c>
@@ -1115,7 +1787,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>19</v>
       </c>
@@ -1193,7 +1865,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.35">
       <c r="F9" t="s">
         <v>9</v>
       </c>
@@ -1261,7 +1933,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:38" ht="14.65" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:38" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F10" t="s">
         <v>88</v>
       </c>
@@ -1278,13 +1950,13 @@
         <v>0.30393385477435431</v>
       </c>
     </row>
-    <row r="11" spans="1:38" ht="14.65" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:38" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>26</v>
       </c>
@@ -1292,7 +1964,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>27</v>
       </c>
@@ -1330,7 +2002,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>29</v>
       </c>
@@ -1368,27 +2040,27 @@
         <v>86</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.35">
       <c r="L16" s="7" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
       <c r="L17" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
       <c r="L18" s="7" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>27</v>
       </c>
@@ -1408,7 +2080,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>32</v>
       </c>
@@ -1426,7 +2098,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>32</v>
       </c>
@@ -1444,7 +2116,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>32</v>
       </c>
@@ -1462,7 +2134,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
         <v>44</v>
       </c>
@@ -1476,7 +2148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
         <v>44</v>
       </c>
@@ -1490,7 +2162,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>49</v>
       </c>
@@ -1505,7 +2177,7 @@
         <v>co2captured</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>65</v>
       </c>
@@ -1516,7 +2188,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
         <v>67</v>
       </c>
@@ -1527,12 +2199,12 @@
         <v>66</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.35">
       <c r="E35" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
         <v>13</v>
       </c>
@@ -1549,7 +2221,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
         <v>39</v>
       </c>
@@ -1563,7 +2235,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="D38" t="s">
         <v>9</v>
       </c>
@@ -1571,7 +2243,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
         <v>41</v>
       </c>
@@ -1585,7 +2257,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="D40" t="s">
         <v>84</v>
       </c>
@@ -1600,29 +2272,29 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{320A1887-1B0C-44A8-9658-90FD86FEE0A5}">
   <dimension ref="A9:J23"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.59765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.265625" customWidth="1"/>
-    <col min="3" max="3" width="8.46484375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.06640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.06640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.46484375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.26953125" customWidth="1"/>
+    <col min="3" max="3" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.6328125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>90</v>
       </c>
@@ -1651,7 +2323,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>91</v>
       </c>
@@ -1680,17 +2352,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B18" s="9" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:8" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="8" t="s">
         <v>48</v>
       </c>
@@ -1716,7 +2388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -1746,7 +2418,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>12</v>
       </c>
@@ -1776,7 +2448,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -1806,7 +2478,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>19</v>
       </c>
@@ -1841,12 +2513,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC33DFE9-8C65-4A33-8FAE-96323628CE2A}">
   <dimension ref="A1:D697"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>50</v>
       </c>
@@ -1860,7 +2532,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>55</v>
       </c>
@@ -1874,7 +2546,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1888,7 +2560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1902,7 +2574,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1916,7 +2588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -1930,7 +2602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -1944,7 +2616,7 @@
         <v>7.9</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>55</v>
       </c>
@@ -1958,7 +2630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1972,7 +2644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>88</v>
       </c>
@@ -1986,7 +2658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -2000,7 +2672,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -2014,7 +2686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -2028,7 +2700,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -2042,7 +2714,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -2056,7 +2728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -2070,7 +2742,7 @@
         <v>7.87</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>55</v>
       </c>
@@ -2084,7 +2756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>9</v>
       </c>
@@ -2098,7 +2770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>88</v>
       </c>
@@ -2112,7 +2784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>55</v>
       </c>
@@ -2126,7 +2798,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>5</v>
       </c>
@@ -2140,7 +2812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -2154,7 +2826,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -2168,7 +2840,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>19</v>
       </c>
@@ -2182,7 +2854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -2196,7 +2868,7 @@
         <v>7.97</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -2210,7 +2882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>9</v>
       </c>
@@ -2224,7 +2896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>88</v>
       </c>
@@ -2238,7 +2910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>55</v>
       </c>
@@ -2252,7 +2924,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>5</v>
       </c>
@@ -2266,7 +2938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>8</v>
       </c>
@@ -2280,7 +2952,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>6</v>
       </c>
@@ -2294,7 +2966,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>19</v>
       </c>
@@ -2308,7 +2980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>23</v>
       </c>
@@ -2322,7 +2994,7 @@
         <v>9.61</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>55</v>
       </c>
@@ -2336,7 +3008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>9</v>
       </c>
@@ -2350,7 +3022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>88</v>
       </c>
@@ -2364,7 +3036,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>55</v>
       </c>
@@ -2378,7 +3050,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>5</v>
       </c>
@@ -2392,7 +3064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>8</v>
       </c>
@@ -2406,7 +3078,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>6</v>
       </c>
@@ -2420,7 +3092,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>19</v>
       </c>
@@ -2434,7 +3106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>23</v>
       </c>
@@ -2448,7 +3120,7 @@
         <v>9.76</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>55</v>
       </c>
@@ -2462,7 +3134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>9</v>
       </c>
@@ -2476,7 +3148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>88</v>
       </c>
@@ -2490,7 +3162,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>55</v>
       </c>
@@ -2504,7 +3176,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>5</v>
       </c>
@@ -2518,7 +3190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>8</v>
       </c>
@@ -2532,7 +3204,7 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>6</v>
       </c>
@@ -2546,7 +3218,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>19</v>
       </c>
@@ -2560,7 +3232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>23</v>
       </c>
@@ -2574,7 +3246,7 @@
         <v>9.5500000000000007</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>55</v>
       </c>
@@ -2588,7 +3260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>9</v>
       </c>
@@ -2602,7 +3274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>88</v>
       </c>
@@ -2616,7 +3288,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>55</v>
       </c>
@@ -2630,7 +3302,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>5</v>
       </c>
@@ -2644,7 +3316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>8</v>
       </c>
@@ -2658,7 +3330,7 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>6</v>
       </c>
@@ -2672,7 +3344,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>19</v>
       </c>
@@ -2686,7 +3358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>23</v>
       </c>
@@ -2700,7 +3372,7 @@
         <v>9.06</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>55</v>
       </c>
@@ -2714,7 +3386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>9</v>
       </c>
@@ -2728,7 +3400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>88</v>
       </c>
@@ -2742,7 +3414,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>55</v>
       </c>
@@ -2756,7 +3428,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>5</v>
       </c>
@@ -2770,7 +3442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>8</v>
       </c>
@@ -2784,7 +3456,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>6</v>
       </c>
@@ -2798,7 +3470,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>19</v>
       </c>
@@ -2812,7 +3484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>23</v>
       </c>
@@ -2826,7 +3498,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>55</v>
       </c>
@@ -2840,7 +3512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>9</v>
       </c>
@@ -2854,7 +3526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>88</v>
       </c>
@@ -2868,7 +3540,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>55</v>
       </c>
@@ -2882,7 +3554,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>5</v>
       </c>
@@ -2896,7 +3568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>8</v>
       </c>
@@ -2910,7 +3582,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>6</v>
       </c>
@@ -2924,7 +3596,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>19</v>
       </c>
@@ -2938,7 +3610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>23</v>
       </c>
@@ -2952,7 +3624,7 @@
         <v>9.9600000000000009</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>55</v>
       </c>
@@ -2966,7 +3638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>9</v>
       </c>
@@ -2980,7 +3652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>88</v>
       </c>
@@ -2994,7 +3666,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>55</v>
       </c>
@@ -3008,7 +3680,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>5</v>
       </c>
@@ -3022,7 +3694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>8</v>
       </c>
@@ -3036,7 +3708,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>6</v>
       </c>
@@ -3050,7 +3722,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>19</v>
       </c>
@@ -3064,7 +3736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>23</v>
       </c>
@@ -3078,7 +3750,7 @@
         <v>8.1300000000000008</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>55</v>
       </c>
@@ -3092,7 +3764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>9</v>
       </c>
@@ -3106,7 +3778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>88</v>
       </c>
@@ -3120,7 +3792,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>55</v>
       </c>
@@ -3134,7 +3806,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>5</v>
       </c>
@@ -3148,7 +3820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>8</v>
       </c>
@@ -3162,7 +3834,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>6</v>
       </c>
@@ -3176,7 +3848,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>19</v>
       </c>
@@ -3190,7 +3862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>23</v>
       </c>
@@ -3204,7 +3876,7 @@
         <v>11.62</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>55</v>
       </c>
@@ -3218,7 +3890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>9</v>
       </c>
@@ -3232,7 +3904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>88</v>
       </c>
@@ -3246,7 +3918,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>55</v>
       </c>
@@ -3260,7 +3932,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>5</v>
       </c>
@@ -3274,7 +3946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>8</v>
       </c>
@@ -3288,7 +3960,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>6</v>
       </c>
@@ -3302,7 +3974,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>19</v>
       </c>
@@ -3316,7 +3988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>23</v>
       </c>
@@ -3330,7 +4002,7 @@
         <v>11.46</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>55</v>
       </c>
@@ -3344,7 +4016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>9</v>
       </c>
@@ -3358,7 +4030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>88</v>
       </c>
@@ -3372,7 +4044,7 @@
         <v>0.37</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>55</v>
       </c>
@@ -3386,7 +4058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>5</v>
       </c>
@@ -3400,7 +4072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>8</v>
       </c>
@@ -3414,7 +4086,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>6</v>
       </c>
@@ -3428,7 +4100,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>19</v>
       </c>
@@ -3442,7 +4114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>23</v>
       </c>
@@ -3456,7 +4128,7 @@
         <v>10.36</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>55</v>
       </c>
@@ -3470,7 +4142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>9</v>
       </c>
@@ -3484,7 +4156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>88</v>
       </c>
@@ -3498,7 +4170,7 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>55</v>
       </c>
@@ -3512,7 +4184,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>5</v>
       </c>
@@ -3526,7 +4198,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>8</v>
       </c>
@@ -3540,7 +4212,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>6</v>
       </c>
@@ -3554,7 +4226,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>19</v>
       </c>
@@ -3568,7 +4240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>23</v>
       </c>
@@ -3582,7 +4254,7 @@
         <v>11.95</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>55</v>
       </c>
@@ -3596,7 +4268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>9</v>
       </c>
@@ -3610,7 +4282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>88</v>
       </c>
@@ -3624,7 +4296,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>55</v>
       </c>
@@ -3638,7 +4310,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>5</v>
       </c>
@@ -3652,7 +4324,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>8</v>
       </c>
@@ -3666,7 +4338,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>6</v>
       </c>
@@ -3680,7 +4352,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>19</v>
       </c>
@@ -3694,7 +4366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>23</v>
       </c>
@@ -3708,7 +4380,7 @@
         <v>10.98</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>55</v>
       </c>
@@ -3722,7 +4394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>9</v>
       </c>
@@ -3736,7 +4408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>88</v>
       </c>
@@ -3750,7 +4422,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>55</v>
       </c>
@@ -3764,7 +4436,7 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>5</v>
       </c>
@@ -3778,7 +4450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>8</v>
       </c>
@@ -3792,7 +4464,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>6</v>
       </c>
@@ -3806,7 +4478,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>19</v>
       </c>
@@ -3820,7 +4492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>23</v>
       </c>
@@ -3834,7 +4506,7 @@
         <v>8.5299999999999994</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>55</v>
       </c>
@@ -3848,7 +4520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>9</v>
       </c>
@@ -3862,7 +4534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>88</v>
       </c>
@@ -3876,7 +4548,7 @@
         <v>0.71</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>55</v>
       </c>
@@ -3890,7 +4562,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>5</v>
       </c>
@@ -3904,7 +4576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>8</v>
       </c>
@@ -3918,7 +4590,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>6</v>
       </c>
@@ -3932,7 +4604,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>19</v>
       </c>
@@ -3946,7 +4618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>23</v>
       </c>
@@ -3960,7 +4632,7 @@
         <v>10.51</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>55</v>
       </c>
@@ -3974,7 +4646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>9</v>
       </c>
@@ -3988,7 +4660,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>88</v>
       </c>
@@ -4002,7 +4674,7 @@
         <v>0.59</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>55</v>
       </c>
@@ -4016,7 +4688,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>5</v>
       </c>
@@ -4030,7 +4702,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>8</v>
       </c>
@@ -4044,7 +4716,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>6</v>
       </c>
@@ -4058,7 +4730,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>19</v>
       </c>
@@ -4072,7 +4744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>23</v>
       </c>
@@ -4086,7 +4758,7 @@
         <v>11.22</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>55</v>
       </c>
@@ -4100,7 +4772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>9</v>
       </c>
@@ -4114,7 +4786,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>88</v>
       </c>
@@ -4128,7 +4800,7 @@
         <v>0.72</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>55</v>
       </c>
@@ -4142,7 +4814,7 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>5</v>
       </c>
@@ -4156,7 +4828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>8</v>
       </c>
@@ -4170,7 +4842,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>6</v>
       </c>
@@ -4184,7 +4856,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>19</v>
       </c>
@@ -4198,7 +4870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>23</v>
       </c>
@@ -4212,7 +4884,7 @@
         <v>10.32</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>55</v>
       </c>
@@ -4226,7 +4898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>9</v>
       </c>
@@ -4240,7 +4912,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>88</v>
       </c>
@@ -4254,7 +4926,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>55</v>
       </c>
@@ -4268,7 +4940,7 @@
         <v>1.36</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>5</v>
       </c>
@@ -4282,7 +4954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>8</v>
       </c>
@@ -4296,7 +4968,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>6</v>
       </c>
@@ -4310,7 +4982,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>19</v>
       </c>
@@ -4324,7 +4996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>23</v>
       </c>
@@ -4338,7 +5010,7 @@
         <v>5.43</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>55</v>
       </c>
@@ -4352,7 +5024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>9</v>
       </c>
@@ -4366,7 +5038,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>88</v>
       </c>
@@ -4380,7 +5052,7 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>55</v>
       </c>
@@ -4394,7 +5066,7 @@
         <v>1.85</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>5</v>
       </c>
@@ -4408,7 +5080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>8</v>
       </c>
@@ -4422,7 +5094,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>6</v>
       </c>
@@ -4436,7 +5108,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>19</v>
       </c>
@@ -4450,7 +5122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>23</v>
       </c>
@@ -4464,7 +5136,7 @@
         <v>3.08</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>55</v>
       </c>
@@ -4478,7 +5150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>9</v>
       </c>
@@ -4492,7 +5164,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>88</v>
       </c>
@@ -4506,7 +5178,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>55</v>
       </c>
@@ -4520,7 +5192,7 @@
         <v>1.77</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>5</v>
       </c>
@@ -4534,7 +5206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>8</v>
       </c>
@@ -4548,7 +5220,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>6</v>
       </c>
@@ -4562,7 +5234,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>19</v>
       </c>
@@ -4576,7 +5248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>23</v>
       </c>
@@ -4590,7 +5262,7 @@
         <v>4.28</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>55</v>
       </c>
@@ -4604,7 +5276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>9</v>
       </c>
@@ -4618,7 +5290,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>88</v>
       </c>
@@ -4632,7 +5304,7 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>55</v>
       </c>
@@ -4646,7 +5318,7 @@
         <v>1.57</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>5</v>
       </c>
@@ -4660,7 +5332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>8</v>
       </c>
@@ -4674,7 +5346,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>6</v>
       </c>
@@ -4688,7 +5360,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>19</v>
       </c>
@@ -4702,7 +5374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>23</v>
       </c>
@@ -4716,7 +5388,7 @@
         <v>6.02</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>55</v>
       </c>
@@ -4730,7 +5402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>9</v>
       </c>
@@ -4744,7 +5416,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>88</v>
       </c>
@@ -4758,7 +5430,7 @@
         <v>0.63</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>55</v>
       </c>
@@ -4772,7 +5444,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>5</v>
       </c>
@@ -4786,7 +5458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>8</v>
       </c>
@@ -4800,7 +5472,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>6</v>
       </c>
@@ -4814,7 +5486,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>19</v>
       </c>
@@ -4828,7 +5500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>23</v>
       </c>
@@ -4842,7 +5514,7 @@
         <v>3.56</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>55</v>
       </c>
@@ -4856,7 +5528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>9</v>
       </c>
@@ -4870,7 +5542,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>88</v>
       </c>
@@ -4884,7 +5556,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>55</v>
       </c>
@@ -4898,7 +5570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>5</v>
       </c>
@@ -4909,7 +5581,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>8</v>
       </c>
@@ -4923,7 +5595,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>6</v>
       </c>
@@ -4937,7 +5609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>19</v>
       </c>
@@ -4948,7 +5620,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>23</v>
       </c>
@@ -4962,7 +5634,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>55</v>
       </c>
@@ -4976,7 +5648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>9</v>
       </c>
@@ -4990,7 +5662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>88</v>
       </c>
@@ -5004,7 +5676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>55</v>
       </c>
@@ -5018,7 +5690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>5</v>
       </c>
@@ -5029,7 +5701,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>8</v>
       </c>
@@ -5043,7 +5715,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>6</v>
       </c>
@@ -5057,7 +5729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>19</v>
       </c>
@@ -5068,7 +5740,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>23</v>
       </c>
@@ -5082,7 +5754,7 @@
         <v>2.44</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>55</v>
       </c>
@@ -5096,7 +5768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>9</v>
       </c>
@@ -5110,7 +5782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>88</v>
       </c>
@@ -5124,7 +5796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>55</v>
       </c>
@@ -5138,7 +5810,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>5</v>
       </c>
@@ -5149,7 +5821,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>8</v>
       </c>
@@ -5163,7 +5835,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>6</v>
       </c>
@@ -5177,7 +5849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>19</v>
       </c>
@@ -5188,7 +5860,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>23</v>
       </c>
@@ -5202,7 +5874,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>55</v>
       </c>
@@ -5216,7 +5888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>9</v>
       </c>
@@ -5230,7 +5902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>88</v>
       </c>
@@ -5244,7 +5916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>55</v>
       </c>
@@ -5258,7 +5930,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>5</v>
       </c>
@@ -5269,7 +5941,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>8</v>
       </c>
@@ -5283,7 +5955,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>6</v>
       </c>
@@ -5297,7 +5969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>19</v>
       </c>
@@ -5308,7 +5980,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>23</v>
       </c>
@@ -5322,7 +5994,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>55</v>
       </c>
@@ -5336,7 +6008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>9</v>
       </c>
@@ -5350,7 +6022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>88</v>
       </c>
@@ -5364,7 +6036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>55</v>
       </c>
@@ -5378,7 +6050,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>5</v>
       </c>
@@ -5389,7 +6061,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>8</v>
       </c>
@@ -5403,7 +6075,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>6</v>
       </c>
@@ -5417,7 +6089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>19</v>
       </c>
@@ -5428,7 +6100,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>23</v>
       </c>
@@ -5442,7 +6114,7 @@
         <v>2.67</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>55</v>
       </c>
@@ -5456,7 +6128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>9</v>
       </c>
@@ -5470,7 +6142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>88</v>
       </c>
@@ -5484,7 +6156,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>55</v>
       </c>
@@ -5498,7 +6170,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>5</v>
       </c>
@@ -5509,7 +6181,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>8</v>
       </c>
@@ -5523,7 +6195,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>6</v>
       </c>
@@ -5537,7 +6209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>19</v>
       </c>
@@ -5548,7 +6220,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>23</v>
       </c>
@@ -5562,7 +6234,7 @@
         <v>2.5099999999999998</v>
       </c>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>55</v>
       </c>
@@ -5576,7 +6248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>9</v>
       </c>
@@ -5590,7 +6262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>88</v>
       </c>
@@ -5604,7 +6276,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>55</v>
       </c>
@@ -5618,7 +6290,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>5</v>
       </c>
@@ -5629,7 +6301,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>8</v>
       </c>
@@ -5643,7 +6315,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>6</v>
       </c>
@@ -5657,7 +6329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="276" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>19</v>
       </c>
@@ -5668,7 +6340,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>23</v>
       </c>
@@ -5682,7 +6354,7 @@
         <v>2.5099999999999998</v>
       </c>
     </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="278" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>55</v>
       </c>
@@ -5696,7 +6368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="279" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>9</v>
       </c>
@@ -5710,7 +6382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="280" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>88</v>
       </c>
@@ -5724,7 +6396,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="281" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>55</v>
       </c>
@@ -5738,7 +6410,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="282" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>5</v>
       </c>
@@ -5749,7 +6421,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="283" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>8</v>
       </c>
@@ -5763,7 +6435,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="284" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>6</v>
       </c>
@@ -5777,7 +6449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="285" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>19</v>
       </c>
@@ -5788,7 +6460,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="286" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>23</v>
       </c>
@@ -5802,7 +6474,7 @@
         <v>2.56</v>
       </c>
     </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="287" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>55</v>
       </c>
@@ -5816,7 +6488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="288" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>9</v>
       </c>
@@ -5830,7 +6502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>88</v>
       </c>
@@ -5844,7 +6516,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>55</v>
       </c>
@@ -5858,7 +6530,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>5</v>
       </c>
@@ -5869,7 +6541,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>8</v>
       </c>
@@ -5883,7 +6555,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>6</v>
       </c>
@@ -5897,7 +6569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>19</v>
       </c>
@@ -5908,7 +6580,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>23</v>
       </c>
@@ -5922,7 +6594,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>55</v>
       </c>
@@ -5936,7 +6608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>9</v>
       </c>
@@ -5950,7 +6622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>88</v>
       </c>
@@ -5964,7 +6636,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>55</v>
       </c>
@@ -5978,7 +6650,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>5</v>
       </c>
@@ -5989,7 +6661,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>8</v>
       </c>
@@ -6003,7 +6675,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>6</v>
       </c>
@@ -6017,7 +6689,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>19</v>
       </c>
@@ -6028,7 +6700,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>23</v>
       </c>
@@ -6042,7 +6714,7 @@
         <v>2.4900000000000002</v>
       </c>
     </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="305" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>55</v>
       </c>
@@ -6056,7 +6728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="306" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>9</v>
       </c>
@@ -6070,7 +6742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>88</v>
       </c>
@@ -6084,7 +6756,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="308" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>55</v>
       </c>
@@ -6098,7 +6770,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="309" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>5</v>
       </c>
@@ -6109,7 +6781,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="310" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>8</v>
       </c>
@@ -6123,7 +6795,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="311" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>6</v>
       </c>
@@ -6137,7 +6809,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="312" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>19</v>
       </c>
@@ -6148,7 +6820,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="313" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>23</v>
       </c>
@@ -6162,7 +6834,7 @@
         <v>2.4900000000000002</v>
       </c>
     </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="314" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>55</v>
       </c>
@@ -6176,7 +6848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="315" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>9</v>
       </c>
@@ -6190,7 +6862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="316" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>88</v>
       </c>
@@ -6204,7 +6876,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="317" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
         <v>55</v>
       </c>
@@ -6218,7 +6890,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="318" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>5</v>
       </c>
@@ -6229,7 +6901,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="319" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>8</v>
       </c>
@@ -6243,7 +6915,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="320" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>6</v>
       </c>
@@ -6257,7 +6929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="321" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>19</v>
       </c>
@@ -6268,7 +6940,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="322" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
         <v>23</v>
       </c>
@@ -6282,7 +6954,7 @@
         <v>2.4900000000000002</v>
       </c>
     </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="323" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
         <v>55</v>
       </c>
@@ -6296,7 +6968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="324" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>9</v>
       </c>
@@ -6310,7 +6982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="325" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
         <v>88</v>
       </c>
@@ -6324,7 +6996,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="326" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
         <v>55</v>
       </c>
@@ -6338,7 +7010,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="327" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>5</v>
       </c>
@@ -6349,7 +7021,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="328" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>8</v>
       </c>
@@ -6363,7 +7035,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="329" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>6</v>
       </c>
@@ -6377,7 +7049,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="330" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
         <v>19</v>
       </c>
@@ -6388,7 +7060,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="331" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
         <v>23</v>
       </c>
@@ -6402,7 +7074,7 @@
         <v>2.48</v>
       </c>
     </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="332" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
         <v>55</v>
       </c>
@@ -6416,7 +7088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="333" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
         <v>9</v>
       </c>
@@ -6430,7 +7102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="334" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
         <v>88</v>
       </c>
@@ -6444,7 +7116,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="335" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
         <v>55</v>
       </c>
@@ -6458,7 +7130,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="336" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
         <v>5</v>
       </c>
@@ -6469,7 +7141,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="337" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
         <v>8</v>
       </c>
@@ -6483,7 +7155,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="338" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
         <v>6</v>
       </c>
@@ -6497,7 +7169,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="339" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
         <v>19</v>
       </c>
@@ -6508,7 +7180,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="340" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
         <v>23</v>
       </c>
@@ -6522,7 +7194,7 @@
         <v>2.39</v>
       </c>
     </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="341" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
         <v>55</v>
       </c>
@@ -6536,7 +7208,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="342" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
         <v>9</v>
       </c>
@@ -6550,7 +7222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="343" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
         <v>88</v>
       </c>
@@ -6564,7 +7236,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="344" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
         <v>55</v>
       </c>
@@ -6578,7 +7250,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="345" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
         <v>5</v>
       </c>
@@ -6589,7 +7261,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="346" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
         <v>8</v>
       </c>
@@ -6603,7 +7275,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="347" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
         <v>6</v>
       </c>
@@ -6617,7 +7289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="348" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
         <v>19</v>
       </c>
@@ -6628,7 +7300,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="349" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
         <v>23</v>
       </c>
@@ -6642,7 +7314,7 @@
         <v>2.4700000000000002</v>
       </c>
     </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="350" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
         <v>55</v>
       </c>
@@ -6656,7 +7328,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="351" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
         <v>9</v>
       </c>
@@ -6670,7 +7342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="352" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
         <v>88</v>
       </c>
@@ -6684,7 +7356,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="353" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
         <v>55</v>
       </c>
@@ -6698,7 +7370,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="354" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
         <v>5</v>
       </c>
@@ -6709,7 +7381,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="355" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
         <v>8</v>
       </c>
@@ -6723,7 +7395,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="356" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
         <v>6</v>
       </c>
@@ -6737,7 +7409,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="357" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
         <v>19</v>
       </c>
@@ -6748,7 +7420,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="358" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
         <v>23</v>
       </c>
@@ -6762,7 +7434,7 @@
         <v>2.27</v>
       </c>
     </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="359" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
         <v>55</v>
       </c>
@@ -6776,7 +7448,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="360" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
         <v>9</v>
       </c>
@@ -6790,7 +7462,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="361" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
         <v>88</v>
       </c>
@@ -6804,7 +7476,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="362" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
         <v>55</v>
       </c>
@@ -6818,7 +7490,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="363" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
         <v>5</v>
       </c>
@@ -6829,7 +7501,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="364" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
         <v>8</v>
       </c>
@@ -6843,7 +7515,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="365" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
         <v>6</v>
       </c>
@@ -6857,7 +7529,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="366" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
         <v>19</v>
       </c>
@@ -6868,7 +7540,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="367" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
         <v>23</v>
       </c>
@@ -6882,7 +7554,7 @@
         <v>1.97</v>
       </c>
     </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="368" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
         <v>55</v>
       </c>
@@ -6896,7 +7568,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="369" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
         <v>9</v>
       </c>
@@ -6910,7 +7582,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="370" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
         <v>88</v>
       </c>
@@ -6924,7 +7596,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="371" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
         <v>55</v>
       </c>
@@ -6938,7 +7610,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="372" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
         <v>5</v>
       </c>
@@ -6949,7 +7621,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="373" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
         <v>8</v>
       </c>
@@ -6963,7 +7635,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="374" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
         <v>6</v>
       </c>
@@ -6977,7 +7649,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="375" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="375" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
         <v>19</v>
       </c>
@@ -6988,7 +7660,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="376" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="376" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
         <v>23</v>
       </c>
@@ -7002,7 +7674,7 @@
         <v>1.93</v>
       </c>
     </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="377" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
         <v>55</v>
       </c>
@@ -7016,7 +7688,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="378" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="378" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
         <v>9</v>
       </c>
@@ -7030,7 +7702,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="379" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
         <v>88</v>
       </c>
@@ -7044,7 +7716,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="380" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
         <v>55</v>
       </c>
@@ -7058,7 +7730,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="381" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="381" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
         <v>5</v>
       </c>
@@ -7069,7 +7741,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="382" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="382" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
         <v>8</v>
       </c>
@@ -7083,7 +7755,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="383" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="383" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
         <v>6</v>
       </c>
@@ -7097,7 +7769,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="384" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="384" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
         <v>19</v>
       </c>
@@ -7108,7 +7780,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="385" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
         <v>23</v>
       </c>
@@ -7122,7 +7794,7 @@
         <v>2.21</v>
       </c>
     </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="386" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
         <v>55</v>
       </c>
@@ -7136,7 +7808,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="387" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
         <v>9</v>
       </c>
@@ -7150,7 +7822,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="388" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
         <v>88</v>
       </c>
@@ -7164,7 +7836,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="389" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="389" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
         <v>55</v>
       </c>
@@ -7178,7 +7850,7 @@
         <v>0.19</v>
       </c>
     </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="390" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
         <v>5</v>
       </c>
@@ -7189,7 +7861,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="391" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
         <v>8</v>
       </c>
@@ -7203,7 +7875,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="392" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
         <v>6</v>
       </c>
@@ -7217,7 +7889,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="393" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
         <v>19</v>
       </c>
@@ -7228,7 +7900,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="394" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="394" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
         <v>23</v>
       </c>
@@ -7242,7 +7914,7 @@
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="395" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="395" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
         <v>55</v>
       </c>
@@ -7256,7 +7928,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="396" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="396" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
         <v>9</v>
       </c>
@@ -7270,7 +7942,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="397" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="397" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
         <v>88</v>
       </c>
@@ -7284,7 +7956,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="398" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
         <v>55</v>
       </c>
@@ -7298,7 +7970,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="399" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="399" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
         <v>5</v>
       </c>
@@ -7309,7 +7981,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="400" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
         <v>8</v>
       </c>
@@ -7323,7 +7995,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="401" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="401" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
         <v>6</v>
       </c>
@@ -7337,7 +8009,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="402" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="402" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
         <v>19</v>
       </c>
@@ -7348,7 +8020,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="403" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="403" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
         <v>23</v>
       </c>
@@ -7362,7 +8034,7 @@
         <v>1.91</v>
       </c>
     </row>
-    <row r="404" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="404" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
         <v>55</v>
       </c>
@@ -7376,7 +8048,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="405" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="405" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
         <v>9</v>
       </c>
@@ -7390,7 +8062,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="406" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="406" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
         <v>88</v>
       </c>
@@ -7404,7 +8076,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="407" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="407" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
         <v>55</v>
       </c>
@@ -7418,7 +8090,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="408" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="408" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
         <v>5</v>
       </c>
@@ -7429,7 +8101,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="409" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="409" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
         <v>8</v>
       </c>
@@ -7443,7 +8115,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="410" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="410" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
         <v>6</v>
       </c>
@@ -7457,7 +8129,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="411" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="411" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
         <v>19</v>
       </c>
@@ -7468,7 +8140,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="412" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="412" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
         <v>23</v>
       </c>
@@ -7482,7 +8154,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="413" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
         <v>55</v>
       </c>
@@ -7496,7 +8168,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="414" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="414" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
         <v>9</v>
       </c>
@@ -7510,7 +8182,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="415" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="415" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
         <v>88</v>
       </c>
@@ -7524,7 +8196,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="416" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="416" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
         <v>55</v>
       </c>
@@ -7538,7 +8210,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="417" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="417" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
         <v>5</v>
       </c>
@@ -7549,7 +8221,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="418" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="418" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
         <v>8</v>
       </c>
@@ -7563,7 +8235,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="419" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="419" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
         <v>6</v>
       </c>
@@ -7577,7 +8249,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="420" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="420" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
         <v>19</v>
       </c>
@@ -7588,7 +8260,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="421" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="421" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
         <v>23</v>
       </c>
@@ -7602,7 +8274,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="422" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="422" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
         <v>55</v>
       </c>
@@ -7616,7 +8288,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="423" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="423" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
         <v>9</v>
       </c>
@@ -7630,7 +8302,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="424" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="424" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
         <v>88</v>
       </c>
@@ -7644,7 +8316,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="425" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="425" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
         <v>55</v>
       </c>
@@ -7658,7 +8330,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="426" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="426" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
         <v>5</v>
       </c>
@@ -7669,7 +8341,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="427" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="427" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
         <v>8</v>
       </c>
@@ -7683,7 +8355,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="428" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="428" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
         <v>6</v>
       </c>
@@ -7697,7 +8369,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="429" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="429" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
         <v>19</v>
       </c>
@@ -7708,7 +8380,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="430" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="430" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
         <v>23</v>
       </c>
@@ -7722,7 +8394,7 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="431" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="431" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
         <v>55</v>
       </c>
@@ -7736,7 +8408,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="432" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="432" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
         <v>9</v>
       </c>
@@ -7750,7 +8422,7 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="433" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="433" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
         <v>88</v>
       </c>
@@ -7764,7 +8436,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="434" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="434" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
         <v>55</v>
       </c>
@@ -7778,7 +8450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="435" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="435" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
         <v>5</v>
       </c>
@@ -7792,7 +8464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="436" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="436" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
         <v>8</v>
       </c>
@@ -7806,7 +8478,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="437" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="437" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
         <v>6</v>
       </c>
@@ -7820,7 +8492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="438" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="438" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
         <v>19</v>
       </c>
@@ -7834,7 +8506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="439" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="439" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
         <v>23</v>
       </c>
@@ -7848,7 +8520,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="440" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="440" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
         <v>55</v>
       </c>
@@ -7862,7 +8534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="441" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="441" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
         <v>9</v>
       </c>
@@ -7876,7 +8548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="442" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="442" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
         <v>88</v>
       </c>
@@ -7890,7 +8562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="443" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="443" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
         <v>55</v>
       </c>
@@ -7904,7 +8576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="444" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="444" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
         <v>5</v>
       </c>
@@ -7918,7 +8590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="445" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="445" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
         <v>8</v>
       </c>
@@ -7932,7 +8604,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="446" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="446" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
         <v>6</v>
       </c>
@@ -7946,7 +8618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="447" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="447" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
         <v>19</v>
       </c>
@@ -7960,7 +8632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="448" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="448" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
         <v>23</v>
       </c>
@@ -7974,7 +8646,7 @@
         <v>5.18</v>
       </c>
     </row>
-    <row r="449" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="449" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
         <v>55</v>
       </c>
@@ -7988,7 +8660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="450" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="450" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
         <v>9</v>
       </c>
@@ -8002,7 +8674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="451" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="451" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
         <v>88</v>
       </c>
@@ -8016,7 +8688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="452" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="452" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
         <v>55</v>
       </c>
@@ -8030,7 +8702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="453" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="453" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
         <v>5</v>
       </c>
@@ -8044,7 +8716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="454" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="454" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
         <v>8</v>
       </c>
@@ -8058,7 +8730,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="455" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="455" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
         <v>6</v>
       </c>
@@ -8072,7 +8744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="456" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="456" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
         <v>19</v>
       </c>
@@ -8086,7 +8758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="457" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="457" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
         <v>23</v>
       </c>
@@ -8100,7 +8772,7 @@
         <v>5.24</v>
       </c>
     </row>
-    <row r="458" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="458" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
         <v>55</v>
       </c>
@@ -8114,7 +8786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="459" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="459" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
         <v>9</v>
       </c>
@@ -8128,7 +8800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="460" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="460" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
         <v>88</v>
       </c>
@@ -8142,7 +8814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="461" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="461" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
         <v>55</v>
       </c>
@@ -8156,7 +8828,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="462" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="462" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
         <v>5</v>
       </c>
@@ -8170,7 +8842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="463" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="463" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
         <v>8</v>
       </c>
@@ -8184,7 +8856,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="464" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="464" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
         <v>6</v>
       </c>
@@ -8198,7 +8870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="465" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="465" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
         <v>19</v>
       </c>
@@ -8212,7 +8884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="466" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="466" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
         <v>23</v>
       </c>
@@ -8226,7 +8898,7 @@
         <v>6.32</v>
       </c>
     </row>
-    <row r="467" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="467" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
         <v>55</v>
       </c>
@@ -8240,7 +8912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="468" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="468" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
         <v>9</v>
       </c>
@@ -8254,7 +8926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="469" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="469" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
         <v>88</v>
       </c>
@@ -8268,7 +8940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="470" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="470" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
         <v>55</v>
       </c>
@@ -8282,7 +8954,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="471" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="471" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
         <v>5</v>
       </c>
@@ -8296,7 +8968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="472" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="472" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
         <v>8</v>
       </c>
@@ -8310,7 +8982,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="473" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="473" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
         <v>6</v>
       </c>
@@ -8324,7 +8996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="474" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="474" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
         <v>19</v>
       </c>
@@ -8338,7 +9010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="475" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="475" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
         <v>23</v>
       </c>
@@ -8352,7 +9024,7 @@
         <v>6.42</v>
       </c>
     </row>
-    <row r="476" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="476" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
         <v>55</v>
       </c>
@@ -8366,7 +9038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="477" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="477" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
         <v>9</v>
       </c>
@@ -8380,7 +9052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="478" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="478" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
         <v>88</v>
       </c>
@@ -8394,7 +9066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="479" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="479" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
         <v>55</v>
       </c>
@@ -8408,7 +9080,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="480" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="480" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
         <v>5</v>
       </c>
@@ -8422,7 +9094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="481" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="481" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
         <v>8</v>
       </c>
@@ -8436,7 +9108,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="482" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="482" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
         <v>6</v>
       </c>
@@ -8450,7 +9122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="483" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="483" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
         <v>19</v>
       </c>
@@ -8464,7 +9136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="484" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="484" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
         <v>23</v>
       </c>
@@ -8478,7 +9150,7 @@
         <v>6.28</v>
       </c>
     </row>
-    <row r="485" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="485" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
         <v>55</v>
       </c>
@@ -8492,7 +9164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="486" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="486" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
         <v>9</v>
       </c>
@@ -8506,7 +9178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="487" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="487" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
         <v>88</v>
       </c>
@@ -8520,7 +9192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="488" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="488" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
         <v>55</v>
       </c>
@@ -8534,7 +9206,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="489" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="489" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
         <v>5</v>
       </c>
@@ -8548,7 +9220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="490" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="490" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
         <v>8</v>
       </c>
@@ -8562,7 +9234,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="491" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="491" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
         <v>6</v>
       </c>
@@ -8576,7 +9248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="492" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="492" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
         <v>19</v>
       </c>
@@ -8590,7 +9262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="493" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="493" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
         <v>23</v>
       </c>
@@ -8604,7 +9276,7 @@
         <v>5.96</v>
       </c>
     </row>
-    <row r="494" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="494" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
         <v>55</v>
       </c>
@@ -8618,7 +9290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="495" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="495" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
         <v>9</v>
       </c>
@@ -8632,7 +9304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="496" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="496" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
         <v>88</v>
       </c>
@@ -8646,7 +9318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="497" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="497" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
         <v>55</v>
       </c>
@@ -8660,7 +9332,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="498" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="498" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
         <v>5</v>
       </c>
@@ -8674,7 +9346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="499" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="499" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
         <v>8</v>
       </c>
@@ -8688,7 +9360,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="500" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="500" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
         <v>6</v>
       </c>
@@ -8702,7 +9374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="501" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="501" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
         <v>19</v>
       </c>
@@ -8716,7 +9388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="502" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="502" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
         <v>23</v>
       </c>
@@ -8730,7 +9402,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="503" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="503" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
         <v>55</v>
       </c>
@@ -8744,7 +9416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="504" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="504" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
         <v>9</v>
       </c>
@@ -8758,7 +9430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="505" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="505" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
         <v>88</v>
       </c>
@@ -8772,7 +9444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="506" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="506" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
         <v>55</v>
       </c>
@@ -8786,7 +9458,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="507" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="507" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
         <v>5</v>
       </c>
@@ -8800,7 +9472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="508" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="508" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
         <v>8</v>
       </c>
@@ -8814,7 +9486,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="509" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="509" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
         <v>6</v>
       </c>
@@ -8828,7 +9500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="510" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="510" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
         <v>19</v>
       </c>
@@ -8842,7 +9514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="511" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="511" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
         <v>23</v>
       </c>
@@ -8856,7 +9528,7 @@
         <v>6.55</v>
       </c>
     </row>
-    <row r="512" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="512" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
         <v>55</v>
       </c>
@@ -8870,7 +9542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="513" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="513" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
         <v>9</v>
       </c>
@@ -8884,7 +9556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="514" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="514" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
         <v>88</v>
       </c>
@@ -8898,7 +9570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="515" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="515" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
         <v>55</v>
       </c>
@@ -8912,7 +9584,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="516" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="516" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
         <v>5</v>
       </c>
@@ -8926,7 +9598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="517" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="517" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
         <v>8</v>
       </c>
@@ -8940,7 +9612,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="518" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="518" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
         <v>6</v>
       </c>
@@ -8954,7 +9626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="519" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="519" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
         <v>19</v>
       </c>
@@ -8968,7 +9640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="520" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="520" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
         <v>23</v>
       </c>
@@ -8982,7 +9654,7 @@
         <v>5.35</v>
       </c>
     </row>
-    <row r="521" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="521" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
         <v>55</v>
       </c>
@@ -8996,7 +9668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="522" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="522" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
         <v>9</v>
       </c>
@@ -9010,7 +9682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="523" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="523" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
         <v>88</v>
       </c>
@@ -9024,7 +9696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="524" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="524" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
         <v>55</v>
       </c>
@@ -9038,7 +9710,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="525" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="525" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
         <v>5</v>
       </c>
@@ -9052,7 +9724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="526" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="526" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
         <v>8</v>
       </c>
@@ -9066,7 +9738,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="527" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="527" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
         <v>6</v>
       </c>
@@ -9080,7 +9752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="528" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="528" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
         <v>19</v>
       </c>
@@ -9094,7 +9766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="529" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="529" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
         <v>23</v>
       </c>
@@ -9108,7 +9780,7 @@
         <v>7.65</v>
       </c>
     </row>
-    <row r="530" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="530" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
         <v>55</v>
       </c>
@@ -9122,7 +9794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="531" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="531" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
         <v>9</v>
       </c>
@@ -9136,7 +9808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="532" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="532" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
         <v>88</v>
       </c>
@@ -9150,7 +9822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="533" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="533" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
         <v>55</v>
       </c>
@@ -9164,7 +9836,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="534" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="534" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
         <v>5</v>
       </c>
@@ -9178,7 +9850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="535" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="535" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
         <v>8</v>
       </c>
@@ -9192,7 +9864,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="536" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="536" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
         <v>6</v>
       </c>
@@ -9206,7 +9878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="537" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="537" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
         <v>19</v>
       </c>
@@ -9220,7 +9892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="538" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="538" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
         <v>23</v>
       </c>
@@ -9234,7 +9906,7 @@
         <v>7.54</v>
       </c>
     </row>
-    <row r="539" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="539" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
         <v>55</v>
       </c>
@@ -9248,7 +9920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="540" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="540" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
         <v>9</v>
       </c>
@@ -9262,7 +9934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="541" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="541" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
         <v>88</v>
       </c>
@@ -9276,7 +9948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="542" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="542" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
         <v>55</v>
       </c>
@@ -9290,7 +9962,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="543" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="543" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
         <v>5</v>
       </c>
@@ -9304,7 +9976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="544" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="544" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
         <v>8</v>
       </c>
@@ -9318,7 +9990,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="545" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="545" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
         <v>6</v>
       </c>
@@ -9332,7 +10004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="546" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="546" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
         <v>19</v>
       </c>
@@ -9346,7 +10018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="547" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="547" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
         <v>23</v>
       </c>
@@ -9360,7 +10032,7 @@
         <v>6.82</v>
       </c>
     </row>
-    <row r="548" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="548" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
         <v>55</v>
       </c>
@@ -9374,7 +10046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="549" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="549" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
         <v>9</v>
       </c>
@@ -9388,7 +10060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="550" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="550" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
         <v>88</v>
       </c>
@@ -9402,7 +10074,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="551" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="551" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
         <v>55</v>
       </c>
@@ -9416,7 +10088,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="552" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="552" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
         <v>5</v>
       </c>
@@ -9430,7 +10102,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="553" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="553" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
         <v>8</v>
       </c>
@@ -9444,7 +10116,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="554" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="554" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
         <v>6</v>
       </c>
@@ -9458,7 +10130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="555" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="555" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
         <v>19</v>
       </c>
@@ -9472,7 +10144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="556" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="556" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
         <v>23</v>
       </c>
@@ -9486,7 +10158,7 @@
         <v>7.86</v>
       </c>
     </row>
-    <row r="557" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="557" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
         <v>55</v>
       </c>
@@ -9500,7 +10172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="558" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="558" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
         <v>9</v>
       </c>
@@ -9514,7 +10186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="559" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="559" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
         <v>88</v>
       </c>
@@ -9528,7 +10200,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="560" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="560" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
         <v>55</v>
       </c>
@@ -9542,7 +10214,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="561" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="561" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
         <v>5</v>
       </c>
@@ -9556,7 +10228,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="562" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="562" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
         <v>8</v>
       </c>
@@ -9570,7 +10242,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="563" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="563" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
         <v>6</v>
       </c>
@@ -9584,7 +10256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="564" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="564" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
         <v>19</v>
       </c>
@@ -9598,7 +10270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="565" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="565" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
         <v>23</v>
       </c>
@@ -9612,7 +10284,7 @@
         <v>7.22</v>
       </c>
     </row>
-    <row r="566" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="566" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
         <v>55</v>
       </c>
@@ -9626,7 +10298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="567" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="567" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
         <v>9</v>
       </c>
@@ -9640,7 +10312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="568" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="568" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
         <v>88</v>
       </c>
@@ -9654,7 +10326,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="569" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="569" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
         <v>55</v>
       </c>
@@ -9668,7 +10340,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="570" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="570" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
         <v>5</v>
       </c>
@@ -9682,7 +10354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="571" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="571" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
         <v>8</v>
       </c>
@@ -9696,7 +10368,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="572" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="572" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
         <v>6</v>
       </c>
@@ -9710,7 +10382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="573" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="573" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
         <v>19</v>
       </c>
@@ -9724,7 +10396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="574" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="574" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
         <v>23</v>
       </c>
@@ -9738,7 +10410,7 @@
         <v>5.61</v>
       </c>
     </row>
-    <row r="575" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="575" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
         <v>55</v>
       </c>
@@ -9752,7 +10424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="576" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="576" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
         <v>9</v>
       </c>
@@ -9766,7 +10438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="577" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="577" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
         <v>88</v>
       </c>
@@ -9780,7 +10452,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="578" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="578" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
         <v>55</v>
       </c>
@@ -9794,7 +10466,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="579" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="579" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
         <v>5</v>
       </c>
@@ -9808,7 +10480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="580" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="580" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
         <v>8</v>
       </c>
@@ -9822,7 +10494,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="581" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="581" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
         <v>6</v>
       </c>
@@ -9836,7 +10508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="582" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="582" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
         <v>19</v>
       </c>
@@ -9850,7 +10522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="583" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="583" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
         <v>23</v>
       </c>
@@ -9864,7 +10536,7 @@
         <v>6.92</v>
       </c>
     </row>
-    <row r="584" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="584" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
         <v>55</v>
       </c>
@@ -9878,7 +10550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="585" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="585" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
         <v>9</v>
       </c>
@@ -9892,7 +10564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="586" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="586" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
         <v>88</v>
       </c>
@@ -9906,7 +10578,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="587" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="587" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
         <v>55</v>
       </c>
@@ -9920,7 +10592,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="588" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="588" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
         <v>5</v>
       </c>
@@ -9934,7 +10606,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="589" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="589" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
         <v>8</v>
       </c>
@@ -9948,7 +10620,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="590" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="590" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
         <v>6</v>
       </c>
@@ -9962,7 +10634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="591" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="591" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
         <v>19</v>
       </c>
@@ -9976,7 +10648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="592" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="592" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
         <v>23</v>
       </c>
@@ -9990,7 +10662,7 @@
         <v>7.38</v>
       </c>
     </row>
-    <row r="593" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="593" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
         <v>55</v>
       </c>
@@ -10004,7 +10676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="594" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="594" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
         <v>9</v>
       </c>
@@ -10018,7 +10690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="595" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="595" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
         <v>88</v>
       </c>
@@ -10032,7 +10704,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="596" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="596" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
         <v>55</v>
       </c>
@@ -10046,7 +10718,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="597" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="597" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
         <v>5</v>
       </c>
@@ -10060,7 +10732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="598" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="598" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
         <v>8</v>
       </c>
@@ -10074,7 +10746,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="599" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="599" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A599" t="s">
         <v>6</v>
       </c>
@@ -10088,7 +10760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="600" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="600" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A600" t="s">
         <v>19</v>
       </c>
@@ -10102,7 +10774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="601" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="601" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
         <v>23</v>
       </c>
@@ -10116,7 +10788,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="602" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="602" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A602" t="s">
         <v>55</v>
       </c>
@@ -10130,7 +10802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="603" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="603" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A603" t="s">
         <v>9</v>
       </c>
@@ -10144,7 +10816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="604" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="604" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A604" t="s">
         <v>88</v>
       </c>
@@ -10158,7 +10830,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="605" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="605" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
         <v>55</v>
       </c>
@@ -10172,7 +10844,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="606" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="606" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
         <v>5</v>
       </c>
@@ -10186,7 +10858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="607" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="607" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
         <v>8</v>
       </c>
@@ -10200,7 +10872,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="608" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="608" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
         <v>6</v>
       </c>
@@ -10214,7 +10886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="609" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="609" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
         <v>19</v>
       </c>
@@ -10228,7 +10900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="610" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="610" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A610" t="s">
         <v>23</v>
       </c>
@@ -10242,7 +10914,7 @@
         <v>3.57</v>
       </c>
     </row>
-    <row r="611" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="611" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
         <v>55</v>
       </c>
@@ -10256,7 +10928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="612" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="612" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A612" t="s">
         <v>9</v>
       </c>
@@ -10270,7 +10942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="613" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="613" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A613" t="s">
         <v>88</v>
       </c>
@@ -10284,7 +10956,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="614" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="614" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A614" t="s">
         <v>55</v>
       </c>
@@ -10298,7 +10970,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="615" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="615" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
         <v>5</v>
       </c>
@@ -10312,7 +10984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="616" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="616" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A616" t="s">
         <v>8</v>
       </c>
@@ -10326,7 +10998,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="617" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="617" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
         <v>6</v>
       </c>
@@ -10340,7 +11012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="618" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="618" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A618" t="s">
         <v>19</v>
       </c>
@@ -10354,7 +11026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="619" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="619" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A619" t="s">
         <v>23</v>
       </c>
@@ -10368,7 +11040,7 @@
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="620" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="620" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
         <v>55</v>
       </c>
@@ -10382,7 +11054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="621" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="621" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A621" t="s">
         <v>9</v>
       </c>
@@ -10396,7 +11068,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="622" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="622" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A622" t="s">
         <v>88</v>
       </c>
@@ -10410,7 +11082,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="623" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="623" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A623" t="s">
         <v>55</v>
       </c>
@@ -10424,7 +11096,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="624" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="624" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A624" t="s">
         <v>5</v>
       </c>
@@ -10438,7 +11110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="625" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="625" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A625" t="s">
         <v>8</v>
       </c>
@@ -10452,7 +11124,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="626" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="626" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A626" t="s">
         <v>6</v>
       </c>
@@ -10466,7 +11138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="627" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="627" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A627" t="s">
         <v>19</v>
       </c>
@@ -10480,7 +11152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="628" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="628" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A628" t="s">
         <v>23</v>
       </c>
@@ -10494,7 +11166,7 @@
         <v>2.82</v>
       </c>
     </row>
-    <row r="629" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="629" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A629" t="s">
         <v>55</v>
       </c>
@@ -10508,7 +11180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="630" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="630" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A630" t="s">
         <v>9</v>
       </c>
@@ -10522,7 +11194,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="631" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="631" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A631" t="s">
         <v>88</v>
       </c>
@@ -10536,7 +11208,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="632" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="632" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A632" t="s">
         <v>55</v>
       </c>
@@ -10550,7 +11222,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="633" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="633" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A633" t="s">
         <v>5</v>
       </c>
@@ -10564,7 +11236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="634" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="634" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A634" t="s">
         <v>8</v>
       </c>
@@ -10578,7 +11250,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="635" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="635" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A635" t="s">
         <v>6</v>
       </c>
@@ -10592,7 +11264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="636" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="636" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A636" t="s">
         <v>19</v>
       </c>
@@ -10606,7 +11278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="637" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="637" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A637" t="s">
         <v>23</v>
       </c>
@@ -10620,7 +11292,7 @@
         <v>3.96</v>
       </c>
     </row>
-    <row r="638" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="638" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A638" t="s">
         <v>55</v>
       </c>
@@ -10634,7 +11306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="639" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="639" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A639" t="s">
         <v>9</v>
       </c>
@@ -10648,7 +11320,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="640" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="640" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A640" t="s">
         <v>88</v>
       </c>
@@ -10662,7 +11334,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="641" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="641" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A641" t="s">
         <v>55</v>
       </c>
@@ -10676,7 +11348,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="642" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="642" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A642" t="s">
         <v>5</v>
       </c>
@@ -10690,7 +11362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="643" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="643" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A643" t="s">
         <v>8</v>
       </c>
@@ -10704,7 +11376,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="644" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="644" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A644" t="s">
         <v>6</v>
       </c>
@@ -10718,7 +11390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="645" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="645" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A645" t="s">
         <v>19</v>
       </c>
@@ -10732,7 +11404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="646" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="646" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A646" t="s">
         <v>23</v>
       </c>
@@ -10746,7 +11418,7 @@
         <v>2.34</v>
       </c>
     </row>
-    <row r="647" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="647" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A647" t="s">
         <v>55</v>
       </c>
@@ -10760,7 +11432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="648" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="648" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A648" t="s">
         <v>9</v>
       </c>
@@ -10774,7 +11446,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="649" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="649" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A649" t="s">
         <v>88</v>
       </c>
@@ -10788,7 +11460,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="650" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="650" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A650" t="s">
         <v>62</v>
       </c>
@@ -10802,7 +11474,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="651" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="651" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A651" t="s">
         <v>63</v>
       </c>
@@ -10816,7 +11488,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="652" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="652" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A652" t="s">
         <v>62</v>
       </c>
@@ -10830,7 +11502,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="653" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="653" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A653" t="s">
         <v>63</v>
       </c>
@@ -10844,7 +11516,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="654" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="654" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A654" t="s">
         <v>62</v>
       </c>
@@ -10858,7 +11530,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="655" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="655" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A655" t="s">
         <v>63</v>
       </c>
@@ -10872,7 +11544,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="656" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="656" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A656" t="s">
         <v>62</v>
       </c>
@@ -10886,7 +11558,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="657" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="657" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A657" t="s">
         <v>63</v>
       </c>
@@ -10900,7 +11572,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="658" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="658" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A658" t="s">
         <v>62</v>
       </c>
@@ -10914,7 +11586,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="659" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="659" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A659" t="s">
         <v>63</v>
       </c>
@@ -10928,7 +11600,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="660" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="660" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A660" t="s">
         <v>62</v>
       </c>
@@ -10942,7 +11614,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="661" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="661" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A661" t="s">
         <v>63</v>
       </c>
@@ -10956,7 +11628,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="662" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="662" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A662" t="s">
         <v>62</v>
       </c>
@@ -10970,7 +11642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="663" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="663" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A663" t="s">
         <v>63</v>
       </c>
@@ -10984,7 +11656,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="664" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="664" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A664" t="s">
         <v>62</v>
       </c>
@@ -10998,7 +11670,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="665" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="665" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A665" t="s">
         <v>63</v>
       </c>
@@ -11012,7 +11684,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="666" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="666" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A666" t="s">
         <v>62</v>
       </c>
@@ -11026,7 +11698,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="667" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="667" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A667" t="s">
         <v>63</v>
       </c>
@@ -11040,7 +11712,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="668" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="668" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A668" t="s">
         <v>62</v>
       </c>
@@ -11054,7 +11726,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="669" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="669" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A669" t="s">
         <v>63</v>
       </c>
@@ -11068,7 +11740,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="670" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="670" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A670" t="s">
         <v>62</v>
       </c>
@@ -11082,7 +11754,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="671" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="671" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A671" t="s">
         <v>63</v>
       </c>
@@ -11096,7 +11768,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="672" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="672" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A672" t="s">
         <v>62</v>
       </c>
@@ -11110,7 +11782,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="673" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="673" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A673" t="s">
         <v>63</v>
       </c>
@@ -11124,7 +11796,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="674" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="674" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A674" t="s">
         <v>62</v>
       </c>
@@ -11138,7 +11810,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="675" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="675" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A675" t="s">
         <v>63</v>
       </c>
@@ -11152,7 +11824,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="676" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="676" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A676" t="s">
         <v>62</v>
       </c>
@@ -11166,7 +11838,7 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="677" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="677" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A677" t="s">
         <v>63</v>
       </c>
@@ -11180,7 +11852,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="678" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="678" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A678" t="s">
         <v>62</v>
       </c>
@@ -11194,7 +11866,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="679" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="679" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A679" t="s">
         <v>63</v>
       </c>
@@ -11208,7 +11880,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="680" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="680" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A680" t="s">
         <v>62</v>
       </c>
@@ -11222,7 +11894,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="681" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="681" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A681" t="s">
         <v>63</v>
       </c>
@@ -11236,7 +11908,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="682" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="682" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A682" t="s">
         <v>62</v>
       </c>
@@ -11250,7 +11922,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="683" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="683" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A683" t="s">
         <v>63</v>
       </c>
@@ -11264,7 +11936,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="684" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="684" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A684" t="s">
         <v>62</v>
       </c>
@@ -11278,7 +11950,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="685" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="685" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A685" t="s">
         <v>63</v>
       </c>
@@ -11292,7 +11964,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="686" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="686" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A686" t="s">
         <v>62</v>
       </c>
@@ -11306,7 +11978,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="687" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="687" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A687" t="s">
         <v>63</v>
       </c>
@@ -11320,7 +11992,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="688" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="688" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A688" t="s">
         <v>62</v>
       </c>
@@ -11334,7 +12006,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="689" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="689" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A689" t="s">
         <v>63</v>
       </c>
@@ -11348,7 +12020,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="690" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="690" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A690" t="s">
         <v>62</v>
       </c>
@@ -11362,7 +12034,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="691" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="691" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A691" t="s">
         <v>63</v>
       </c>
@@ -11376,7 +12048,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="692" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="692" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A692" t="s">
         <v>62</v>
       </c>
@@ -11390,7 +12062,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="693" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="693" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A693" t="s">
         <v>63</v>
       </c>
@@ -11404,7 +12076,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="694" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="694" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A694" t="s">
         <v>62</v>
       </c>
@@ -11418,7 +12090,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="695" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="695" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A695" t="s">
         <v>63</v>
       </c>
@@ -11432,7 +12104,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="696" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="696" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A696" t="s">
         <v>62</v>
       </c>
@@ -11446,7 +12118,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="697" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="697" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A697" t="s">
         <v>63</v>
       </c>

--- a/VerveStacks_EST/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_Base_VS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A137AE38-A6B2-4249-B163-6EA6F1A2042D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27DF836C-4FCF-4835-B61A-C53748507AF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="re_targets" sheetId="5" r:id="rId1"/>
@@ -124,7 +124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1666" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1685" uniqueCount="135">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -481,6 +481,57 @@
   </si>
   <si>
     <t>share_of_generation_pct</t>
+  </si>
+  <si>
+    <t>Additions by Kristopher</t>
+  </si>
+  <si>
+    <t>PP_RENEW</t>
+  </si>
+  <si>
+    <t>Pset_Set</t>
+  </si>
+  <si>
+    <t>Pset_PN</t>
+  </si>
+  <si>
+    <t>Pset_CI</t>
+  </si>
+  <si>
+    <t>Pset_CO</t>
+  </si>
+  <si>
+    <t>Cset_CN</t>
+  </si>
+  <si>
+    <t>LimType</t>
+  </si>
+  <si>
+    <t>UC_FLO</t>
+  </si>
+  <si>
+    <t>UC_RHSRTS</t>
+  </si>
+  <si>
+    <t>UC_RHSRTS~0</t>
+  </si>
+  <si>
+    <t>UC_Desc</t>
+  </si>
+  <si>
+    <t>ELC</t>
+  </si>
+  <si>
+    <t>LO</t>
+  </si>
+  <si>
+    <t>Minimum renewable power plants penetration</t>
+  </si>
+  <si>
+    <t>UC_min_renew_20235</t>
+  </si>
+  <si>
+    <t>~UC_T: UC_COMPRD</t>
   </si>
 </sst>
 </file>
@@ -490,7 +541,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -556,6 +607,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="186"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -616,7 +681,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -629,11 +694,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="4"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Heading 3" xfId="2" builtinId="18"/>
@@ -972,581 +1039,572 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9293F70F-DBAF-4231-9F91-306A64614683}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="B9:L25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B9" s="12" t="s">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
         <v>92</v>
       </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="12"/>
-      <c r="L9" s="12"/>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B10" s="12" t="s">
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
         <v>93</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" t="s">
         <v>94</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" t="s">
         <v>95</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" t="s">
         <v>96</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" t="s">
         <v>97</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G10" t="s">
         <v>98</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="H10" t="s">
         <v>99</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="I10" t="s">
         <v>100</v>
       </c>
-      <c r="J10" s="12" t="s">
+      <c r="J10" t="s">
         <v>101</v>
       </c>
-      <c r="K10" s="12" t="s">
+      <c r="K10" t="s">
         <v>102</v>
       </c>
-      <c r="L10" s="12" t="s">
+      <c r="L10" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="B11" s="12">
+    <row r="11" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="B11">
         <v>2030</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" t="s">
         <v>104</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" t="s">
         <v>105</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11">
         <v>0.36699999999999999</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" t="s">
         <v>106</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="G11" t="s">
         <v>107</v>
       </c>
-      <c r="H11" s="12" t="s">
+      <c r="H11" t="s">
         <v>108</v>
       </c>
-      <c r="I11" s="13">
+      <c r="I11" s="12">
         <v>45155</v>
       </c>
-      <c r="J11" s="12" t="s">
+      <c r="J11" t="s">
         <v>109</v>
       </c>
-      <c r="K11" s="14" t="s">
+      <c r="K11" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="L11" s="14" t="s">
+      <c r="L11" s="13" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="12" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="B12" s="12">
+    <row r="12" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="B12">
         <v>2030</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" t="s">
         <v>112</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" t="s">
         <v>105</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" t="s">
         <v>106</v>
       </c>
-      <c r="G12" s="12" t="s">
+      <c r="G12" t="s">
         <v>107</v>
       </c>
-      <c r="H12" s="12" t="s">
+      <c r="H12" t="s">
         <v>108</v>
       </c>
-      <c r="I12" s="13">
+      <c r="I12" s="12">
         <v>45155</v>
       </c>
-      <c r="J12" s="12" t="s">
+      <c r="J12" t="s">
         <v>109</v>
       </c>
-      <c r="K12" s="14" t="s">
+      <c r="K12" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="L12" s="14" t="s">
+      <c r="L12" s="13" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="B13" s="12">
+    <row r="13" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="B13">
         <v>2030</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" t="s">
         <v>113</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" t="s">
         <v>105</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13">
         <v>1</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" t="s">
         <v>106</v>
       </c>
-      <c r="G13" s="12" t="s">
+      <c r="G13" t="s">
         <v>107</v>
       </c>
-      <c r="H13" s="12" t="s">
+      <c r="H13" t="s">
         <v>108</v>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="12">
         <v>45155</v>
       </c>
-      <c r="J13" s="12" t="s">
+      <c r="J13" t="s">
         <v>109</v>
       </c>
-      <c r="K13" s="14" t="s">
+      <c r="K13" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="L13" s="14" t="s">
+      <c r="L13" s="13" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="B14" s="12">
+    <row r="14" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="B14">
         <v>2030</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" t="s">
         <v>114</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" t="s">
         <v>105</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14">
         <v>1.31</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" t="s">
         <v>106</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="G14" t="s">
         <v>107</v>
       </c>
-      <c r="H14" s="12" t="s">
+      <c r="H14" t="s">
         <v>108</v>
       </c>
-      <c r="I14" s="13">
+      <c r="I14" s="12">
         <v>45155</v>
       </c>
-      <c r="J14" s="12" t="s">
+      <c r="J14" t="s">
         <v>109</v>
       </c>
-      <c r="K14" s="14" t="s">
+      <c r="K14" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="L14" s="14" t="s">
+      <c r="L14" s="13" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="15" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="B15" s="12">
+    <row r="15" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="B15">
         <v>2030</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" t="s">
         <v>115</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" t="s">
         <v>105</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E15">
         <v>1.2</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="F15" t="s">
         <v>106</v>
       </c>
-      <c r="G15" s="12" t="s">
+      <c r="G15" t="s">
         <v>107</v>
       </c>
-      <c r="H15" s="12" t="s">
+      <c r="H15" t="s">
         <v>108</v>
       </c>
-      <c r="I15" s="13">
+      <c r="I15" s="12">
         <v>45155</v>
       </c>
-      <c r="J15" s="12" t="s">
+      <c r="J15" t="s">
         <v>109</v>
       </c>
-      <c r="K15" s="14" t="s">
+      <c r="K15" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="L15" s="14" t="s">
+      <c r="L15" s="13" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="16" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="B16" s="12">
+    <row r="16" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="B16">
         <v>2030</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" t="s">
         <v>104</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" t="s">
         <v>116</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E16">
         <v>1.54</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F16" t="s">
         <v>106</v>
       </c>
-      <c r="G16" s="12" t="s">
+      <c r="G16" t="s">
         <v>107</v>
       </c>
-      <c r="H16" s="12" t="s">
+      <c r="H16" t="s">
         <v>108</v>
       </c>
-      <c r="I16" s="13">
+      <c r="I16" s="12">
         <v>45155</v>
       </c>
-      <c r="J16" s="12" t="s">
+      <c r="J16" t="s">
         <v>109</v>
       </c>
-      <c r="K16" s="14" t="s">
+      <c r="K16" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="L16" s="14" t="s">
+      <c r="L16" s="13" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="17" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="B17" s="12">
+    <row r="17" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="B17">
         <v>2030</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" t="s">
         <v>112</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" t="s">
         <v>116</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E17">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="F17" t="s">
         <v>106</v>
       </c>
-      <c r="G17" s="12" t="s">
+      <c r="G17" t="s">
         <v>107</v>
       </c>
-      <c r="H17" s="12" t="s">
+      <c r="H17" t="s">
         <v>108</v>
       </c>
-      <c r="I17" s="13">
+      <c r="I17" s="12">
         <v>45155</v>
       </c>
-      <c r="J17" s="12" t="s">
+      <c r="J17" t="s">
         <v>109</v>
       </c>
-      <c r="K17" s="14" t="s">
+      <c r="K17" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="L17" s="14" t="s">
+      <c r="L17" s="13" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="18" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="B18" s="12">
+    <row r="18" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="B18">
         <v>2030</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" t="s">
         <v>113</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" t="s">
         <v>116</v>
       </c>
-      <c r="E18" s="12">
+      <c r="E18">
         <v>3.7149999999999999</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="F18" t="s">
         <v>106</v>
       </c>
-      <c r="G18" s="12" t="s">
+      <c r="G18" t="s">
         <v>107</v>
       </c>
-      <c r="H18" s="12" t="s">
+      <c r="H18" t="s">
         <v>108</v>
       </c>
-      <c r="I18" s="13">
+      <c r="I18" s="12">
         <v>45155</v>
       </c>
-      <c r="J18" s="12" t="s">
+      <c r="J18" t="s">
         <v>109</v>
       </c>
-      <c r="K18" s="14" t="s">
+      <c r="K18" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="L18" s="14" t="s">
+      <c r="L18" s="13" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="19" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="B19" s="12">
+    <row r="19" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="B19">
         <v>2030</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" t="s">
         <v>114</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" t="s">
         <v>116</v>
       </c>
-      <c r="E19" s="12">
+      <c r="E19">
         <v>3.1240000000000001</v>
       </c>
-      <c r="F19" s="12" t="s">
+      <c r="F19" t="s">
         <v>106</v>
       </c>
-      <c r="G19" s="12" t="s">
+      <c r="G19" t="s">
         <v>107</v>
       </c>
-      <c r="H19" s="12" t="s">
+      <c r="H19" t="s">
         <v>108</v>
       </c>
-      <c r="I19" s="13">
+      <c r="I19" s="12">
         <v>45155</v>
       </c>
-      <c r="J19" s="12" t="s">
+      <c r="J19" t="s">
         <v>109</v>
       </c>
-      <c r="K19" s="14" t="s">
+      <c r="K19" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="L19" s="14" t="s">
+      <c r="L19" s="13" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="20" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="B20" s="12">
+    <row r="20" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="B20">
         <v>2030</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" t="s">
         <v>115</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" t="s">
         <v>116</v>
       </c>
-      <c r="E20" s="12">
+      <c r="E20">
         <v>1</v>
       </c>
-      <c r="F20" s="12" t="s">
+      <c r="F20" t="s">
         <v>106</v>
       </c>
-      <c r="G20" s="12" t="s">
+      <c r="G20" t="s">
         <v>107</v>
       </c>
-      <c r="H20" s="12" t="s">
+      <c r="H20" t="s">
         <v>108</v>
       </c>
-      <c r="I20" s="13">
+      <c r="I20" s="12">
         <v>45155</v>
       </c>
-      <c r="J20" s="12" t="s">
+      <c r="J20" t="s">
         <v>109</v>
       </c>
-      <c r="K20" s="14" t="s">
+      <c r="K20" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="L20" s="14" t="s">
+      <c r="L20" s="13" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="21" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="B21" s="12">
+    <row r="21" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="B21">
         <v>2030</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" t="s">
         <v>104</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" t="s">
         <v>117</v>
       </c>
-      <c r="E21" s="12">
+      <c r="E21">
         <v>16.376000000000001</v>
       </c>
-      <c r="F21" s="12" t="s">
+      <c r="F21" t="s">
         <v>106</v>
       </c>
-      <c r="G21" s="12" t="s">
+      <c r="G21" t="s">
         <v>107</v>
       </c>
-      <c r="H21" s="12" t="s">
+      <c r="H21" t="s">
         <v>108</v>
       </c>
-      <c r="I21" s="13">
+      <c r="I21" s="12">
         <v>45155</v>
       </c>
-      <c r="J21" s="12" t="s">
+      <c r="J21" t="s">
         <v>109</v>
       </c>
-      <c r="K21" s="14" t="s">
+      <c r="K21" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="L21" s="14" t="s">
+      <c r="L21" s="13" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="22" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="B22" s="12">
+    <row r="22" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="B22">
         <v>2030</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" t="s">
         <v>112</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" t="s">
         <v>117</v>
       </c>
-      <c r="E22" s="12">
+      <c r="E22">
         <v>0.26600000000000001</v>
       </c>
-      <c r="F22" s="12" t="s">
+      <c r="F22" t="s">
         <v>106</v>
       </c>
-      <c r="G22" s="12" t="s">
+      <c r="G22" t="s">
         <v>107</v>
       </c>
-      <c r="H22" s="12" t="s">
+      <c r="H22" t="s">
         <v>108</v>
       </c>
-      <c r="I22" s="13">
+      <c r="I22" s="12">
         <v>45155</v>
       </c>
-      <c r="J22" s="12" t="s">
+      <c r="J22" t="s">
         <v>109</v>
       </c>
-      <c r="K22" s="14" t="s">
+      <c r="K22" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="L22" s="14" t="s">
+      <c r="L22" s="13" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="23" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="B23" s="12">
+    <row r="23" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="B23">
         <v>2030</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" t="s">
         <v>113</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" t="s">
         <v>117</v>
       </c>
-      <c r="E23" s="12">
+      <c r="E23">
         <v>39.503999999999998</v>
       </c>
-      <c r="F23" s="12" t="s">
+      <c r="F23" t="s">
         <v>106</v>
       </c>
-      <c r="G23" s="12" t="s">
+      <c r="G23" t="s">
         <v>107</v>
       </c>
-      <c r="H23" s="12" t="s">
+      <c r="H23" t="s">
         <v>108</v>
       </c>
-      <c r="I23" s="13">
+      <c r="I23" s="12">
         <v>45155</v>
       </c>
-      <c r="J23" s="12" t="s">
+      <c r="J23" t="s">
         <v>109</v>
       </c>
-      <c r="K23" s="14" t="s">
+      <c r="K23" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="L23" s="14" t="s">
+      <c r="L23" s="13" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="24" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="B24" s="12">
+    <row r="24" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="B24">
         <v>2030</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" t="s">
         <v>114</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" t="s">
         <v>117</v>
       </c>
-      <c r="E24" s="12">
+      <c r="E24">
         <v>33.22</v>
       </c>
-      <c r="F24" s="12" t="s">
+      <c r="F24" t="s">
         <v>106</v>
       </c>
-      <c r="G24" s="12" t="s">
+      <c r="G24" t="s">
         <v>107</v>
       </c>
-      <c r="H24" s="12" t="s">
+      <c r="H24" t="s">
         <v>108</v>
       </c>
-      <c r="I24" s="13">
+      <c r="I24" s="12">
         <v>45155</v>
       </c>
-      <c r="J24" s="12" t="s">
+      <c r="J24" t="s">
         <v>109</v>
       </c>
-      <c r="K24" s="14" t="s">
+      <c r="K24" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="L24" s="14" t="s">
+      <c r="L24" s="13" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="25" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="B25" s="12">
+    <row r="25" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="B25">
         <v>2030</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C25" t="s">
         <v>115</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="D25" t="s">
         <v>117</v>
       </c>
-      <c r="E25" s="12">
+      <c r="E25">
         <v>10.634</v>
       </c>
-      <c r="F25" s="12" t="s">
+      <c r="F25" t="s">
         <v>106</v>
       </c>
-      <c r="G25" s="12" t="s">
+      <c r="G25" t="s">
         <v>107</v>
       </c>
-      <c r="H25" s="12" t="s">
+      <c r="H25" t="s">
         <v>108</v>
       </c>
-      <c r="I25" s="13">
+      <c r="I25" s="12">
         <v>45155</v>
       </c>
-      <c r="J25" s="12" t="s">
+      <c r="J25" t="s">
         <v>109</v>
       </c>
-      <c r="K25" s="14" t="s">
+      <c r="K25" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="L25" s="14" t="s">
+      <c r="L25" s="13" t="s">
         <v>111</v>
       </c>
     </row>
@@ -1557,41 +1615,45 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AL40"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="10.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.6328125" customWidth="1"/>
-    <col min="5" max="5" width="9.54296875" customWidth="1"/>
-    <col min="6" max="6" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="10.7265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.6328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.90625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.26953125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.08984375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="4.1796875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.7265625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.1796875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.7265625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="24" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.36328125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="7.08984375" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="4.7265625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="23.7265625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="6.36328125" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="7" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="4.7265625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5703125" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="27" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="12" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="AB1">
         <v>1.1000000000000001</v>
       </c>
@@ -1599,7 +1661,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
       <c r="F2" s="6" t="s">
         <v>50</v>
       </c>
@@ -1616,7 +1678,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>0</v>
       </c>
@@ -1639,7 +1701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>48</v>
       </c>
@@ -1664,7 +1726,7 @@
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>87</v>
       </c>
@@ -1684,7 +1746,7 @@
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>0.28000000000000003</v>
       </c>
@@ -1720,7 +1782,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>83</v>
       </c>
@@ -1787,7 +1849,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>19</v>
       </c>
@@ -1865,7 +1927,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
       <c r="F9" t="s">
         <v>9</v>
       </c>
@@ -1933,7 +1995,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:38" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:38" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F10" t="s">
         <v>88</v>
       </c>
@@ -1950,13 +2012,13 @@
         <v>0.30393385477435431</v>
       </c>
     </row>
-    <row r="11" spans="1:38" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:38" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>26</v>
       </c>
@@ -1964,7 +2026,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>27</v>
       </c>
@@ -2002,7 +2064,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>29</v>
       </c>
@@ -2040,27 +2102,33 @@
         <v>86</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.25">
       <c r="L16" s="7" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:32" x14ac:dyDescent="0.25">
       <c r="L17" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:32" x14ac:dyDescent="0.25">
       <c r="L18" s="7" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="U18" s="14" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="20" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="AC20" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="21" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>27</v>
       </c>
@@ -2079,8 +2147,44 @@
       <c r="G21" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="U21" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="V21" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="W21" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="X21" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="Y21" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z21" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="AA21" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="AB21" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC21" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="AD21" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="AE21" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF21" s="16" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="22" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>32</v>
       </c>
@@ -2097,8 +2201,32 @@
       <c r="I22">
         <v>94</v>
       </c>
-    </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="U22" t="s">
+        <v>133</v>
+      </c>
+      <c r="V22" t="s">
+        <v>119</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>130</v>
+      </c>
+      <c r="AA22">
+        <v>2035</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>131</v>
+      </c>
+      <c r="AC22" s="15">
+        <v>-0.65</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="23" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>32</v>
       </c>
@@ -2115,8 +2243,10 @@
       <c r="I23">
         <v>55</v>
       </c>
-    </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="AE23" s="15"/>
+      <c r="AF23" s="15"/>
+    </row>
+    <row r="24" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>32</v>
       </c>
@@ -2134,7 +2264,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>44</v>
       </c>
@@ -2148,7 +2278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>44</v>
       </c>
@@ -2162,7 +2292,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>49</v>
       </c>
@@ -2177,7 +2307,7 @@
         <v>co2captured</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>65</v>
       </c>
@@ -2188,7 +2318,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>67</v>
       </c>
@@ -2199,12 +2329,12 @@
         <v>66</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
       <c r="E35" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>13</v>
       </c>
@@ -2221,7 +2351,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>39</v>
       </c>
@@ -2235,7 +2365,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
       <c r="D38" t="s">
         <v>9</v>
       </c>
@@ -2243,7 +2373,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>41</v>
       </c>
@@ -2257,7 +2387,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
       <c r="D40" t="s">
         <v>84</v>
       </c>
@@ -2274,27 +2404,28 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{320A1887-1B0C-44A8-9658-90FD86FEE0A5}">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="A9:J23"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.26953125" customWidth="1"/>
-    <col min="3" max="3" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.28515625" customWidth="1"/>
+    <col min="3" max="3" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>90</v>
       </c>
@@ -2323,7 +2454,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>91</v>
       </c>
@@ -2352,17 +2483,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="9" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:8" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
         <v>48</v>
       </c>
@@ -2388,7 +2519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -2418,7 +2549,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>12</v>
       </c>
@@ -2448,7 +2579,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -2478,7 +2609,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>19</v>
       </c>
@@ -2515,10 +2646,11 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC33DFE9-8C65-4A33-8FAE-96323628CE2A}">
+  <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:D697"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>50</v>
       </c>
@@ -2532,7 +2664,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>55</v>
       </c>
@@ -2546,7 +2678,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -2560,7 +2692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -2574,7 +2706,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -2588,7 +2720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -2602,7 +2734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -2616,7 +2748,7 @@
         <v>7.9</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>55</v>
       </c>
@@ -2630,7 +2762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -2644,7 +2776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>88</v>
       </c>
@@ -2658,7 +2790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -2672,7 +2804,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -2686,7 +2818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -2700,7 +2832,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -2714,7 +2846,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -2728,7 +2860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -2742,7 +2874,7 @@
         <v>7.87</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>55</v>
       </c>
@@ -2756,7 +2888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>9</v>
       </c>
@@ -2770,7 +2902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>88</v>
       </c>
@@ -2784,7 +2916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>55</v>
       </c>
@@ -2798,7 +2930,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>5</v>
       </c>
@@ -2812,7 +2944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -2826,7 +2958,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -2840,7 +2972,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>19</v>
       </c>
@@ -2854,7 +2986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -2868,7 +3000,7 @@
         <v>7.97</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -2882,7 +3014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>9</v>
       </c>
@@ -2896,7 +3028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>88</v>
       </c>
@@ -2910,7 +3042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>55</v>
       </c>
@@ -2924,7 +3056,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>5</v>
       </c>
@@ -2938,7 +3070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>8</v>
       </c>
@@ -2952,7 +3084,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>6</v>
       </c>
@@ -2966,7 +3098,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>19</v>
       </c>
@@ -2980,7 +3112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>23</v>
       </c>
@@ -2994,7 +3126,7 @@
         <v>9.61</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>55</v>
       </c>
@@ -3008,7 +3140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>9</v>
       </c>
@@ -3022,7 +3154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>88</v>
       </c>
@@ -3036,7 +3168,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>55</v>
       </c>
@@ -3050,7 +3182,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>5</v>
       </c>
@@ -3064,7 +3196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>8</v>
       </c>
@@ -3078,7 +3210,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>6</v>
       </c>
@@ -3092,7 +3224,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>19</v>
       </c>
@@ -3106,7 +3238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>23</v>
       </c>
@@ -3120,7 +3252,7 @@
         <v>9.76</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>55</v>
       </c>
@@ -3134,7 +3266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>9</v>
       </c>
@@ -3148,7 +3280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>88</v>
       </c>
@@ -3162,7 +3294,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>55</v>
       </c>
@@ -3176,7 +3308,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>5</v>
       </c>
@@ -3190,7 +3322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>8</v>
       </c>
@@ -3204,7 +3336,7 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>6</v>
       </c>
@@ -3218,7 +3350,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>19</v>
       </c>
@@ -3232,7 +3364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>23</v>
       </c>
@@ -3246,7 +3378,7 @@
         <v>9.5500000000000007</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>55</v>
       </c>
@@ -3260,7 +3392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>9</v>
       </c>
@@ -3274,7 +3406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>88</v>
       </c>
@@ -3288,7 +3420,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>55</v>
       </c>
@@ -3302,7 +3434,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>5</v>
       </c>
@@ -3316,7 +3448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>8</v>
       </c>
@@ -3330,7 +3462,7 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>6</v>
       </c>
@@ -3344,7 +3476,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>19</v>
       </c>
@@ -3358,7 +3490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>23</v>
       </c>
@@ -3372,7 +3504,7 @@
         <v>9.06</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>55</v>
       </c>
@@ -3386,7 +3518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>9</v>
       </c>
@@ -3400,7 +3532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>88</v>
       </c>
@@ -3414,7 +3546,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>55</v>
       </c>
@@ -3428,7 +3560,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>5</v>
       </c>
@@ -3442,7 +3574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>8</v>
       </c>
@@ -3456,7 +3588,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>6</v>
       </c>
@@ -3470,7 +3602,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>19</v>
       </c>
@@ -3484,7 +3616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>23</v>
       </c>
@@ -3498,7 +3630,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>55</v>
       </c>
@@ -3512,7 +3644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>9</v>
       </c>
@@ -3526,7 +3658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>88</v>
       </c>
@@ -3540,7 +3672,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>55</v>
       </c>
@@ -3554,7 +3686,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>5</v>
       </c>
@@ -3568,7 +3700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>8</v>
       </c>
@@ -3582,7 +3714,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>6</v>
       </c>
@@ -3596,7 +3728,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>19</v>
       </c>
@@ -3610,7 +3742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>23</v>
       </c>
@@ -3624,7 +3756,7 @@
         <v>9.9600000000000009</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>55</v>
       </c>
@@ -3638,7 +3770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>9</v>
       </c>
@@ -3652,7 +3784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>88</v>
       </c>
@@ -3666,7 +3798,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>55</v>
       </c>
@@ -3680,7 +3812,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>5</v>
       </c>
@@ -3694,7 +3826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>8</v>
       </c>
@@ -3708,7 +3840,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>6</v>
       </c>
@@ -3722,7 +3854,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>19</v>
       </c>
@@ -3736,7 +3868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>23</v>
       </c>
@@ -3750,7 +3882,7 @@
         <v>8.1300000000000008</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>55</v>
       </c>
@@ -3764,7 +3896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>9</v>
       </c>
@@ -3778,7 +3910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>88</v>
       </c>
@@ -3792,7 +3924,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>55</v>
       </c>
@@ -3806,7 +3938,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>5</v>
       </c>
@@ -3820,7 +3952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>8</v>
       </c>
@@ -3834,7 +3966,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>6</v>
       </c>
@@ -3848,7 +3980,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>19</v>
       </c>
@@ -3862,7 +3994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>23</v>
       </c>
@@ -3876,7 +4008,7 @@
         <v>11.62</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>55</v>
       </c>
@@ -3890,7 +4022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>9</v>
       </c>
@@ -3904,7 +4036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>88</v>
       </c>
@@ -3918,7 +4050,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>55</v>
       </c>
@@ -3932,7 +4064,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>5</v>
       </c>
@@ -3946,7 +4078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>8</v>
       </c>
@@ -3960,7 +4092,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>6</v>
       </c>
@@ -3974,7 +4106,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>19</v>
       </c>
@@ -3988,7 +4120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>23</v>
       </c>
@@ -4002,7 +4134,7 @@
         <v>11.46</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>55</v>
       </c>
@@ -4016,7 +4148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>9</v>
       </c>
@@ -4030,7 +4162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>88</v>
       </c>
@@ -4044,7 +4176,7 @@
         <v>0.37</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>55</v>
       </c>
@@ -4058,7 +4190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>5</v>
       </c>
@@ -4072,7 +4204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>8</v>
       </c>
@@ -4086,7 +4218,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>6</v>
       </c>
@@ -4100,7 +4232,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>19</v>
       </c>
@@ -4114,7 +4246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>23</v>
       </c>
@@ -4128,7 +4260,7 @@
         <v>10.36</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>55</v>
       </c>
@@ -4142,7 +4274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>9</v>
       </c>
@@ -4156,7 +4288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>88</v>
       </c>
@@ -4170,7 +4302,7 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>55</v>
       </c>
@@ -4184,7 +4316,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>5</v>
       </c>
@@ -4198,7 +4330,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>8</v>
       </c>
@@ -4212,7 +4344,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>6</v>
       </c>
@@ -4226,7 +4358,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>19</v>
       </c>
@@ -4240,7 +4372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>23</v>
       </c>
@@ -4254,7 +4386,7 @@
         <v>11.95</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>55</v>
       </c>
@@ -4268,7 +4400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>9</v>
       </c>
@@ -4282,7 +4414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>88</v>
       </c>
@@ -4296,7 +4428,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>55</v>
       </c>
@@ -4310,7 +4442,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>5</v>
       </c>
@@ -4324,7 +4456,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>8</v>
       </c>
@@ -4338,7 +4470,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>6</v>
       </c>
@@ -4352,7 +4484,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>19</v>
       </c>
@@ -4366,7 +4498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>23</v>
       </c>
@@ -4380,7 +4512,7 @@
         <v>10.98</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>55</v>
       </c>
@@ -4394,7 +4526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>9</v>
       </c>
@@ -4408,7 +4540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>88</v>
       </c>
@@ -4422,7 +4554,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>55</v>
       </c>
@@ -4436,7 +4568,7 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>5</v>
       </c>
@@ -4450,7 +4582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>8</v>
       </c>
@@ -4464,7 +4596,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>6</v>
       </c>
@@ -4478,7 +4610,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>19</v>
       </c>
@@ -4492,7 +4624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>23</v>
       </c>
@@ -4506,7 +4638,7 @@
         <v>8.5299999999999994</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>55</v>
       </c>
@@ -4520,7 +4652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>9</v>
       </c>
@@ -4534,7 +4666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>88</v>
       </c>
@@ -4548,7 +4680,7 @@
         <v>0.71</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>55</v>
       </c>
@@ -4562,7 +4694,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>5</v>
       </c>
@@ -4576,7 +4708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>8</v>
       </c>
@@ -4590,7 +4722,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>6</v>
       </c>
@@ -4604,7 +4736,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>19</v>
       </c>
@@ -4618,7 +4750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>23</v>
       </c>
@@ -4632,7 +4764,7 @@
         <v>10.51</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>55</v>
       </c>
@@ -4646,7 +4778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>9</v>
       </c>
@@ -4660,7 +4792,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>88</v>
       </c>
@@ -4674,7 +4806,7 @@
         <v>0.59</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>55</v>
       </c>
@@ -4688,7 +4820,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>5</v>
       </c>
@@ -4702,7 +4834,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>8</v>
       </c>
@@ -4716,7 +4848,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>6</v>
       </c>
@@ -4730,7 +4862,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>19</v>
       </c>
@@ -4744,7 +4876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>23</v>
       </c>
@@ -4758,7 +4890,7 @@
         <v>11.22</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>55</v>
       </c>
@@ -4772,7 +4904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>9</v>
       </c>
@@ -4786,7 +4918,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>88</v>
       </c>
@@ -4800,7 +4932,7 @@
         <v>0.72</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>55</v>
       </c>
@@ -4814,7 +4946,7 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>5</v>
       </c>
@@ -4828,7 +4960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>8</v>
       </c>
@@ -4842,7 +4974,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>6</v>
       </c>
@@ -4856,7 +4988,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>19</v>
       </c>
@@ -4870,7 +5002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>23</v>
       </c>
@@ -4884,7 +5016,7 @@
         <v>10.32</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>55</v>
       </c>
@@ -4898,7 +5030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>9</v>
       </c>
@@ -4912,7 +5044,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>88</v>
       </c>
@@ -4926,7 +5058,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>55</v>
       </c>
@@ -4940,7 +5072,7 @@
         <v>1.36</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>5</v>
       </c>
@@ -4954,7 +5086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>8</v>
       </c>
@@ -4968,7 +5100,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>6</v>
       </c>
@@ -4982,7 +5114,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>19</v>
       </c>
@@ -4996,7 +5128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>23</v>
       </c>
@@ -5010,7 +5142,7 @@
         <v>5.43</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>55</v>
       </c>
@@ -5024,7 +5156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>9</v>
       </c>
@@ -5038,7 +5170,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>88</v>
       </c>
@@ -5052,7 +5184,7 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>55</v>
       </c>
@@ -5066,7 +5198,7 @@
         <v>1.85</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>5</v>
       </c>
@@ -5080,7 +5212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>8</v>
       </c>
@@ -5094,7 +5226,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>6</v>
       </c>
@@ -5108,7 +5240,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>19</v>
       </c>
@@ -5122,7 +5254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>23</v>
       </c>
@@ -5136,7 +5268,7 @@
         <v>3.08</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>55</v>
       </c>
@@ -5150,7 +5282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>9</v>
       </c>
@@ -5164,7 +5296,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>88</v>
       </c>
@@ -5178,7 +5310,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>55</v>
       </c>
@@ -5192,7 +5324,7 @@
         <v>1.77</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>5</v>
       </c>
@@ -5206,7 +5338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>8</v>
       </c>
@@ -5220,7 +5352,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>6</v>
       </c>
@@ -5234,7 +5366,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>19</v>
       </c>
@@ -5248,7 +5380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>23</v>
       </c>
@@ -5262,7 +5394,7 @@
         <v>4.28</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>55</v>
       </c>
@@ -5276,7 +5408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>9</v>
       </c>
@@ -5290,7 +5422,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>88</v>
       </c>
@@ -5304,7 +5436,7 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>55</v>
       </c>
@@ -5318,7 +5450,7 @@
         <v>1.57</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>5</v>
       </c>
@@ -5332,7 +5464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>8</v>
       </c>
@@ -5346,7 +5478,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>6</v>
       </c>
@@ -5360,7 +5492,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>19</v>
       </c>
@@ -5374,7 +5506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>23</v>
       </c>
@@ -5388,7 +5520,7 @@
         <v>6.02</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>55</v>
       </c>
@@ -5402,7 +5534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>9</v>
       </c>
@@ -5416,7 +5548,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>88</v>
       </c>
@@ -5430,7 +5562,7 @@
         <v>0.63</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>55</v>
       </c>
@@ -5444,7 +5576,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>5</v>
       </c>
@@ -5458,7 +5590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>8</v>
       </c>
@@ -5472,7 +5604,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>6</v>
       </c>
@@ -5486,7 +5618,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>19</v>
       </c>
@@ -5500,7 +5632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>23</v>
       </c>
@@ -5514,7 +5646,7 @@
         <v>3.56</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>55</v>
       </c>
@@ -5528,7 +5660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>9</v>
       </c>
@@ -5542,7 +5674,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>88</v>
       </c>
@@ -5556,7 +5688,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>55</v>
       </c>
@@ -5570,7 +5702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>5</v>
       </c>
@@ -5581,7 +5713,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>8</v>
       </c>
@@ -5595,7 +5727,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>6</v>
       </c>
@@ -5609,7 +5741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>19</v>
       </c>
@@ -5620,7 +5752,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>23</v>
       </c>
@@ -5634,7 +5766,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>55</v>
       </c>
@@ -5648,7 +5780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>9</v>
       </c>
@@ -5662,7 +5794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>88</v>
       </c>
@@ -5676,7 +5808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>55</v>
       </c>
@@ -5690,7 +5822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>5</v>
       </c>
@@ -5701,7 +5833,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>8</v>
       </c>
@@ -5715,7 +5847,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>6</v>
       </c>
@@ -5729,7 +5861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>19</v>
       </c>
@@ -5740,7 +5872,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>23</v>
       </c>
@@ -5754,7 +5886,7 @@
         <v>2.44</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>55</v>
       </c>
@@ -5768,7 +5900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>9</v>
       </c>
@@ -5782,7 +5914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>88</v>
       </c>
@@ -5796,7 +5928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>55</v>
       </c>
@@ -5810,7 +5942,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>5</v>
       </c>
@@ -5821,7 +5953,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>8</v>
       </c>
@@ -5835,7 +5967,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>6</v>
       </c>
@@ -5849,7 +5981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>19</v>
       </c>
@@ -5860,7 +5992,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>23</v>
       </c>
@@ -5874,7 +6006,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>55</v>
       </c>
@@ -5888,7 +6020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>9</v>
       </c>
@@ -5902,7 +6034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>88</v>
       </c>
@@ -5916,7 +6048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>55</v>
       </c>
@@ -5930,7 +6062,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>5</v>
       </c>
@@ -5941,7 +6073,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>8</v>
       </c>
@@ -5955,7 +6087,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>6</v>
       </c>
@@ -5969,7 +6101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>19</v>
       </c>
@@ -5980,7 +6112,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>23</v>
       </c>
@@ -5994,7 +6126,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>55</v>
       </c>
@@ -6008,7 +6140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>9</v>
       </c>
@@ -6022,7 +6154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>88</v>
       </c>
@@ -6036,7 +6168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>55</v>
       </c>
@@ -6050,7 +6182,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>5</v>
       </c>
@@ -6061,7 +6193,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>8</v>
       </c>
@@ -6075,7 +6207,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>6</v>
       </c>
@@ -6089,7 +6221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>19</v>
       </c>
@@ -6100,7 +6232,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>23</v>
       </c>
@@ -6114,7 +6246,7 @@
         <v>2.67</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>55</v>
       </c>
@@ -6128,7 +6260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>9</v>
       </c>
@@ -6142,7 +6274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>88</v>
       </c>
@@ -6156,7 +6288,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>55</v>
       </c>
@@ -6170,7 +6302,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>5</v>
       </c>
@@ -6181,7 +6313,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>8</v>
       </c>
@@ -6195,7 +6327,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>6</v>
       </c>
@@ -6209,7 +6341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>19</v>
       </c>
@@ -6220,7 +6352,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>23</v>
       </c>
@@ -6234,7 +6366,7 @@
         <v>2.5099999999999998</v>
       </c>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>55</v>
       </c>
@@ -6248,7 +6380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>9</v>
       </c>
@@ -6262,7 +6394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>88</v>
       </c>
@@ -6276,7 +6408,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>55</v>
       </c>
@@ -6290,7 +6422,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>5</v>
       </c>
@@ -6301,7 +6433,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>8</v>
       </c>
@@ -6315,7 +6447,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>6</v>
       </c>
@@ -6329,7 +6461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>19</v>
       </c>
@@ -6340,7 +6472,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>23</v>
       </c>
@@ -6354,7 +6486,7 @@
         <v>2.5099999999999998</v>
       </c>
     </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>55</v>
       </c>
@@ -6368,7 +6500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>9</v>
       </c>
@@ -6382,7 +6514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>88</v>
       </c>
@@ -6396,7 +6528,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>55</v>
       </c>
@@ -6410,7 +6542,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>5</v>
       </c>
@@ -6421,7 +6553,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>8</v>
       </c>
@@ -6435,7 +6567,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>6</v>
       </c>
@@ -6449,7 +6581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>19</v>
       </c>
@@ -6460,7 +6592,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>23</v>
       </c>
@@ -6474,7 +6606,7 @@
         <v>2.56</v>
       </c>
     </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>55</v>
       </c>
@@ -6488,7 +6620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>9</v>
       </c>
@@ -6502,7 +6634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>88</v>
       </c>
@@ -6516,7 +6648,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>55</v>
       </c>
@@ -6530,7 +6662,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>5</v>
       </c>
@@ -6541,7 +6673,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>8</v>
       </c>
@@ -6555,7 +6687,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>6</v>
       </c>
@@ -6569,7 +6701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>19</v>
       </c>
@@ -6580,7 +6712,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>23</v>
       </c>
@@ -6594,7 +6726,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>55</v>
       </c>
@@ -6608,7 +6740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>9</v>
       </c>
@@ -6622,7 +6754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>88</v>
       </c>
@@ -6636,7 +6768,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>55</v>
       </c>
@@ -6650,7 +6782,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>5</v>
       </c>
@@ -6661,7 +6793,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>8</v>
       </c>
@@ -6675,7 +6807,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>6</v>
       </c>
@@ -6689,7 +6821,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>19</v>
       </c>
@@ -6700,7 +6832,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>23</v>
       </c>
@@ -6714,7 +6846,7 @@
         <v>2.4900000000000002</v>
       </c>
     </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>55</v>
       </c>
@@ -6728,7 +6860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>9</v>
       </c>
@@ -6742,7 +6874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>88</v>
       </c>
@@ -6756,7 +6888,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>55</v>
       </c>
@@ -6770,7 +6902,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>5</v>
       </c>
@@ -6781,7 +6913,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>8</v>
       </c>
@@ -6795,7 +6927,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>6</v>
       </c>
@@ -6809,7 +6941,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>19</v>
       </c>
@@ -6820,7 +6952,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>23</v>
       </c>
@@ -6834,7 +6966,7 @@
         <v>2.4900000000000002</v>
       </c>
     </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>55</v>
       </c>
@@ -6848,7 +6980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>9</v>
       </c>
@@ -6862,7 +6994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>88</v>
       </c>
@@ -6876,7 +7008,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>55</v>
       </c>
@@ -6890,7 +7022,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>5</v>
       </c>
@@ -6901,7 +7033,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>8</v>
       </c>
@@ -6915,7 +7047,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>6</v>
       </c>
@@ -6929,7 +7061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>19</v>
       </c>
@@ -6940,7 +7072,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>23</v>
       </c>
@@ -6954,7 +7086,7 @@
         <v>2.4900000000000002</v>
       </c>
     </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>55</v>
       </c>
@@ -6968,7 +7100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>9</v>
       </c>
@@ -6982,7 +7114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>88</v>
       </c>
@@ -6996,7 +7128,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>55</v>
       </c>
@@ -7010,7 +7142,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>5</v>
       </c>
@@ -7021,7 +7153,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>8</v>
       </c>
@@ -7035,7 +7167,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>6</v>
       </c>
@@ -7049,7 +7181,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>19</v>
       </c>
@@ -7060,7 +7192,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>23</v>
       </c>
@@ -7074,7 +7206,7 @@
         <v>2.48</v>
       </c>
     </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>55</v>
       </c>
@@ -7088,7 +7220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>9</v>
       </c>
@@ -7102,7 +7234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>88</v>
       </c>
@@ -7116,7 +7248,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>55</v>
       </c>
@@ -7130,7 +7262,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>5</v>
       </c>
@@ -7141,7 +7273,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>8</v>
       </c>
@@ -7155,7 +7287,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>6</v>
       </c>
@@ -7169,7 +7301,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>19</v>
       </c>
@@ -7180,7 +7312,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>23</v>
       </c>
@@ -7194,7 +7326,7 @@
         <v>2.39</v>
       </c>
     </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>55</v>
       </c>
@@ -7208,7 +7340,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>9</v>
       </c>
@@ -7222,7 +7354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>88</v>
       </c>
@@ -7236,7 +7368,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>55</v>
       </c>
@@ -7250,7 +7382,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>5</v>
       </c>
@@ -7261,7 +7393,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>8</v>
       </c>
@@ -7275,7 +7407,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>6</v>
       </c>
@@ -7289,7 +7421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>19</v>
       </c>
@@ -7300,7 +7432,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>23</v>
       </c>
@@ -7314,7 +7446,7 @@
         <v>2.4700000000000002</v>
       </c>
     </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>55</v>
       </c>
@@ -7328,7 +7460,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>9</v>
       </c>
@@ -7342,7 +7474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>88</v>
       </c>
@@ -7356,7 +7488,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>55</v>
       </c>
@@ -7370,7 +7502,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>5</v>
       </c>
@@ -7381,7 +7513,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>8</v>
       </c>
@@ -7395,7 +7527,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>6</v>
       </c>
@@ -7409,7 +7541,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>19</v>
       </c>
@@ -7420,7 +7552,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>23</v>
       </c>
@@ -7434,7 +7566,7 @@
         <v>2.27</v>
       </c>
     </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>55</v>
       </c>
@@ -7448,7 +7580,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>9</v>
       </c>
@@ -7462,7 +7594,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>88</v>
       </c>
@@ -7476,7 +7608,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>55</v>
       </c>
@@ -7490,7 +7622,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>5</v>
       </c>
@@ -7501,7 +7633,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>8</v>
       </c>
@@ -7515,7 +7647,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>6</v>
       </c>
@@ -7529,7 +7661,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>19</v>
       </c>
@@ -7540,7 +7672,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>23</v>
       </c>
@@ -7554,7 +7686,7 @@
         <v>1.97</v>
       </c>
     </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>55</v>
       </c>
@@ -7568,7 +7700,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>9</v>
       </c>
@@ -7582,7 +7714,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>88</v>
       </c>
@@ -7596,7 +7728,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>55</v>
       </c>
@@ -7610,7 +7742,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>5</v>
       </c>
@@ -7621,7 +7753,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>8</v>
       </c>
@@ -7635,7 +7767,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>6</v>
       </c>
@@ -7649,7 +7781,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="375" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>19</v>
       </c>
@@ -7660,7 +7792,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="376" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>23</v>
       </c>
@@ -7674,7 +7806,7 @@
         <v>1.93</v>
       </c>
     </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>55</v>
       </c>
@@ -7688,7 +7820,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="378" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>9</v>
       </c>
@@ -7702,7 +7834,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>88</v>
       </c>
@@ -7716,7 +7848,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>55</v>
       </c>
@@ -7730,7 +7862,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="381" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>5</v>
       </c>
@@ -7741,7 +7873,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="382" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>8</v>
       </c>
@@ -7755,7 +7887,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="383" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>6</v>
       </c>
@@ -7769,7 +7901,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="384" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>19</v>
       </c>
@@ -7780,7 +7912,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>23</v>
       </c>
@@ -7794,7 +7926,7 @@
         <v>2.21</v>
       </c>
     </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>55</v>
       </c>
@@ -7808,7 +7940,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>9</v>
       </c>
@@ -7822,7 +7954,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>88</v>
       </c>
@@ -7836,7 +7968,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="389" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>55</v>
       </c>
@@ -7850,7 +7982,7 @@
         <v>0.19</v>
       </c>
     </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>5</v>
       </c>
@@ -7861,7 +7993,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>8</v>
       </c>
@@ -7875,7 +8007,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>6</v>
       </c>
@@ -7889,7 +8021,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>19</v>
       </c>
@@ -7900,7 +8032,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="394" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>23</v>
       </c>
@@ -7914,7 +8046,7 @@
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="395" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>55</v>
       </c>
@@ -7928,7 +8060,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="396" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>9</v>
       </c>
@@ -7942,7 +8074,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="397" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>88</v>
       </c>
@@ -7956,7 +8088,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>55</v>
       </c>
@@ -7970,7 +8102,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="399" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>5</v>
       </c>
@@ -7981,7 +8113,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>8</v>
       </c>
@@ -7995,7 +8127,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="401" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>6</v>
       </c>
@@ -8009,7 +8141,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="402" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>19</v>
       </c>
@@ -8020,7 +8152,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="403" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>23</v>
       </c>
@@ -8034,7 +8166,7 @@
         <v>1.91</v>
       </c>
     </row>
-    <row r="404" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>55</v>
       </c>
@@ -8048,7 +8180,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="405" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>9</v>
       </c>
@@ -8062,7 +8194,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="406" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>88</v>
       </c>
@@ -8076,7 +8208,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="407" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>55</v>
       </c>
@@ -8090,7 +8222,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="408" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>5</v>
       </c>
@@ -8101,7 +8233,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="409" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>8</v>
       </c>
@@ -8115,7 +8247,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="410" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>6</v>
       </c>
@@ -8129,7 +8261,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="411" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>19</v>
       </c>
@@ -8140,7 +8272,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="412" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>23</v>
       </c>
@@ -8154,7 +8286,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>55</v>
       </c>
@@ -8168,7 +8300,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="414" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>9</v>
       </c>
@@ -8182,7 +8314,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="415" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>88</v>
       </c>
@@ -8196,7 +8328,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="416" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>55</v>
       </c>
@@ -8210,7 +8342,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="417" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>5</v>
       </c>
@@ -8221,7 +8353,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="418" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>8</v>
       </c>
@@ -8235,7 +8367,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="419" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>6</v>
       </c>
@@ -8249,7 +8381,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="420" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>19</v>
       </c>
@@ -8260,7 +8392,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="421" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>23</v>
       </c>
@@ -8274,7 +8406,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="422" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>55</v>
       </c>
@@ -8288,7 +8420,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="423" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>9</v>
       </c>
@@ -8302,7 +8434,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="424" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>88</v>
       </c>
@@ -8316,7 +8448,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="425" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>55</v>
       </c>
@@ -8330,7 +8462,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="426" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>5</v>
       </c>
@@ -8341,7 +8473,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="427" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>8</v>
       </c>
@@ -8355,7 +8487,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="428" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>6</v>
       </c>
@@ -8369,7 +8501,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="429" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>19</v>
       </c>
@@ -8380,7 +8512,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="430" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>23</v>
       </c>
@@ -8394,7 +8526,7 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="431" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>55</v>
       </c>
@@ -8408,7 +8540,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="432" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>9</v>
       </c>
@@ -8422,7 +8554,7 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="433" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>88</v>
       </c>
@@ -8436,7 +8568,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="434" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>55</v>
       </c>
@@ -8450,7 +8582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="435" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>5</v>
       </c>
@@ -8464,7 +8596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="436" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>8</v>
       </c>
@@ -8478,7 +8610,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="437" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>6</v>
       </c>
@@ -8492,7 +8624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="438" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>19</v>
       </c>
@@ -8506,7 +8638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="439" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>23</v>
       </c>
@@ -8520,7 +8652,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="440" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>55</v>
       </c>
@@ -8534,7 +8666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="441" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>9</v>
       </c>
@@ -8548,7 +8680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="442" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>88</v>
       </c>
@@ -8562,7 +8694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="443" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>55</v>
       </c>
@@ -8576,7 +8708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="444" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>5</v>
       </c>
@@ -8590,7 +8722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="445" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>8</v>
       </c>
@@ -8604,7 +8736,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="446" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>6</v>
       </c>
@@ -8618,7 +8750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="447" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>19</v>
       </c>
@@ -8632,7 +8764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="448" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>23</v>
       </c>
@@ -8646,7 +8778,7 @@
         <v>5.18</v>
       </c>
     </row>
-    <row r="449" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>55</v>
       </c>
@@ -8660,7 +8792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="450" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>9</v>
       </c>
@@ -8674,7 +8806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="451" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>88</v>
       </c>
@@ -8688,7 +8820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="452" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>55</v>
       </c>
@@ -8702,7 +8834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="453" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>5</v>
       </c>
@@ -8716,7 +8848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="454" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>8</v>
       </c>
@@ -8730,7 +8862,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="455" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>6</v>
       </c>
@@ -8744,7 +8876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="456" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>19</v>
       </c>
@@ -8758,7 +8890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="457" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>23</v>
       </c>
@@ -8772,7 +8904,7 @@
         <v>5.24</v>
       </c>
     </row>
-    <row r="458" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>55</v>
       </c>
@@ -8786,7 +8918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="459" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>9</v>
       </c>
@@ -8800,7 +8932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="460" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>88</v>
       </c>
@@ -8814,7 +8946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="461" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>55</v>
       </c>
@@ -8828,7 +8960,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="462" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>5</v>
       </c>
@@ -8842,7 +8974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="463" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>8</v>
       </c>
@@ -8856,7 +8988,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="464" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>6</v>
       </c>
@@ -8870,7 +9002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="465" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>19</v>
       </c>
@@ -8884,7 +9016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="466" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>23</v>
       </c>
@@ -8898,7 +9030,7 @@
         <v>6.32</v>
       </c>
     </row>
-    <row r="467" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>55</v>
       </c>
@@ -8912,7 +9044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="468" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>9</v>
       </c>
@@ -8926,7 +9058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="469" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>88</v>
       </c>
@@ -8940,7 +9072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="470" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>55</v>
       </c>
@@ -8954,7 +9086,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="471" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>5</v>
       </c>
@@ -8968,7 +9100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="472" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>8</v>
       </c>
@@ -8982,7 +9114,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="473" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>6</v>
       </c>
@@ -8996,7 +9128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="474" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>19</v>
       </c>
@@ -9010,7 +9142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="475" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>23</v>
       </c>
@@ -9024,7 +9156,7 @@
         <v>6.42</v>
       </c>
     </row>
-    <row r="476" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>55</v>
       </c>
@@ -9038,7 +9170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="477" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>9</v>
       </c>
@@ -9052,7 +9184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="478" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>88</v>
       </c>
@@ -9066,7 +9198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="479" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>55</v>
       </c>
@@ -9080,7 +9212,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="480" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>5</v>
       </c>
@@ -9094,7 +9226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="481" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>8</v>
       </c>
@@ -9108,7 +9240,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="482" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>6</v>
       </c>
@@ -9122,7 +9254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="483" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>19</v>
       </c>
@@ -9136,7 +9268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="484" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>23</v>
       </c>
@@ -9150,7 +9282,7 @@
         <v>6.28</v>
       </c>
     </row>
-    <row r="485" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>55</v>
       </c>
@@ -9164,7 +9296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="486" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>9</v>
       </c>
@@ -9178,7 +9310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="487" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>88</v>
       </c>
@@ -9192,7 +9324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="488" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>55</v>
       </c>
@@ -9206,7 +9338,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="489" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>5</v>
       </c>
@@ -9220,7 +9352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="490" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>8</v>
       </c>
@@ -9234,7 +9366,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="491" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>6</v>
       </c>
@@ -9248,7 +9380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="492" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>19</v>
       </c>
@@ -9262,7 +9394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="493" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>23</v>
       </c>
@@ -9276,7 +9408,7 @@
         <v>5.96</v>
       </c>
     </row>
-    <row r="494" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>55</v>
       </c>
@@ -9290,7 +9422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="495" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>9</v>
       </c>
@@ -9304,7 +9436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="496" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>88</v>
       </c>
@@ -9318,7 +9450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="497" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>55</v>
       </c>
@@ -9332,7 +9464,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="498" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>5</v>
       </c>
@@ -9346,7 +9478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="499" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>8</v>
       </c>
@@ -9360,7 +9492,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="500" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>6</v>
       </c>
@@ -9374,7 +9506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="501" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>19</v>
       </c>
@@ -9388,7 +9520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="502" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>23</v>
       </c>
@@ -9402,7 +9534,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="503" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>55</v>
       </c>
@@ -9416,7 +9548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="504" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>9</v>
       </c>
@@ -9430,7 +9562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="505" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>88</v>
       </c>
@@ -9444,7 +9576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="506" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>55</v>
       </c>
@@ -9458,7 +9590,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="507" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>5</v>
       </c>
@@ -9472,7 +9604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="508" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>8</v>
       </c>
@@ -9486,7 +9618,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="509" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>6</v>
       </c>
@@ -9500,7 +9632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="510" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>19</v>
       </c>
@@ -9514,7 +9646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="511" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>23</v>
       </c>
@@ -9528,7 +9660,7 @@
         <v>6.55</v>
       </c>
     </row>
-    <row r="512" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>55</v>
       </c>
@@ -9542,7 +9674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="513" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>9</v>
       </c>
@@ -9556,7 +9688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="514" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>88</v>
       </c>
@@ -9570,7 +9702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="515" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>55</v>
       </c>
@@ -9584,7 +9716,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="516" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>5</v>
       </c>
@@ -9598,7 +9730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="517" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>8</v>
       </c>
@@ -9612,7 +9744,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="518" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>6</v>
       </c>
@@ -9626,7 +9758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="519" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>19</v>
       </c>
@@ -9640,7 +9772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="520" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>23</v>
       </c>
@@ -9654,7 +9786,7 @@
         <v>5.35</v>
       </c>
     </row>
-    <row r="521" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>55</v>
       </c>
@@ -9668,7 +9800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="522" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>9</v>
       </c>
@@ -9682,7 +9814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="523" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>88</v>
       </c>
@@ -9696,7 +9828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="524" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>55</v>
       </c>
@@ -9710,7 +9842,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="525" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>5</v>
       </c>
@@ -9724,7 +9856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="526" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>8</v>
       </c>
@@ -9738,7 +9870,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="527" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>6</v>
       </c>
@@ -9752,7 +9884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="528" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>19</v>
       </c>
@@ -9766,7 +9898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="529" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>23</v>
       </c>
@@ -9780,7 +9912,7 @@
         <v>7.65</v>
       </c>
     </row>
-    <row r="530" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>55</v>
       </c>
@@ -9794,7 +9926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="531" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>9</v>
       </c>
@@ -9808,7 +9940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="532" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>88</v>
       </c>
@@ -9822,7 +9954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="533" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>55</v>
       </c>
@@ -9836,7 +9968,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="534" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>5</v>
       </c>
@@ -9850,7 +9982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="535" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>8</v>
       </c>
@@ -9864,7 +9996,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="536" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>6</v>
       </c>
@@ -9878,7 +10010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="537" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>19</v>
       </c>
@@ -9892,7 +10024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="538" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>23</v>
       </c>
@@ -9906,7 +10038,7 @@
         <v>7.54</v>
       </c>
     </row>
-    <row r="539" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>55</v>
       </c>
@@ -9920,7 +10052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="540" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>9</v>
       </c>
@@ -9934,7 +10066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="541" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>88</v>
       </c>
@@ -9948,7 +10080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="542" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>55</v>
       </c>
@@ -9962,7 +10094,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="543" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>5</v>
       </c>
@@ -9976,7 +10108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="544" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>8</v>
       </c>
@@ -9990,7 +10122,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="545" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>6</v>
       </c>
@@ -10004,7 +10136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="546" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>19</v>
       </c>
@@ -10018,7 +10150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="547" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>23</v>
       </c>
@@ -10032,7 +10164,7 @@
         <v>6.82</v>
       </c>
     </row>
-    <row r="548" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>55</v>
       </c>
@@ -10046,7 +10178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="549" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>9</v>
       </c>
@@ -10060,7 +10192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="550" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>88</v>
       </c>
@@ -10074,7 +10206,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="551" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>55</v>
       </c>
@@ -10088,7 +10220,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="552" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>5</v>
       </c>
@@ -10102,7 +10234,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="553" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>8</v>
       </c>
@@ -10116,7 +10248,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="554" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>6</v>
       </c>
@@ -10130,7 +10262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="555" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>19</v>
       </c>
@@ -10144,7 +10276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="556" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>23</v>
       </c>
@@ -10158,7 +10290,7 @@
         <v>7.86</v>
       </c>
     </row>
-    <row r="557" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>55</v>
       </c>
@@ -10172,7 +10304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="558" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>9</v>
       </c>
@@ -10186,7 +10318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="559" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>88</v>
       </c>
@@ -10200,7 +10332,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="560" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>55</v>
       </c>
@@ -10214,7 +10346,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="561" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>5</v>
       </c>
@@ -10228,7 +10360,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="562" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>8</v>
       </c>
@@ -10242,7 +10374,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="563" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>6</v>
       </c>
@@ -10256,7 +10388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="564" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>19</v>
       </c>
@@ -10270,7 +10402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="565" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>23</v>
       </c>
@@ -10284,7 +10416,7 @@
         <v>7.22</v>
       </c>
     </row>
-    <row r="566" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>55</v>
       </c>
@@ -10298,7 +10430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="567" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>9</v>
       </c>
@@ -10312,7 +10444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="568" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>88</v>
       </c>
@@ -10326,7 +10458,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="569" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>55</v>
       </c>
@@ -10340,7 +10472,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="570" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>5</v>
       </c>
@@ -10354,7 +10486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="571" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>8</v>
       </c>
@@ -10368,7 +10500,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="572" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>6</v>
       </c>
@@ -10382,7 +10514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="573" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>19</v>
       </c>
@@ -10396,7 +10528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="574" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>23</v>
       </c>
@@ -10410,7 +10542,7 @@
         <v>5.61</v>
       </c>
     </row>
-    <row r="575" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>55</v>
       </c>
@@ -10424,7 +10556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="576" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>9</v>
       </c>
@@ -10438,7 +10570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="577" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>88</v>
       </c>
@@ -10452,7 +10584,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="578" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>55</v>
       </c>
@@ -10466,7 +10598,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="579" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
         <v>5</v>
       </c>
@@ -10480,7 +10612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="580" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
         <v>8</v>
       </c>
@@ -10494,7 +10626,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="581" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
         <v>6</v>
       </c>
@@ -10508,7 +10640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="582" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>19</v>
       </c>
@@ -10522,7 +10654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="583" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
         <v>23</v>
       </c>
@@ -10536,7 +10668,7 @@
         <v>6.92</v>
       </c>
     </row>
-    <row r="584" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>55</v>
       </c>
@@ -10550,7 +10682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="585" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>9</v>
       </c>
@@ -10564,7 +10696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="586" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>88</v>
       </c>
@@ -10578,7 +10710,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="587" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>55</v>
       </c>
@@ -10592,7 +10724,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="588" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>5</v>
       </c>
@@ -10606,7 +10738,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="589" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>8</v>
       </c>
@@ -10620,7 +10752,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="590" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>6</v>
       </c>
@@ -10634,7 +10766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="591" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>19</v>
       </c>
@@ -10648,7 +10780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="592" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>23</v>
       </c>
@@ -10662,7 +10794,7 @@
         <v>7.38</v>
       </c>
     </row>
-    <row r="593" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
         <v>55</v>
       </c>
@@ -10676,7 +10808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="594" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>9</v>
       </c>
@@ -10690,7 +10822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="595" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
         <v>88</v>
       </c>
@@ -10704,7 +10836,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="596" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>55</v>
       </c>
@@ -10718,7 +10850,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="597" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>5</v>
       </c>
@@ -10732,7 +10864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="598" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>8</v>
       </c>
@@ -10746,7 +10878,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="599" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
         <v>6</v>
       </c>
@@ -10760,7 +10892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="600" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
         <v>19</v>
       </c>
@@ -10774,7 +10906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="601" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
         <v>23</v>
       </c>
@@ -10788,7 +10920,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="602" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
         <v>55</v>
       </c>
@@ -10802,7 +10934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="603" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>9</v>
       </c>
@@ -10816,7 +10948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="604" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
         <v>88</v>
       </c>
@@ -10830,7 +10962,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="605" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>55</v>
       </c>
@@ -10844,7 +10976,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="606" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>5</v>
       </c>
@@ -10858,7 +10990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="607" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
         <v>8</v>
       </c>
@@ -10872,7 +11004,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="608" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
         <v>6</v>
       </c>
@@ -10886,7 +11018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="609" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
         <v>19</v>
       </c>
@@ -10900,7 +11032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="610" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
         <v>23</v>
       </c>
@@ -10914,7 +11046,7 @@
         <v>3.57</v>
       </c>
     </row>
-    <row r="611" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
         <v>55</v>
       </c>
@@ -10928,7 +11060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="612" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
         <v>9</v>
       </c>
@@ -10942,7 +11074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="613" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
         <v>88</v>
       </c>
@@ -10956,7 +11088,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="614" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
         <v>55</v>
       </c>
@@ -10970,7 +11102,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="615" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
         <v>5</v>
       </c>
@@ -10984,7 +11116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="616" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
         <v>8</v>
       </c>
@@ -10998,7 +11130,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="617" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
         <v>6</v>
       </c>
@@ -11012,7 +11144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="618" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>19</v>
       </c>
@@ -11026,7 +11158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="619" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>23</v>
       </c>
@@ -11040,7 +11172,7 @@
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="620" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>55</v>
       </c>
@@ -11054,7 +11186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="621" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
         <v>9</v>
       </c>
@@ -11068,7 +11200,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="622" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
         <v>88</v>
       </c>
@@ -11082,7 +11214,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="623" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="623" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>55</v>
       </c>
@@ -11096,7 +11228,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="624" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="624" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
         <v>5</v>
       </c>
@@ -11110,7 +11242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="625" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="625" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
         <v>8</v>
       </c>
@@ -11124,7 +11256,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="626" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
         <v>6</v>
       </c>
@@ -11138,7 +11270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="627" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>19</v>
       </c>
@@ -11152,7 +11284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="628" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
         <v>23</v>
       </c>
@@ -11166,7 +11298,7 @@
         <v>2.82</v>
       </c>
     </row>
-    <row r="629" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
         <v>55</v>
       </c>
@@ -11180,7 +11312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="630" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
         <v>9</v>
       </c>
@@ -11194,7 +11326,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="631" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
         <v>88</v>
       </c>
@@ -11208,7 +11340,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="632" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
         <v>55</v>
       </c>
@@ -11222,7 +11354,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="633" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
         <v>5</v>
       </c>
@@ -11236,7 +11368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="634" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="634" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
         <v>8</v>
       </c>
@@ -11250,7 +11382,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="635" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
         <v>6</v>
       </c>
@@ -11264,7 +11396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="636" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
         <v>19</v>
       </c>
@@ -11278,7 +11410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="637" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
         <v>23</v>
       </c>
@@ -11292,7 +11424,7 @@
         <v>3.96</v>
       </c>
     </row>
-    <row r="638" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
         <v>55</v>
       </c>
@@ -11306,7 +11438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="639" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
         <v>9</v>
       </c>
@@ -11320,7 +11452,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="640" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
         <v>88</v>
       </c>
@@ -11334,7 +11466,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="641" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>55</v>
       </c>
@@ -11348,7 +11480,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="642" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
         <v>5</v>
       </c>
@@ -11362,7 +11494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="643" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>8</v>
       </c>
@@ -11376,7 +11508,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="644" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>6</v>
       </c>
@@ -11390,7 +11522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="645" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>19</v>
       </c>
@@ -11404,7 +11536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="646" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="646" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>23</v>
       </c>
@@ -11418,7 +11550,7 @@
         <v>2.34</v>
       </c>
     </row>
-    <row r="647" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="647" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>55</v>
       </c>
@@ -11432,7 +11564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="648" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="648" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
         <v>9</v>
       </c>
@@ -11446,7 +11578,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="649" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="649" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>88</v>
       </c>
@@ -11460,7 +11592,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="650" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>62</v>
       </c>
@@ -11474,7 +11606,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="651" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>63</v>
       </c>
@@ -11488,7 +11620,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="652" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
         <v>62</v>
       </c>
@@ -11502,7 +11634,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="653" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>63</v>
       </c>
@@ -11516,7 +11648,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="654" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>62</v>
       </c>
@@ -11530,7 +11662,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="655" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>63</v>
       </c>
@@ -11544,7 +11676,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="656" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>62</v>
       </c>
@@ -11558,7 +11690,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="657" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
         <v>63</v>
       </c>
@@ -11572,7 +11704,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="658" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
         <v>62</v>
       </c>
@@ -11586,7 +11718,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="659" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
         <v>63</v>
       </c>
@@ -11600,7 +11732,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="660" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="660" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
         <v>62</v>
       </c>
@@ -11614,7 +11746,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="661" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="661" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
         <v>63</v>
       </c>
@@ -11628,7 +11760,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="662" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="662" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
         <v>62</v>
       </c>
@@ -11642,7 +11774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="663" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="663" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
         <v>63</v>
       </c>
@@ -11656,7 +11788,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="664" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
         <v>62</v>
       </c>
@@ -11670,7 +11802,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="665" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
         <v>63</v>
       </c>
@@ -11684,7 +11816,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="666" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="666" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>62</v>
       </c>
@@ -11698,7 +11830,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="667" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
         <v>63</v>
       </c>
@@ -11712,7 +11844,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="668" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="668" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
         <v>62</v>
       </c>
@@ -11726,7 +11858,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="669" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="669" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
         <v>63</v>
       </c>
@@ -11740,7 +11872,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="670" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="670" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
         <v>62</v>
       </c>
@@ -11754,7 +11886,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="671" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="671" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
         <v>63</v>
       </c>
@@ -11768,7 +11900,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="672" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="672" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
         <v>62</v>
       </c>
@@ -11782,7 +11914,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="673" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="673" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
         <v>63</v>
       </c>
@@ -11796,7 +11928,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="674" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="674" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>62</v>
       </c>
@@ -11810,7 +11942,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="675" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="675" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>63</v>
       </c>
@@ -11824,7 +11956,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="676" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="676" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
         <v>62</v>
       </c>
@@ -11838,7 +11970,7 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="677" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="677" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>63</v>
       </c>
@@ -11852,7 +11984,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="678" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="678" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
         <v>62</v>
       </c>
@@ -11866,7 +11998,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="679" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="679" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>63</v>
       </c>
@@ -11880,7 +12012,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="680" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="680" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>62</v>
       </c>
@@ -11894,7 +12026,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="681" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="681" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
         <v>63</v>
       </c>
@@ -11908,7 +12040,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="682" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="682" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>62</v>
       </c>
@@ -11922,7 +12054,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="683" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="683" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>63</v>
       </c>
@@ -11936,7 +12068,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="684" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="684" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>62</v>
       </c>
@@ -11950,7 +12082,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="685" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="685" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>63</v>
       </c>
@@ -11964,7 +12096,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="686" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="686" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>62</v>
       </c>
@@ -11978,7 +12110,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="687" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="687" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
         <v>63</v>
       </c>
@@ -11992,7 +12124,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="688" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="688" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>62</v>
       </c>
@@ -12006,7 +12138,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="689" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="689" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>63</v>
       </c>
@@ -12020,7 +12152,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="690" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="690" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>62</v>
       </c>
@@ -12034,7 +12166,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="691" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="691" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>63</v>
       </c>
@@ -12048,7 +12180,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="692" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="692" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>62</v>
       </c>
@@ -12062,7 +12194,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="693" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="693" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>63</v>
       </c>
@@ -12076,7 +12208,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="694" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="694" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>62</v>
       </c>
@@ -12090,7 +12222,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="695" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="695" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>63</v>
       </c>
@@ -12104,7 +12236,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="696" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="696" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>62</v>
       </c>
@@ -12118,7 +12250,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="697" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="697" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>63</v>
       </c>

--- a/VerveStacks_EST/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27DF836C-4FCF-4835-B61A-C53748507AF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{295E83BC-6C17-4947-9432-9178FD4E6147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="re_targets" sheetId="5" r:id="rId1"/>
@@ -49,7 +49,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="186"/>
           </rPr>
           <t>Amit Kanudia:</t>
         </r>
@@ -58,7 +59,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="186"/>
           </rPr>
           <t xml:space="preserve">
 11-09-2025
@@ -75,7 +77,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="186"/>
           </rPr>
           <t>Amit Kanudia:</t>
         </r>
@@ -84,7 +87,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="186"/>
           </rPr>
           <t xml:space="preserve">
 29-07-2025
@@ -101,7 +105,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="186"/>
           </rPr>
           <t>Amit Kanudia:</t>
         </r>
@@ -110,7 +115,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="186"/>
           </rPr>
           <t xml:space="preserve">
 03-08-2025
@@ -124,7 +130,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1685" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1686" uniqueCount="135">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -560,14 +566,16 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
+      <charset val="186"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
+      <charset val="186"/>
     </font>
     <font>
       <b/>
@@ -681,7 +689,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -700,7 +708,8 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Heading 3" xfId="2" builtinId="18"/>
@@ -2107,12 +2116,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:33" x14ac:dyDescent="0.25">
       <c r="L17" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:33" x14ac:dyDescent="0.25">
       <c r="L18" s="7" t="s">
         <v>36</v>
       </c>
@@ -2120,7 +2129,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="20" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>26</v>
       </c>
@@ -2128,7 +2137,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="21" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>27</v>
       </c>
@@ -2175,16 +2184,19 @@
         <v>126</v>
       </c>
       <c r="AD21" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE21" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="AE21" s="16" t="s">
+      <c r="AF21" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="AF21" s="16" t="s">
+      <c r="AG21" s="16" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="22" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>32</v>
       </c>
@@ -2216,17 +2228,23 @@
       <c r="AB22" t="s">
         <v>131</v>
       </c>
-      <c r="AC22" s="15">
+      <c r="AC22" s="17">
+        <v>1</v>
+      </c>
+      <c r="AD22" s="15">
         <v>-0.65</v>
       </c>
-      <c r="AD22">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="s">
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>15</v>
+      </c>
+      <c r="AG22" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="23" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>32</v>
       </c>
@@ -2246,7 +2264,7 @@
       <c r="AE23" s="15"/>
       <c r="AF23" s="15"/>
     </row>
-    <row r="24" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>32</v>
       </c>
@@ -2264,7 +2282,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="25" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>44</v>
       </c>
@@ -2278,7 +2296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>44</v>
       </c>
@@ -2292,7 +2310,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="27" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>49</v>
       </c>
@@ -2307,7 +2325,7 @@
         <v>co2captured</v>
       </c>
     </row>
-    <row r="28" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>65</v>
       </c>
@@ -2318,7 +2336,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="29" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>67</v>
       </c>

--- a/VerveStacks_EST/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{295E83BC-6C17-4947-9432-9178FD4E6147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6328A232-9BF1-47D6-A4D2-2A6223C6EB4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="re_targets" sheetId="5" r:id="rId1"/>
@@ -130,7 +130,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1686" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1666" uniqueCount="118">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -488,57 +488,6 @@
   <si>
     <t>share_of_generation_pct</t>
   </si>
-  <si>
-    <t>Additions by Kristopher</t>
-  </si>
-  <si>
-    <t>PP_RENEW</t>
-  </si>
-  <si>
-    <t>Pset_Set</t>
-  </si>
-  <si>
-    <t>Pset_PN</t>
-  </si>
-  <si>
-    <t>Pset_CI</t>
-  </si>
-  <si>
-    <t>Pset_CO</t>
-  </si>
-  <si>
-    <t>Cset_CN</t>
-  </si>
-  <si>
-    <t>LimType</t>
-  </si>
-  <si>
-    <t>UC_FLO</t>
-  </si>
-  <si>
-    <t>UC_RHSRTS</t>
-  </si>
-  <si>
-    <t>UC_RHSRTS~0</t>
-  </si>
-  <si>
-    <t>UC_Desc</t>
-  </si>
-  <si>
-    <t>ELC</t>
-  </si>
-  <si>
-    <t>LO</t>
-  </si>
-  <si>
-    <t>Minimum renewable power plants penetration</t>
-  </si>
-  <si>
-    <t>UC_min_renew_20235</t>
-  </si>
-  <si>
-    <t>~UC_T: UC_COMPRD</t>
-  </si>
 </sst>
 </file>
 
@@ -547,7 +496,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -615,20 +564,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="186"/>
-    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -689,7 +624,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -706,10 +641,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Heading 3" xfId="2" builtinId="18"/>
@@ -2116,28 +2047,22 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="L17" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
       <c r="L18" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="U18" s="14" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="20" spans="2:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>26</v>
       </c>
-      <c r="AC20" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="21" spans="2:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>27</v>
       </c>
@@ -2156,47 +2081,8 @@
       <c r="G21" t="s">
         <v>3</v>
       </c>
-      <c r="U21" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="V21" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="W21" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="X21" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="Y21" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z21" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="AA21" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="AB21" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="AC21" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="AD21" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE21" s="16" t="s">
-        <v>127</v>
-      </c>
-      <c r="AF21" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="AG21" s="16" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="22" spans="2:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>32</v>
       </c>
@@ -2213,38 +2099,8 @@
       <c r="I22">
         <v>94</v>
       </c>
-      <c r="U22" t="s">
-        <v>133</v>
-      </c>
-      <c r="V22" t="s">
-        <v>119</v>
-      </c>
-      <c r="Z22" t="s">
-        <v>130</v>
-      </c>
-      <c r="AA22">
-        <v>2035</v>
-      </c>
-      <c r="AB22" t="s">
-        <v>131</v>
-      </c>
-      <c r="AC22" s="17">
-        <v>1</v>
-      </c>
-      <c r="AD22" s="15">
-        <v>-0.65</v>
-      </c>
-      <c r="AE22">
-        <v>0</v>
-      </c>
-      <c r="AF22">
-        <v>15</v>
-      </c>
-      <c r="AG22" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="23" spans="2:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>32</v>
       </c>
@@ -2261,10 +2117,8 @@
       <c r="I23">
         <v>55</v>
       </c>
-      <c r="AE23" s="15"/>
-      <c r="AF23" s="15"/>
-    </row>
-    <row r="24" spans="2:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>32</v>
       </c>
@@ -2282,7 +2136,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="25" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>44</v>
       </c>
@@ -2296,7 +2150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>44</v>
       </c>
@@ -2310,7 +2164,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="27" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>49</v>
       </c>
@@ -2325,7 +2179,7 @@
         <v>co2captured</v>
       </c>
     </row>
-    <row r="28" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>65</v>
       </c>
@@ -2336,7 +2190,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="29" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>67</v>
       </c>

--- a/VerveStacks_EST/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_Base_VS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A137AE38-A6B2-4249-B163-6EA6F1A2042D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6328A232-9BF1-47D6-A4D2-2A6223C6EB4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="re_targets" sheetId="5" r:id="rId1"/>
@@ -49,7 +49,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="186"/>
           </rPr>
           <t>Amit Kanudia:</t>
         </r>
@@ -58,7 +59,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="186"/>
           </rPr>
           <t xml:space="preserve">
 11-09-2025
@@ -75,7 +77,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="186"/>
           </rPr>
           <t>Amit Kanudia:</t>
         </r>
@@ -84,7 +87,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="186"/>
           </rPr>
           <t xml:space="preserve">
 29-07-2025
@@ -101,7 +105,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="186"/>
           </rPr>
           <t>Amit Kanudia:</t>
         </r>
@@ -110,7 +115,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="186"/>
           </rPr>
           <t xml:space="preserve">
 03-08-2025
@@ -509,14 +515,16 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
+      <charset val="186"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
+      <charset val="186"/>
     </font>
     <font>
       <b/>
@@ -616,7 +624,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -629,7 +637,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="4"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -972,581 +979,572 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9293F70F-DBAF-4231-9F91-306A64614683}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="B9:L25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B9" s="12" t="s">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
         <v>92</v>
       </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="12"/>
-      <c r="L9" s="12"/>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B10" s="12" t="s">
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
         <v>93</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" t="s">
         <v>94</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" t="s">
         <v>95</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" t="s">
         <v>96</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" t="s">
         <v>97</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G10" t="s">
         <v>98</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="H10" t="s">
         <v>99</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="I10" t="s">
         <v>100</v>
       </c>
-      <c r="J10" s="12" t="s">
+      <c r="J10" t="s">
         <v>101</v>
       </c>
-      <c r="K10" s="12" t="s">
+      <c r="K10" t="s">
         <v>102</v>
       </c>
-      <c r="L10" s="12" t="s">
+      <c r="L10" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="B11" s="12">
+    <row r="11" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="B11">
         <v>2030</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" t="s">
         <v>104</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" t="s">
         <v>105</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11">
         <v>0.36699999999999999</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" t="s">
         <v>106</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="G11" t="s">
         <v>107</v>
       </c>
-      <c r="H11" s="12" t="s">
+      <c r="H11" t="s">
         <v>108</v>
       </c>
-      <c r="I11" s="13">
+      <c r="I11" s="12">
         <v>45155</v>
       </c>
-      <c r="J11" s="12" t="s">
+      <c r="J11" t="s">
         <v>109</v>
       </c>
-      <c r="K11" s="14" t="s">
+      <c r="K11" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="L11" s="14" t="s">
+      <c r="L11" s="13" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="12" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="B12" s="12">
+    <row r="12" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="B12">
         <v>2030</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" t="s">
         <v>112</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" t="s">
         <v>105</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" t="s">
         <v>106</v>
       </c>
-      <c r="G12" s="12" t="s">
+      <c r="G12" t="s">
         <v>107</v>
       </c>
-      <c r="H12" s="12" t="s">
+      <c r="H12" t="s">
         <v>108</v>
       </c>
-      <c r="I12" s="13">
+      <c r="I12" s="12">
         <v>45155</v>
       </c>
-      <c r="J12" s="12" t="s">
+      <c r="J12" t="s">
         <v>109</v>
       </c>
-      <c r="K12" s="14" t="s">
+      <c r="K12" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="L12" s="14" t="s">
+      <c r="L12" s="13" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="B13" s="12">
+    <row r="13" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="B13">
         <v>2030</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" t="s">
         <v>113</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" t="s">
         <v>105</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13">
         <v>1</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" t="s">
         <v>106</v>
       </c>
-      <c r="G13" s="12" t="s">
+      <c r="G13" t="s">
         <v>107</v>
       </c>
-      <c r="H13" s="12" t="s">
+      <c r="H13" t="s">
         <v>108</v>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="12">
         <v>45155</v>
       </c>
-      <c r="J13" s="12" t="s">
+      <c r="J13" t="s">
         <v>109</v>
       </c>
-      <c r="K13" s="14" t="s">
+      <c r="K13" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="L13" s="14" t="s">
+      <c r="L13" s="13" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="B14" s="12">
+    <row r="14" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="B14">
         <v>2030</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" t="s">
         <v>114</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" t="s">
         <v>105</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14">
         <v>1.31</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" t="s">
         <v>106</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="G14" t="s">
         <v>107</v>
       </c>
-      <c r="H14" s="12" t="s">
+      <c r="H14" t="s">
         <v>108</v>
       </c>
-      <c r="I14" s="13">
+      <c r="I14" s="12">
         <v>45155</v>
       </c>
-      <c r="J14" s="12" t="s">
+      <c r="J14" t="s">
         <v>109</v>
       </c>
-      <c r="K14" s="14" t="s">
+      <c r="K14" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="L14" s="14" t="s">
+      <c r="L14" s="13" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="15" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="B15" s="12">
+    <row r="15" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="B15">
         <v>2030</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" t="s">
         <v>115</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" t="s">
         <v>105</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E15">
         <v>1.2</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="F15" t="s">
         <v>106</v>
       </c>
-      <c r="G15" s="12" t="s">
+      <c r="G15" t="s">
         <v>107</v>
       </c>
-      <c r="H15" s="12" t="s">
+      <c r="H15" t="s">
         <v>108</v>
       </c>
-      <c r="I15" s="13">
+      <c r="I15" s="12">
         <v>45155</v>
       </c>
-      <c r="J15" s="12" t="s">
+      <c r="J15" t="s">
         <v>109</v>
       </c>
-      <c r="K15" s="14" t="s">
+      <c r="K15" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="L15" s="14" t="s">
+      <c r="L15" s="13" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="16" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="B16" s="12">
+    <row r="16" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="B16">
         <v>2030</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" t="s">
         <v>104</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" t="s">
         <v>116</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E16">
         <v>1.54</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F16" t="s">
         <v>106</v>
       </c>
-      <c r="G16" s="12" t="s">
+      <c r="G16" t="s">
         <v>107</v>
       </c>
-      <c r="H16" s="12" t="s">
+      <c r="H16" t="s">
         <v>108</v>
       </c>
-      <c r="I16" s="13">
+      <c r="I16" s="12">
         <v>45155</v>
       </c>
-      <c r="J16" s="12" t="s">
+      <c r="J16" t="s">
         <v>109</v>
       </c>
-      <c r="K16" s="14" t="s">
+      <c r="K16" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="L16" s="14" t="s">
+      <c r="L16" s="13" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="17" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="B17" s="12">
+    <row r="17" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="B17">
         <v>2030</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" t="s">
         <v>112</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" t="s">
         <v>116</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E17">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="F17" t="s">
         <v>106</v>
       </c>
-      <c r="G17" s="12" t="s">
+      <c r="G17" t="s">
         <v>107</v>
       </c>
-      <c r="H17" s="12" t="s">
+      <c r="H17" t="s">
         <v>108</v>
       </c>
-      <c r="I17" s="13">
+      <c r="I17" s="12">
         <v>45155</v>
       </c>
-      <c r="J17" s="12" t="s">
+      <c r="J17" t="s">
         <v>109</v>
       </c>
-      <c r="K17" s="14" t="s">
+      <c r="K17" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="L17" s="14" t="s">
+      <c r="L17" s="13" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="18" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="B18" s="12">
+    <row r="18" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="B18">
         <v>2030</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" t="s">
         <v>113</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" t="s">
         <v>116</v>
       </c>
-      <c r="E18" s="12">
+      <c r="E18">
         <v>3.7149999999999999</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="F18" t="s">
         <v>106</v>
       </c>
-      <c r="G18" s="12" t="s">
+      <c r="G18" t="s">
         <v>107</v>
       </c>
-      <c r="H18" s="12" t="s">
+      <c r="H18" t="s">
         <v>108</v>
       </c>
-      <c r="I18" s="13">
+      <c r="I18" s="12">
         <v>45155</v>
       </c>
-      <c r="J18" s="12" t="s">
+      <c r="J18" t="s">
         <v>109</v>
       </c>
-      <c r="K18" s="14" t="s">
+      <c r="K18" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="L18" s="14" t="s">
+      <c r="L18" s="13" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="19" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="B19" s="12">
+    <row r="19" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="B19">
         <v>2030</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" t="s">
         <v>114</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" t="s">
         <v>116</v>
       </c>
-      <c r="E19" s="12">
+      <c r="E19">
         <v>3.1240000000000001</v>
       </c>
-      <c r="F19" s="12" t="s">
+      <c r="F19" t="s">
         <v>106</v>
       </c>
-      <c r="G19" s="12" t="s">
+      <c r="G19" t="s">
         <v>107</v>
       </c>
-      <c r="H19" s="12" t="s">
+      <c r="H19" t="s">
         <v>108</v>
       </c>
-      <c r="I19" s="13">
+      <c r="I19" s="12">
         <v>45155</v>
       </c>
-      <c r="J19" s="12" t="s">
+      <c r="J19" t="s">
         <v>109</v>
       </c>
-      <c r="K19" s="14" t="s">
+      <c r="K19" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="L19" s="14" t="s">
+      <c r="L19" s="13" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="20" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="B20" s="12">
+    <row r="20" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="B20">
         <v>2030</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" t="s">
         <v>115</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" t="s">
         <v>116</v>
       </c>
-      <c r="E20" s="12">
+      <c r="E20">
         <v>1</v>
       </c>
-      <c r="F20" s="12" t="s">
+      <c r="F20" t="s">
         <v>106</v>
       </c>
-      <c r="G20" s="12" t="s">
+      <c r="G20" t="s">
         <v>107</v>
       </c>
-      <c r="H20" s="12" t="s">
+      <c r="H20" t="s">
         <v>108</v>
       </c>
-      <c r="I20" s="13">
+      <c r="I20" s="12">
         <v>45155</v>
       </c>
-      <c r="J20" s="12" t="s">
+      <c r="J20" t="s">
         <v>109</v>
       </c>
-      <c r="K20" s="14" t="s">
+      <c r="K20" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="L20" s="14" t="s">
+      <c r="L20" s="13" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="21" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="B21" s="12">
+    <row r="21" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="B21">
         <v>2030</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" t="s">
         <v>104</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" t="s">
         <v>117</v>
       </c>
-      <c r="E21" s="12">
+      <c r="E21">
         <v>16.376000000000001</v>
       </c>
-      <c r="F21" s="12" t="s">
+      <c r="F21" t="s">
         <v>106</v>
       </c>
-      <c r="G21" s="12" t="s">
+      <c r="G21" t="s">
         <v>107</v>
       </c>
-      <c r="H21" s="12" t="s">
+      <c r="H21" t="s">
         <v>108</v>
       </c>
-      <c r="I21" s="13">
+      <c r="I21" s="12">
         <v>45155</v>
       </c>
-      <c r="J21" s="12" t="s">
+      <c r="J21" t="s">
         <v>109</v>
       </c>
-      <c r="K21" s="14" t="s">
+      <c r="K21" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="L21" s="14" t="s">
+      <c r="L21" s="13" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="22" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="B22" s="12">
+    <row r="22" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="B22">
         <v>2030</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" t="s">
         <v>112</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" t="s">
         <v>117</v>
       </c>
-      <c r="E22" s="12">
+      <c r="E22">
         <v>0.26600000000000001</v>
       </c>
-      <c r="F22" s="12" t="s">
+      <c r="F22" t="s">
         <v>106</v>
       </c>
-      <c r="G22" s="12" t="s">
+      <c r="G22" t="s">
         <v>107</v>
       </c>
-      <c r="H22" s="12" t="s">
+      <c r="H22" t="s">
         <v>108</v>
       </c>
-      <c r="I22" s="13">
+      <c r="I22" s="12">
         <v>45155</v>
       </c>
-      <c r="J22" s="12" t="s">
+      <c r="J22" t="s">
         <v>109</v>
       </c>
-      <c r="K22" s="14" t="s">
+      <c r="K22" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="L22" s="14" t="s">
+      <c r="L22" s="13" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="23" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="B23" s="12">
+    <row r="23" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="B23">
         <v>2030</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" t="s">
         <v>113</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" t="s">
         <v>117</v>
       </c>
-      <c r="E23" s="12">
+      <c r="E23">
         <v>39.503999999999998</v>
       </c>
-      <c r="F23" s="12" t="s">
+      <c r="F23" t="s">
         <v>106</v>
       </c>
-      <c r="G23" s="12" t="s">
+      <c r="G23" t="s">
         <v>107</v>
       </c>
-      <c r="H23" s="12" t="s">
+      <c r="H23" t="s">
         <v>108</v>
       </c>
-      <c r="I23" s="13">
+      <c r="I23" s="12">
         <v>45155</v>
       </c>
-      <c r="J23" s="12" t="s">
+      <c r="J23" t="s">
         <v>109</v>
       </c>
-      <c r="K23" s="14" t="s">
+      <c r="K23" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="L23" s="14" t="s">
+      <c r="L23" s="13" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="24" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="B24" s="12">
+    <row r="24" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="B24">
         <v>2030</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" t="s">
         <v>114</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" t="s">
         <v>117</v>
       </c>
-      <c r="E24" s="12">
+      <c r="E24">
         <v>33.22</v>
       </c>
-      <c r="F24" s="12" t="s">
+      <c r="F24" t="s">
         <v>106</v>
       </c>
-      <c r="G24" s="12" t="s">
+      <c r="G24" t="s">
         <v>107</v>
       </c>
-      <c r="H24" s="12" t="s">
+      <c r="H24" t="s">
         <v>108</v>
       </c>
-      <c r="I24" s="13">
+      <c r="I24" s="12">
         <v>45155</v>
       </c>
-      <c r="J24" s="12" t="s">
+      <c r="J24" t="s">
         <v>109</v>
       </c>
-      <c r="K24" s="14" t="s">
+      <c r="K24" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="L24" s="14" t="s">
+      <c r="L24" s="13" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="25" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="B25" s="12">
+    <row r="25" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="B25">
         <v>2030</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C25" t="s">
         <v>115</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="D25" t="s">
         <v>117</v>
       </c>
-      <c r="E25" s="12">
+      <c r="E25">
         <v>10.634</v>
       </c>
-      <c r="F25" s="12" t="s">
+      <c r="F25" t="s">
         <v>106</v>
       </c>
-      <c r="G25" s="12" t="s">
+      <c r="G25" t="s">
         <v>107</v>
       </c>
-      <c r="H25" s="12" t="s">
+      <c r="H25" t="s">
         <v>108</v>
       </c>
-      <c r="I25" s="13">
+      <c r="I25" s="12">
         <v>45155</v>
       </c>
-      <c r="J25" s="12" t="s">
+      <c r="J25" t="s">
         <v>109</v>
       </c>
-      <c r="K25" s="14" t="s">
+      <c r="K25" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="L25" s="14" t="s">
+      <c r="L25" s="13" t="s">
         <v>111</v>
       </c>
     </row>
@@ -1557,41 +1555,45 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AL40"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="10.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.6328125" customWidth="1"/>
-    <col min="5" max="5" width="9.54296875" customWidth="1"/>
-    <col min="6" max="6" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="10.7265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.6328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.90625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.26953125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.08984375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="4.1796875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.7265625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.1796875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.7265625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="24" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.36328125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="7.08984375" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="4.7265625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="23.7265625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="6.36328125" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="7" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="4.7265625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5703125" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="27" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="12" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="AB1">
         <v>1.1000000000000001</v>
       </c>
@@ -1599,7 +1601,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
       <c r="F2" s="6" t="s">
         <v>50</v>
       </c>
@@ -1616,7 +1618,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>0</v>
       </c>
@@ -1639,7 +1641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>48</v>
       </c>
@@ -1664,7 +1666,7 @@
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>87</v>
       </c>
@@ -1684,7 +1686,7 @@
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>0.28000000000000003</v>
       </c>
@@ -1720,7 +1722,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>83</v>
       </c>
@@ -1787,7 +1789,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>19</v>
       </c>
@@ -1865,7 +1867,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
       <c r="F9" t="s">
         <v>9</v>
       </c>
@@ -1933,7 +1935,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:38" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:38" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F10" t="s">
         <v>88</v>
       </c>
@@ -1950,13 +1952,13 @@
         <v>0.30393385477435431</v>
       </c>
     </row>
-    <row r="11" spans="1:38" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:38" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>26</v>
       </c>
@@ -1964,7 +1966,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>27</v>
       </c>
@@ -2002,7 +2004,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>29</v>
       </c>
@@ -2040,27 +2042,27 @@
         <v>86</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.25">
       <c r="L16" s="7" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="L17" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
       <c r="L18" s="7" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>27</v>
       </c>
@@ -2080,7 +2082,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>32</v>
       </c>
@@ -2098,7 +2100,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>32</v>
       </c>
@@ -2116,7 +2118,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>32</v>
       </c>
@@ -2134,7 +2136,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>44</v>
       </c>
@@ -2148,7 +2150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>44</v>
       </c>
@@ -2162,7 +2164,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>49</v>
       </c>
@@ -2177,7 +2179,7 @@
         <v>co2captured</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>65</v>
       </c>
@@ -2188,7 +2190,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>67</v>
       </c>
@@ -2199,12 +2201,12 @@
         <v>66</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
       <c r="E35" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>13</v>
       </c>
@@ -2221,7 +2223,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>39</v>
       </c>
@@ -2235,7 +2237,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
       <c r="D38" t="s">
         <v>9</v>
       </c>
@@ -2243,7 +2245,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>41</v>
       </c>
@@ -2257,7 +2259,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
       <c r="D40" t="s">
         <v>84</v>
       </c>
@@ -2274,27 +2276,28 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{320A1887-1B0C-44A8-9658-90FD86FEE0A5}">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="A9:J23"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.26953125" customWidth="1"/>
-    <col min="3" max="3" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.28515625" customWidth="1"/>
+    <col min="3" max="3" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>90</v>
       </c>
@@ -2323,7 +2326,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>91</v>
       </c>
@@ -2352,17 +2355,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="9" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:8" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
         <v>48</v>
       </c>
@@ -2388,7 +2391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -2418,7 +2421,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>12</v>
       </c>
@@ -2448,7 +2451,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -2478,7 +2481,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>19</v>
       </c>
@@ -2515,10 +2518,11 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC33DFE9-8C65-4A33-8FAE-96323628CE2A}">
+  <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:D697"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>50</v>
       </c>
@@ -2532,7 +2536,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>55</v>
       </c>
@@ -2546,7 +2550,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -2560,7 +2564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -2574,7 +2578,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -2588,7 +2592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -2602,7 +2606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -2616,7 +2620,7 @@
         <v>7.9</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>55</v>
       </c>
@@ -2630,7 +2634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -2644,7 +2648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>88</v>
       </c>
@@ -2658,7 +2662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -2672,7 +2676,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -2686,7 +2690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -2700,7 +2704,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -2714,7 +2718,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -2728,7 +2732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -2742,7 +2746,7 @@
         <v>7.87</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>55</v>
       </c>
@@ -2756,7 +2760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>9</v>
       </c>
@@ -2770,7 +2774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>88</v>
       </c>
@@ -2784,7 +2788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>55</v>
       </c>
@@ -2798,7 +2802,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>5</v>
       </c>
@@ -2812,7 +2816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -2826,7 +2830,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -2840,7 +2844,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>19</v>
       </c>
@@ -2854,7 +2858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -2868,7 +2872,7 @@
         <v>7.97</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -2882,7 +2886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>9</v>
       </c>
@@ -2896,7 +2900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>88</v>
       </c>
@@ -2910,7 +2914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>55</v>
       </c>
@@ -2924,7 +2928,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>5</v>
       </c>
@@ -2938,7 +2942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>8</v>
       </c>
@@ -2952,7 +2956,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>6</v>
       </c>
@@ -2966,7 +2970,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>19</v>
       </c>
@@ -2980,7 +2984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>23</v>
       </c>
@@ -2994,7 +2998,7 @@
         <v>9.61</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>55</v>
       </c>
@@ -3008,7 +3012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>9</v>
       </c>
@@ -3022,7 +3026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>88</v>
       </c>
@@ -3036,7 +3040,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>55</v>
       </c>
@@ -3050,7 +3054,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>5</v>
       </c>
@@ -3064,7 +3068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>8</v>
       </c>
@@ -3078,7 +3082,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>6</v>
       </c>
@@ -3092,7 +3096,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>19</v>
       </c>
@@ -3106,7 +3110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>23</v>
       </c>
@@ -3120,7 +3124,7 @@
         <v>9.76</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>55</v>
       </c>
@@ -3134,7 +3138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>9</v>
       </c>
@@ -3148,7 +3152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>88</v>
       </c>
@@ -3162,7 +3166,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>55</v>
       </c>
@@ -3176,7 +3180,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>5</v>
       </c>
@@ -3190,7 +3194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>8</v>
       </c>
@@ -3204,7 +3208,7 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>6</v>
       </c>
@@ -3218,7 +3222,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>19</v>
       </c>
@@ -3232,7 +3236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>23</v>
       </c>
@@ -3246,7 +3250,7 @@
         <v>9.5500000000000007</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>55</v>
       </c>
@@ -3260,7 +3264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>9</v>
       </c>
@@ -3274,7 +3278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>88</v>
       </c>
@@ -3288,7 +3292,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>55</v>
       </c>
@@ -3302,7 +3306,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>5</v>
       </c>
@@ -3316,7 +3320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>8</v>
       </c>
@@ -3330,7 +3334,7 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>6</v>
       </c>
@@ -3344,7 +3348,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>19</v>
       </c>
@@ -3358,7 +3362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>23</v>
       </c>
@@ -3372,7 +3376,7 @@
         <v>9.06</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>55</v>
       </c>
@@ -3386,7 +3390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>9</v>
       </c>
@@ -3400,7 +3404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>88</v>
       </c>
@@ -3414,7 +3418,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>55</v>
       </c>
@@ -3428,7 +3432,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>5</v>
       </c>
@@ -3442,7 +3446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>8</v>
       </c>
@@ -3456,7 +3460,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>6</v>
       </c>
@@ -3470,7 +3474,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>19</v>
       </c>
@@ -3484,7 +3488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>23</v>
       </c>
@@ -3498,7 +3502,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>55</v>
       </c>
@@ -3512,7 +3516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>9</v>
       </c>
@@ -3526,7 +3530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>88</v>
       </c>
@@ -3540,7 +3544,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>55</v>
       </c>
@@ -3554,7 +3558,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>5</v>
       </c>
@@ -3568,7 +3572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>8</v>
       </c>
@@ -3582,7 +3586,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>6</v>
       </c>
@@ -3596,7 +3600,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>19</v>
       </c>
@@ -3610,7 +3614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>23</v>
       </c>
@@ -3624,7 +3628,7 @@
         <v>9.9600000000000009</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>55</v>
       </c>
@@ -3638,7 +3642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>9</v>
       </c>
@@ -3652,7 +3656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>88</v>
       </c>
@@ -3666,7 +3670,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>55</v>
       </c>
@@ -3680,7 +3684,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>5</v>
       </c>
@@ -3694,7 +3698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>8</v>
       </c>
@@ -3708,7 +3712,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>6</v>
       </c>
@@ -3722,7 +3726,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>19</v>
       </c>
@@ -3736,7 +3740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>23</v>
       </c>
@@ -3750,7 +3754,7 @@
         <v>8.1300000000000008</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>55</v>
       </c>
@@ -3764,7 +3768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>9</v>
       </c>
@@ -3778,7 +3782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>88</v>
       </c>
@@ -3792,7 +3796,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>55</v>
       </c>
@@ -3806,7 +3810,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>5</v>
       </c>
@@ -3820,7 +3824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>8</v>
       </c>
@@ -3834,7 +3838,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>6</v>
       </c>
@@ -3848,7 +3852,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>19</v>
       </c>
@@ -3862,7 +3866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>23</v>
       </c>
@@ -3876,7 +3880,7 @@
         <v>11.62</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>55</v>
       </c>
@@ -3890,7 +3894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>9</v>
       </c>
@@ -3904,7 +3908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>88</v>
       </c>
@@ -3918,7 +3922,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>55</v>
       </c>
@@ -3932,7 +3936,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>5</v>
       </c>
@@ -3946,7 +3950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>8</v>
       </c>
@@ -3960,7 +3964,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>6</v>
       </c>
@@ -3974,7 +3978,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>19</v>
       </c>
@@ -3988,7 +3992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>23</v>
       </c>
@@ -4002,7 +4006,7 @@
         <v>11.46</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>55</v>
       </c>
@@ -4016,7 +4020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>9</v>
       </c>
@@ -4030,7 +4034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>88</v>
       </c>
@@ -4044,7 +4048,7 @@
         <v>0.37</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>55</v>
       </c>
@@ -4058,7 +4062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>5</v>
       </c>
@@ -4072,7 +4076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>8</v>
       </c>
@@ -4086,7 +4090,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>6</v>
       </c>
@@ -4100,7 +4104,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>19</v>
       </c>
@@ -4114,7 +4118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>23</v>
       </c>
@@ -4128,7 +4132,7 @@
         <v>10.36</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>55</v>
       </c>
@@ -4142,7 +4146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>9</v>
       </c>
@@ -4156,7 +4160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>88</v>
       </c>
@@ -4170,7 +4174,7 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>55</v>
       </c>
@@ -4184,7 +4188,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>5</v>
       </c>
@@ -4198,7 +4202,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>8</v>
       </c>
@@ -4212,7 +4216,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>6</v>
       </c>
@@ -4226,7 +4230,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>19</v>
       </c>
@@ -4240,7 +4244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>23</v>
       </c>
@@ -4254,7 +4258,7 @@
         <v>11.95</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>55</v>
       </c>
@@ -4268,7 +4272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>9</v>
       </c>
@@ -4282,7 +4286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>88</v>
       </c>
@@ -4296,7 +4300,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>55</v>
       </c>
@@ -4310,7 +4314,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>5</v>
       </c>
@@ -4324,7 +4328,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>8</v>
       </c>
@@ -4338,7 +4342,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>6</v>
       </c>
@@ -4352,7 +4356,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>19</v>
       </c>
@@ -4366,7 +4370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>23</v>
       </c>
@@ -4380,7 +4384,7 @@
         <v>10.98</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>55</v>
       </c>
@@ -4394,7 +4398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>9</v>
       </c>
@@ -4408,7 +4412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>88</v>
       </c>
@@ -4422,7 +4426,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>55</v>
       </c>
@@ -4436,7 +4440,7 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>5</v>
       </c>
@@ -4450,7 +4454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>8</v>
       </c>
@@ -4464,7 +4468,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>6</v>
       </c>
@@ -4478,7 +4482,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>19</v>
       </c>
@@ -4492,7 +4496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>23</v>
       </c>
@@ -4506,7 +4510,7 @@
         <v>8.5299999999999994</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>55</v>
       </c>
@@ -4520,7 +4524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>9</v>
       </c>
@@ -4534,7 +4538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>88</v>
       </c>
@@ -4548,7 +4552,7 @@
         <v>0.71</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>55</v>
       </c>
@@ -4562,7 +4566,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>5</v>
       </c>
@@ -4576,7 +4580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>8</v>
       </c>
@@ -4590,7 +4594,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>6</v>
       </c>
@@ -4604,7 +4608,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>19</v>
       </c>
@@ -4618,7 +4622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>23</v>
       </c>
@@ -4632,7 +4636,7 @@
         <v>10.51</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>55</v>
       </c>
@@ -4646,7 +4650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>9</v>
       </c>
@@ -4660,7 +4664,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>88</v>
       </c>
@@ -4674,7 +4678,7 @@
         <v>0.59</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>55</v>
       </c>
@@ -4688,7 +4692,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>5</v>
       </c>
@@ -4702,7 +4706,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>8</v>
       </c>
@@ -4716,7 +4720,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>6</v>
       </c>
@@ -4730,7 +4734,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>19</v>
       </c>
@@ -4744,7 +4748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>23</v>
       </c>
@@ -4758,7 +4762,7 @@
         <v>11.22</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>55</v>
       </c>
@@ -4772,7 +4776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>9</v>
       </c>
@@ -4786,7 +4790,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>88</v>
       </c>
@@ -4800,7 +4804,7 @@
         <v>0.72</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>55</v>
       </c>
@@ -4814,7 +4818,7 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>5</v>
       </c>
@@ -4828,7 +4832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>8</v>
       </c>
@@ -4842,7 +4846,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>6</v>
       </c>
@@ -4856,7 +4860,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>19</v>
       </c>
@@ -4870,7 +4874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>23</v>
       </c>
@@ -4884,7 +4888,7 @@
         <v>10.32</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>55</v>
       </c>
@@ -4898,7 +4902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>9</v>
       </c>
@@ -4912,7 +4916,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>88</v>
       </c>
@@ -4926,7 +4930,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>55</v>
       </c>
@@ -4940,7 +4944,7 @@
         <v>1.36</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>5</v>
       </c>
@@ -4954,7 +4958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>8</v>
       </c>
@@ -4968,7 +4972,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>6</v>
       </c>
@@ -4982,7 +4986,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>19</v>
       </c>
@@ -4996,7 +5000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>23</v>
       </c>
@@ -5010,7 +5014,7 @@
         <v>5.43</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>55</v>
       </c>
@@ -5024,7 +5028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>9</v>
       </c>
@@ -5038,7 +5042,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>88</v>
       </c>
@@ -5052,7 +5056,7 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>55</v>
       </c>
@@ -5066,7 +5070,7 @@
         <v>1.85</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>5</v>
       </c>
@@ -5080,7 +5084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>8</v>
       </c>
@@ -5094,7 +5098,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>6</v>
       </c>
@@ -5108,7 +5112,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>19</v>
       </c>
@@ -5122,7 +5126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>23</v>
       </c>
@@ -5136,7 +5140,7 @@
         <v>3.08</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>55</v>
       </c>
@@ -5150,7 +5154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>9</v>
       </c>
@@ -5164,7 +5168,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>88</v>
       </c>
@@ -5178,7 +5182,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>55</v>
       </c>
@@ -5192,7 +5196,7 @@
         <v>1.77</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>5</v>
       </c>
@@ -5206,7 +5210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>8</v>
       </c>
@@ -5220,7 +5224,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>6</v>
       </c>
@@ -5234,7 +5238,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>19</v>
       </c>
@@ -5248,7 +5252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>23</v>
       </c>
@@ -5262,7 +5266,7 @@
         <v>4.28</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>55</v>
       </c>
@@ -5276,7 +5280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>9</v>
       </c>
@@ -5290,7 +5294,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>88</v>
       </c>
@@ -5304,7 +5308,7 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>55</v>
       </c>
@@ -5318,7 +5322,7 @@
         <v>1.57</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>5</v>
       </c>
@@ -5332,7 +5336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>8</v>
       </c>
@@ -5346,7 +5350,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>6</v>
       </c>
@@ -5360,7 +5364,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>19</v>
       </c>
@@ -5374,7 +5378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>23</v>
       </c>
@@ -5388,7 +5392,7 @@
         <v>6.02</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>55</v>
       </c>
@@ -5402,7 +5406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>9</v>
       </c>
@@ -5416,7 +5420,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>88</v>
       </c>
@@ -5430,7 +5434,7 @@
         <v>0.63</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>55</v>
       </c>
@@ -5444,7 +5448,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>5</v>
       </c>
@@ -5458,7 +5462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>8</v>
       </c>
@@ -5472,7 +5476,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>6</v>
       </c>
@@ -5486,7 +5490,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>19</v>
       </c>
@@ -5500,7 +5504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>23</v>
       </c>
@@ -5514,7 +5518,7 @@
         <v>3.56</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>55</v>
       </c>
@@ -5528,7 +5532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>9</v>
       </c>
@@ -5542,7 +5546,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>88</v>
       </c>
@@ -5556,7 +5560,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>55</v>
       </c>
@@ -5570,7 +5574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>5</v>
       </c>
@@ -5581,7 +5585,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>8</v>
       </c>
@@ -5595,7 +5599,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>6</v>
       </c>
@@ -5609,7 +5613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>19</v>
       </c>
@@ -5620,7 +5624,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>23</v>
       </c>
@@ -5634,7 +5638,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>55</v>
       </c>
@@ -5648,7 +5652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>9</v>
       </c>
@@ -5662,7 +5666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>88</v>
       </c>
@@ -5676,7 +5680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>55</v>
       </c>
@@ -5690,7 +5694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>5</v>
       </c>
@@ -5701,7 +5705,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>8</v>
       </c>
@@ -5715,7 +5719,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>6</v>
       </c>
@@ -5729,7 +5733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>19</v>
       </c>
@@ -5740,7 +5744,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>23</v>
       </c>
@@ -5754,7 +5758,7 @@
         <v>2.44</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>55</v>
       </c>
@@ -5768,7 +5772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>9</v>
       </c>
@@ -5782,7 +5786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>88</v>
       </c>
@@ -5796,7 +5800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>55</v>
       </c>
@@ -5810,7 +5814,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>5</v>
       </c>
@@ -5821,7 +5825,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>8</v>
       </c>
@@ -5835,7 +5839,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>6</v>
       </c>
@@ -5849,7 +5853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>19</v>
       </c>
@@ -5860,7 +5864,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>23</v>
       </c>
@@ -5874,7 +5878,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>55</v>
       </c>
@@ -5888,7 +5892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>9</v>
       </c>
@@ -5902,7 +5906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>88</v>
       </c>
@@ -5916,7 +5920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>55</v>
       </c>
@@ -5930,7 +5934,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>5</v>
       </c>
@@ -5941,7 +5945,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>8</v>
       </c>
@@ -5955,7 +5959,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>6</v>
       </c>
@@ -5969,7 +5973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>19</v>
       </c>
@@ -5980,7 +5984,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>23</v>
       </c>
@@ -5994,7 +5998,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>55</v>
       </c>
@@ -6008,7 +6012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>9</v>
       </c>
@@ -6022,7 +6026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>88</v>
       </c>
@@ -6036,7 +6040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>55</v>
       </c>
@@ -6050,7 +6054,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>5</v>
       </c>
@@ -6061,7 +6065,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>8</v>
       </c>
@@ -6075,7 +6079,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>6</v>
       </c>
@@ -6089,7 +6093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>19</v>
       </c>
@@ -6100,7 +6104,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>23</v>
       </c>
@@ -6114,7 +6118,7 @@
         <v>2.67</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>55</v>
       </c>
@@ -6128,7 +6132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>9</v>
       </c>
@@ -6142,7 +6146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>88</v>
       </c>
@@ -6156,7 +6160,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>55</v>
       </c>
@@ -6170,7 +6174,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>5</v>
       </c>
@@ -6181,7 +6185,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>8</v>
       </c>
@@ -6195,7 +6199,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>6</v>
       </c>
@@ -6209,7 +6213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>19</v>
       </c>
@@ -6220,7 +6224,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>23</v>
       </c>
@@ -6234,7 +6238,7 @@
         <v>2.5099999999999998</v>
       </c>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>55</v>
       </c>
@@ -6248,7 +6252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>9</v>
       </c>
@@ -6262,7 +6266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>88</v>
       </c>
@@ -6276,7 +6280,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>55</v>
       </c>
@@ -6290,7 +6294,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>5</v>
       </c>
@@ -6301,7 +6305,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>8</v>
       </c>
@@ -6315,7 +6319,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>6</v>
       </c>
@@ -6329,7 +6333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>19</v>
       </c>
@@ -6340,7 +6344,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>23</v>
       </c>
@@ -6354,7 +6358,7 @@
         <v>2.5099999999999998</v>
       </c>
     </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>55</v>
       </c>
@@ -6368,7 +6372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>9</v>
       </c>
@@ -6382,7 +6386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>88</v>
       </c>
@@ -6396,7 +6400,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>55</v>
       </c>
@@ -6410,7 +6414,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>5</v>
       </c>
@@ -6421,7 +6425,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>8</v>
       </c>
@@ -6435,7 +6439,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>6</v>
       </c>
@@ -6449,7 +6453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>19</v>
       </c>
@@ -6460,7 +6464,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>23</v>
       </c>
@@ -6474,7 +6478,7 @@
         <v>2.56</v>
       </c>
     </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>55</v>
       </c>
@@ -6488,7 +6492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>9</v>
       </c>
@@ -6502,7 +6506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>88</v>
       </c>
@@ -6516,7 +6520,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>55</v>
       </c>
@@ -6530,7 +6534,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>5</v>
       </c>
@@ -6541,7 +6545,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>8</v>
       </c>
@@ -6555,7 +6559,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>6</v>
       </c>
@@ -6569,7 +6573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>19</v>
       </c>
@@ -6580,7 +6584,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>23</v>
       </c>
@@ -6594,7 +6598,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>55</v>
       </c>
@@ -6608,7 +6612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>9</v>
       </c>
@@ -6622,7 +6626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>88</v>
       </c>
@@ -6636,7 +6640,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>55</v>
       </c>
@@ -6650,7 +6654,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>5</v>
       </c>
@@ -6661,7 +6665,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>8</v>
       </c>
@@ -6675,7 +6679,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>6</v>
       </c>
@@ -6689,7 +6693,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>19</v>
       </c>
@@ -6700,7 +6704,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>23</v>
       </c>
@@ -6714,7 +6718,7 @@
         <v>2.4900000000000002</v>
       </c>
     </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>55</v>
       </c>
@@ -6728,7 +6732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>9</v>
       </c>
@@ -6742,7 +6746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>88</v>
       </c>
@@ -6756,7 +6760,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>55</v>
       </c>
@@ -6770,7 +6774,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>5</v>
       </c>
@@ -6781,7 +6785,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>8</v>
       </c>
@@ -6795,7 +6799,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>6</v>
       </c>
@@ -6809,7 +6813,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>19</v>
       </c>
@@ -6820,7 +6824,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>23</v>
       </c>
@@ -6834,7 +6838,7 @@
         <v>2.4900000000000002</v>
       </c>
     </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>55</v>
       </c>
@@ -6848,7 +6852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>9</v>
       </c>
@@ -6862,7 +6866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>88</v>
       </c>
@@ -6876,7 +6880,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>55</v>
       </c>
@@ -6890,7 +6894,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>5</v>
       </c>
@@ -6901,7 +6905,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>8</v>
       </c>
@@ -6915,7 +6919,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>6</v>
       </c>
@@ -6929,7 +6933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>19</v>
       </c>
@@ -6940,7 +6944,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>23</v>
       </c>
@@ -6954,7 +6958,7 @@
         <v>2.4900000000000002</v>
       </c>
     </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>55</v>
       </c>
@@ -6968,7 +6972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>9</v>
       </c>
@@ -6982,7 +6986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>88</v>
       </c>
@@ -6996,7 +7000,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>55</v>
       </c>
@@ -7010,7 +7014,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>5</v>
       </c>
@@ -7021,7 +7025,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>8</v>
       </c>
@@ -7035,7 +7039,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>6</v>
       </c>
@@ -7049,7 +7053,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>19</v>
       </c>
@@ -7060,7 +7064,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>23</v>
       </c>
@@ -7074,7 +7078,7 @@
         <v>2.48</v>
       </c>
     </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>55</v>
       </c>
@@ -7088,7 +7092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>9</v>
       </c>
@@ -7102,7 +7106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>88</v>
       </c>
@@ -7116,7 +7120,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>55</v>
       </c>
@@ -7130,7 +7134,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>5</v>
       </c>
@@ -7141,7 +7145,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>8</v>
       </c>
@@ -7155,7 +7159,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>6</v>
       </c>
@@ -7169,7 +7173,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>19</v>
       </c>
@@ -7180,7 +7184,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>23</v>
       </c>
@@ -7194,7 +7198,7 @@
         <v>2.39</v>
       </c>
     </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>55</v>
       </c>
@@ -7208,7 +7212,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>9</v>
       </c>
@@ -7222,7 +7226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>88</v>
       </c>
@@ -7236,7 +7240,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>55</v>
       </c>
@@ -7250,7 +7254,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>5</v>
       </c>
@@ -7261,7 +7265,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>8</v>
       </c>
@@ -7275,7 +7279,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>6</v>
       </c>
@@ -7289,7 +7293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>19</v>
       </c>
@@ -7300,7 +7304,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>23</v>
       </c>
@@ -7314,7 +7318,7 @@
         <v>2.4700000000000002</v>
       </c>
     </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>55</v>
       </c>
@@ -7328,7 +7332,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>9</v>
       </c>
@@ -7342,7 +7346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>88</v>
       </c>
@@ -7356,7 +7360,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>55</v>
       </c>
@@ -7370,7 +7374,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>5</v>
       </c>
@@ -7381,7 +7385,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>8</v>
       </c>
@@ -7395,7 +7399,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>6</v>
       </c>
@@ -7409,7 +7413,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>19</v>
       </c>
@@ -7420,7 +7424,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>23</v>
       </c>
@@ -7434,7 +7438,7 @@
         <v>2.27</v>
       </c>
     </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>55</v>
       </c>
@@ -7448,7 +7452,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>9</v>
       </c>
@@ -7462,7 +7466,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>88</v>
       </c>
@@ -7476,7 +7480,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>55</v>
       </c>
@@ -7490,7 +7494,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>5</v>
       </c>
@@ -7501,7 +7505,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>8</v>
       </c>
@@ -7515,7 +7519,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>6</v>
       </c>
@@ -7529,7 +7533,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>19</v>
       </c>
@@ -7540,7 +7544,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>23</v>
       </c>
@@ -7554,7 +7558,7 @@
         <v>1.97</v>
       </c>
     </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>55</v>
       </c>
@@ -7568,7 +7572,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>9</v>
       </c>
@@ -7582,7 +7586,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>88</v>
       </c>
@@ -7596,7 +7600,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>55</v>
       </c>
@@ -7610,7 +7614,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>5</v>
       </c>
@@ -7621,7 +7625,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>8</v>
       </c>
@@ -7635,7 +7639,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>6</v>
       </c>
@@ -7649,7 +7653,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="375" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>19</v>
       </c>
@@ -7660,7 +7664,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="376" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>23</v>
       </c>
@@ -7674,7 +7678,7 @@
         <v>1.93</v>
       </c>
     </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>55</v>
       </c>
@@ -7688,7 +7692,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="378" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>9</v>
       </c>
@@ -7702,7 +7706,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>88</v>
       </c>
@@ -7716,7 +7720,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>55</v>
       </c>
@@ -7730,7 +7734,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="381" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>5</v>
       </c>
@@ -7741,7 +7745,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="382" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>8</v>
       </c>
@@ -7755,7 +7759,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="383" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>6</v>
       </c>
@@ -7769,7 +7773,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="384" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>19</v>
       </c>
@@ -7780,7 +7784,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>23</v>
       </c>
@@ -7794,7 +7798,7 @@
         <v>2.21</v>
       </c>
     </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>55</v>
       </c>
@@ -7808,7 +7812,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>9</v>
       </c>
@@ -7822,7 +7826,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>88</v>
       </c>
@@ -7836,7 +7840,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="389" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>55</v>
       </c>
@@ -7850,7 +7854,7 @@
         <v>0.19</v>
       </c>
     </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>5</v>
       </c>
@@ -7861,7 +7865,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>8</v>
       </c>
@@ -7875,7 +7879,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>6</v>
       </c>
@@ -7889,7 +7893,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>19</v>
       </c>
@@ -7900,7 +7904,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="394" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>23</v>
       </c>
@@ -7914,7 +7918,7 @@
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="395" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>55</v>
       </c>
@@ -7928,7 +7932,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="396" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>9</v>
       </c>
@@ -7942,7 +7946,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="397" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>88</v>
       </c>
@@ -7956,7 +7960,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>55</v>
       </c>
@@ -7970,7 +7974,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="399" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>5</v>
       </c>
@@ -7981,7 +7985,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>8</v>
       </c>
@@ -7995,7 +7999,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="401" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>6</v>
       </c>
@@ -8009,7 +8013,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="402" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>19</v>
       </c>
@@ -8020,7 +8024,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="403" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>23</v>
       </c>
@@ -8034,7 +8038,7 @@
         <v>1.91</v>
       </c>
     </row>
-    <row r="404" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>55</v>
       </c>
@@ -8048,7 +8052,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="405" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>9</v>
       </c>
@@ -8062,7 +8066,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="406" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>88</v>
       </c>
@@ -8076,7 +8080,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="407" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>55</v>
       </c>
@@ -8090,7 +8094,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="408" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>5</v>
       </c>
@@ -8101,7 +8105,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="409" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>8</v>
       </c>
@@ -8115,7 +8119,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="410" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>6</v>
       </c>
@@ -8129,7 +8133,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="411" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>19</v>
       </c>
@@ -8140,7 +8144,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="412" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>23</v>
       </c>
@@ -8154,7 +8158,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>55</v>
       </c>
@@ -8168,7 +8172,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="414" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>9</v>
       </c>
@@ -8182,7 +8186,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="415" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>88</v>
       </c>
@@ -8196,7 +8200,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="416" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>55</v>
       </c>
@@ -8210,7 +8214,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="417" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>5</v>
       </c>
@@ -8221,7 +8225,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="418" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>8</v>
       </c>
@@ -8235,7 +8239,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="419" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>6</v>
       </c>
@@ -8249,7 +8253,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="420" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>19</v>
       </c>
@@ -8260,7 +8264,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="421" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>23</v>
       </c>
@@ -8274,7 +8278,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="422" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>55</v>
       </c>
@@ -8288,7 +8292,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="423" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>9</v>
       </c>
@@ -8302,7 +8306,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="424" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>88</v>
       </c>
@@ -8316,7 +8320,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="425" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>55</v>
       </c>
@@ -8330,7 +8334,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="426" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>5</v>
       </c>
@@ -8341,7 +8345,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="427" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>8</v>
       </c>
@@ -8355,7 +8359,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="428" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>6</v>
       </c>
@@ -8369,7 +8373,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="429" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>19</v>
       </c>
@@ -8380,7 +8384,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="430" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>23</v>
       </c>
@@ -8394,7 +8398,7 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="431" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>55</v>
       </c>
@@ -8408,7 +8412,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="432" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>9</v>
       </c>
@@ -8422,7 +8426,7 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="433" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>88</v>
       </c>
@@ -8436,7 +8440,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="434" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>55</v>
       </c>
@@ -8450,7 +8454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="435" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>5</v>
       </c>
@@ -8464,7 +8468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="436" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>8</v>
       </c>
@@ -8478,7 +8482,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="437" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>6</v>
       </c>
@@ -8492,7 +8496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="438" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>19</v>
       </c>
@@ -8506,7 +8510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="439" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>23</v>
       </c>
@@ -8520,7 +8524,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="440" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>55</v>
       </c>
@@ -8534,7 +8538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="441" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>9</v>
       </c>
@@ -8548,7 +8552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="442" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>88</v>
       </c>
@@ -8562,7 +8566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="443" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>55</v>
       </c>
@@ -8576,7 +8580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="444" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>5</v>
       </c>
@@ -8590,7 +8594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="445" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>8</v>
       </c>
@@ -8604,7 +8608,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="446" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>6</v>
       </c>
@@ -8618,7 +8622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="447" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>19</v>
       </c>
@@ -8632,7 +8636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="448" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>23</v>
       </c>
@@ -8646,7 +8650,7 @@
         <v>5.18</v>
       </c>
     </row>
-    <row r="449" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>55</v>
       </c>
@@ -8660,7 +8664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="450" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>9</v>
       </c>
@@ -8674,7 +8678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="451" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>88</v>
       </c>
@@ -8688,7 +8692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="452" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>55</v>
       </c>
@@ -8702,7 +8706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="453" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>5</v>
       </c>
@@ -8716,7 +8720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="454" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>8</v>
       </c>
@@ -8730,7 +8734,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="455" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>6</v>
       </c>
@@ -8744,7 +8748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="456" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>19</v>
       </c>
@@ -8758,7 +8762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="457" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>23</v>
       </c>
@@ -8772,7 +8776,7 @@
         <v>5.24</v>
       </c>
     </row>
-    <row r="458" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>55</v>
       </c>
@@ -8786,7 +8790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="459" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>9</v>
       </c>
@@ -8800,7 +8804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="460" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>88</v>
       </c>
@@ -8814,7 +8818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="461" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>55</v>
       </c>
@@ -8828,7 +8832,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="462" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>5</v>
       </c>
@@ -8842,7 +8846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="463" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>8</v>
       </c>
@@ -8856,7 +8860,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="464" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>6</v>
       </c>
@@ -8870,7 +8874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="465" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>19</v>
       </c>
@@ -8884,7 +8888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="466" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>23</v>
       </c>
@@ -8898,7 +8902,7 @@
         <v>6.32</v>
       </c>
     </row>
-    <row r="467" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>55</v>
       </c>
@@ -8912,7 +8916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="468" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>9</v>
       </c>
@@ -8926,7 +8930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="469" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>88</v>
       </c>
@@ -8940,7 +8944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="470" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>55</v>
       </c>
@@ -8954,7 +8958,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="471" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>5</v>
       </c>
@@ -8968,7 +8972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="472" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>8</v>
       </c>
@@ -8982,7 +8986,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="473" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>6</v>
       </c>
@@ -8996,7 +9000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="474" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>19</v>
       </c>
@@ -9010,7 +9014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="475" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>23</v>
       </c>
@@ -9024,7 +9028,7 @@
         <v>6.42</v>
       </c>
     </row>
-    <row r="476" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>55</v>
       </c>
@@ -9038,7 +9042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="477" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>9</v>
       </c>
@@ -9052,7 +9056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="478" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>88</v>
       </c>
@@ -9066,7 +9070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="479" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>55</v>
       </c>
@@ -9080,7 +9084,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="480" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>5</v>
       </c>
@@ -9094,7 +9098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="481" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>8</v>
       </c>
@@ -9108,7 +9112,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="482" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>6</v>
       </c>
@@ -9122,7 +9126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="483" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>19</v>
       </c>
@@ -9136,7 +9140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="484" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>23</v>
       </c>
@@ -9150,7 +9154,7 @@
         <v>6.28</v>
       </c>
     </row>
-    <row r="485" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>55</v>
       </c>
@@ -9164,7 +9168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="486" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>9</v>
       </c>
@@ -9178,7 +9182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="487" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>88</v>
       </c>
@@ -9192,7 +9196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="488" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>55</v>
       </c>
@@ -9206,7 +9210,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="489" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>5</v>
       </c>
@@ -9220,7 +9224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="490" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>8</v>
       </c>
@@ -9234,7 +9238,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="491" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>6</v>
       </c>
@@ -9248,7 +9252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="492" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>19</v>
       </c>
@@ -9262,7 +9266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="493" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>23</v>
       </c>
@@ -9276,7 +9280,7 @@
         <v>5.96</v>
       </c>
     </row>
-    <row r="494" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>55</v>
       </c>
@@ -9290,7 +9294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="495" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>9</v>
       </c>
@@ -9304,7 +9308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="496" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>88</v>
       </c>
@@ -9318,7 +9322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="497" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>55</v>
       </c>
@@ -9332,7 +9336,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="498" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>5</v>
       </c>
@@ -9346,7 +9350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="499" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>8</v>
       </c>
@@ -9360,7 +9364,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="500" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>6</v>
       </c>
@@ -9374,7 +9378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="501" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>19</v>
       </c>
@@ -9388,7 +9392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="502" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>23</v>
       </c>
@@ -9402,7 +9406,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="503" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>55</v>
       </c>
@@ -9416,7 +9420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="504" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>9</v>
       </c>
@@ -9430,7 +9434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="505" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>88</v>
       </c>
@@ -9444,7 +9448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="506" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>55</v>
       </c>
@@ -9458,7 +9462,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="507" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>5</v>
       </c>
@@ -9472,7 +9476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="508" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>8</v>
       </c>
@@ -9486,7 +9490,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="509" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>6</v>
       </c>
@@ -9500,7 +9504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="510" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>19</v>
       </c>
@@ -9514,7 +9518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="511" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>23</v>
       </c>
@@ -9528,7 +9532,7 @@
         <v>6.55</v>
       </c>
     </row>
-    <row r="512" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>55</v>
       </c>
@@ -9542,7 +9546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="513" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>9</v>
       </c>
@@ -9556,7 +9560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="514" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>88</v>
       </c>
@@ -9570,7 +9574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="515" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>55</v>
       </c>
@@ -9584,7 +9588,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="516" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>5</v>
       </c>
@@ -9598,7 +9602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="517" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>8</v>
       </c>
@@ -9612,7 +9616,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="518" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>6</v>
       </c>
@@ -9626,7 +9630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="519" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>19</v>
       </c>
@@ -9640,7 +9644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="520" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>23</v>
       </c>
@@ -9654,7 +9658,7 @@
         <v>5.35</v>
       </c>
     </row>
-    <row r="521" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>55</v>
       </c>
@@ -9668,7 +9672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="522" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>9</v>
       </c>
@@ -9682,7 +9686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="523" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>88</v>
       </c>
@@ -9696,7 +9700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="524" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>55</v>
       </c>
@@ -9710,7 +9714,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="525" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>5</v>
       </c>
@@ -9724,7 +9728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="526" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>8</v>
       </c>
@@ -9738,7 +9742,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="527" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>6</v>
       </c>
@@ -9752,7 +9756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="528" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>19</v>
       </c>
@@ -9766,7 +9770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="529" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>23</v>
       </c>
@@ -9780,7 +9784,7 @@
         <v>7.65</v>
       </c>
     </row>
-    <row r="530" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>55</v>
       </c>
@@ -9794,7 +9798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="531" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>9</v>
       </c>
@@ -9808,7 +9812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="532" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>88</v>
       </c>
@@ -9822,7 +9826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="533" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>55</v>
       </c>
@@ -9836,7 +9840,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="534" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>5</v>
       </c>
@@ -9850,7 +9854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="535" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>8</v>
       </c>
@@ -9864,7 +9868,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="536" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>6</v>
       </c>
@@ -9878,7 +9882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="537" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>19</v>
       </c>
@@ -9892,7 +9896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="538" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>23</v>
       </c>
@@ -9906,7 +9910,7 @@
         <v>7.54</v>
       </c>
     </row>
-    <row r="539" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>55</v>
       </c>
@@ -9920,7 +9924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="540" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>9</v>
       </c>
@@ -9934,7 +9938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="541" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>88</v>
       </c>
@@ -9948,7 +9952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="542" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>55</v>
       </c>
@@ -9962,7 +9966,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="543" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>5</v>
       </c>
@@ -9976,7 +9980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="544" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>8</v>
       </c>
@@ -9990,7 +9994,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="545" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>6</v>
       </c>
@@ -10004,7 +10008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="546" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>19</v>
       </c>
@@ -10018,7 +10022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="547" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>23</v>
       </c>
@@ -10032,7 +10036,7 @@
         <v>6.82</v>
       </c>
     </row>
-    <row r="548" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>55</v>
       </c>
@@ -10046,7 +10050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="549" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>9</v>
       </c>
@@ -10060,7 +10064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="550" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>88</v>
       </c>
@@ -10074,7 +10078,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="551" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>55</v>
       </c>
@@ -10088,7 +10092,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="552" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>5</v>
       </c>
@@ -10102,7 +10106,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="553" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>8</v>
       </c>
@@ -10116,7 +10120,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="554" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>6</v>
       </c>
@@ -10130,7 +10134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="555" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>19</v>
       </c>
@@ -10144,7 +10148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="556" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>23</v>
       </c>
@@ -10158,7 +10162,7 @@
         <v>7.86</v>
       </c>
     </row>
-    <row r="557" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>55</v>
       </c>
@@ -10172,7 +10176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="558" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>9</v>
       </c>
@@ -10186,7 +10190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="559" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>88</v>
       </c>
@@ -10200,7 +10204,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="560" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>55</v>
       </c>
@@ -10214,7 +10218,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="561" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>5</v>
       </c>
@@ -10228,7 +10232,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="562" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>8</v>
       </c>
@@ -10242,7 +10246,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="563" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>6</v>
       </c>
@@ -10256,7 +10260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="564" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>19</v>
       </c>
@@ -10270,7 +10274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="565" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>23</v>
       </c>
@@ -10284,7 +10288,7 @@
         <v>7.22</v>
       </c>
     </row>
-    <row r="566" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>55</v>
       </c>
@@ -10298,7 +10302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="567" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>9</v>
       </c>
@@ -10312,7 +10316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="568" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>88</v>
       </c>
@@ -10326,7 +10330,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="569" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>55</v>
       </c>
@@ -10340,7 +10344,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="570" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>5</v>
       </c>
@@ -10354,7 +10358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="571" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>8</v>
       </c>
@@ -10368,7 +10372,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="572" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>6</v>
       </c>
@@ -10382,7 +10386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="573" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>19</v>
       </c>
@@ -10396,7 +10400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="574" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>23</v>
       </c>
@@ -10410,7 +10414,7 @@
         <v>5.61</v>
       </c>
     </row>
-    <row r="575" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>55</v>
       </c>
@@ -10424,7 +10428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="576" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>9</v>
       </c>
@@ -10438,7 +10442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="577" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>88</v>
       </c>
@@ -10452,7 +10456,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="578" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>55</v>
       </c>
@@ -10466,7 +10470,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="579" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
         <v>5</v>
       </c>
@@ -10480,7 +10484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="580" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
         <v>8</v>
       </c>
@@ -10494,7 +10498,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="581" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
         <v>6</v>
       </c>
@@ -10508,7 +10512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="582" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>19</v>
       </c>
@@ -10522,7 +10526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="583" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
         <v>23</v>
       </c>
@@ -10536,7 +10540,7 @@
         <v>6.92</v>
       </c>
     </row>
-    <row r="584" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>55</v>
       </c>
@@ -10550,7 +10554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="585" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>9</v>
       </c>
@@ -10564,7 +10568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="586" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>88</v>
       </c>
@@ -10578,7 +10582,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="587" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>55</v>
       </c>
@@ -10592,7 +10596,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="588" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>5</v>
       </c>
@@ -10606,7 +10610,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="589" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>8</v>
       </c>
@@ -10620,7 +10624,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="590" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>6</v>
       </c>
@@ -10634,7 +10638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="591" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>19</v>
       </c>
@@ -10648,7 +10652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="592" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>23</v>
       </c>
@@ -10662,7 +10666,7 @@
         <v>7.38</v>
       </c>
     </row>
-    <row r="593" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
         <v>55</v>
       </c>
@@ -10676,7 +10680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="594" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>9</v>
       </c>
@@ -10690,7 +10694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="595" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
         <v>88</v>
       </c>
@@ -10704,7 +10708,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="596" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>55</v>
       </c>
@@ -10718,7 +10722,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="597" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>5</v>
       </c>
@@ -10732,7 +10736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="598" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>8</v>
       </c>
@@ -10746,7 +10750,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="599" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
         <v>6</v>
       </c>
@@ -10760,7 +10764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="600" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
         <v>19</v>
       </c>
@@ -10774,7 +10778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="601" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
         <v>23</v>
       </c>
@@ -10788,7 +10792,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="602" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
         <v>55</v>
       </c>
@@ -10802,7 +10806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="603" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>9</v>
       </c>
@@ -10816,7 +10820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="604" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
         <v>88</v>
       </c>
@@ -10830,7 +10834,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="605" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>55</v>
       </c>
@@ -10844,7 +10848,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="606" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>5</v>
       </c>
@@ -10858,7 +10862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="607" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
         <v>8</v>
       </c>
@@ -10872,7 +10876,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="608" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
         <v>6</v>
       </c>
@@ -10886,7 +10890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="609" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
         <v>19</v>
       </c>
@@ -10900,7 +10904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="610" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
         <v>23</v>
       </c>
@@ -10914,7 +10918,7 @@
         <v>3.57</v>
       </c>
     </row>
-    <row r="611" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
         <v>55</v>
       </c>
@@ -10928,7 +10932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="612" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
         <v>9</v>
       </c>
@@ -10942,7 +10946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="613" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
         <v>88</v>
       </c>
@@ -10956,7 +10960,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="614" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
         <v>55</v>
       </c>
@@ -10970,7 +10974,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="615" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
         <v>5</v>
       </c>
@@ -10984,7 +10988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="616" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
         <v>8</v>
       </c>
@@ -10998,7 +11002,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="617" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
         <v>6</v>
       </c>
@@ -11012,7 +11016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="618" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>19</v>
       </c>
@@ -11026,7 +11030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="619" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>23</v>
       </c>
@@ -11040,7 +11044,7 @@
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="620" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>55</v>
       </c>
@@ -11054,7 +11058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="621" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
         <v>9</v>
       </c>
@@ -11068,7 +11072,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="622" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
         <v>88</v>
       </c>
@@ -11082,7 +11086,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="623" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="623" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>55</v>
       </c>
@@ -11096,7 +11100,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="624" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="624" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
         <v>5</v>
       </c>
@@ -11110,7 +11114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="625" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="625" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
         <v>8</v>
       </c>
@@ -11124,7 +11128,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="626" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
         <v>6</v>
       </c>
@@ -11138,7 +11142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="627" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>19</v>
       </c>
@@ -11152,7 +11156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="628" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
         <v>23</v>
       </c>
@@ -11166,7 +11170,7 @@
         <v>2.82</v>
       </c>
     </row>
-    <row r="629" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
         <v>55</v>
       </c>
@@ -11180,7 +11184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="630" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
         <v>9</v>
       </c>
@@ -11194,7 +11198,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="631" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
         <v>88</v>
       </c>
@@ -11208,7 +11212,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="632" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
         <v>55</v>
       </c>
@@ -11222,7 +11226,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="633" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
         <v>5</v>
       </c>
@@ -11236,7 +11240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="634" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="634" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
         <v>8</v>
       </c>
@@ -11250,7 +11254,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="635" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
         <v>6</v>
       </c>
@@ -11264,7 +11268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="636" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
         <v>19</v>
       </c>
@@ -11278,7 +11282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="637" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
         <v>23</v>
       </c>
@@ -11292,7 +11296,7 @@
         <v>3.96</v>
       </c>
     </row>
-    <row r="638" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
         <v>55</v>
       </c>
@@ -11306,7 +11310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="639" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
         <v>9</v>
       </c>
@@ -11320,7 +11324,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="640" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
         <v>88</v>
       </c>
@@ -11334,7 +11338,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="641" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>55</v>
       </c>
@@ -11348,7 +11352,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="642" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
         <v>5</v>
       </c>
@@ -11362,7 +11366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="643" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>8</v>
       </c>
@@ -11376,7 +11380,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="644" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>6</v>
       </c>
@@ -11390,7 +11394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="645" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>19</v>
       </c>
@@ -11404,7 +11408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="646" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="646" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>23</v>
       </c>
@@ -11418,7 +11422,7 @@
         <v>2.34</v>
       </c>
     </row>
-    <row r="647" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="647" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>55</v>
       </c>
@@ -11432,7 +11436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="648" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="648" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
         <v>9</v>
       </c>
@@ -11446,7 +11450,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="649" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="649" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>88</v>
       </c>
@@ -11460,7 +11464,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="650" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>62</v>
       </c>
@@ -11474,7 +11478,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="651" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>63</v>
       </c>
@@ -11488,7 +11492,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="652" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
         <v>62</v>
       </c>
@@ -11502,7 +11506,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="653" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>63</v>
       </c>
@@ -11516,7 +11520,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="654" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>62</v>
       </c>
@@ -11530,7 +11534,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="655" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>63</v>
       </c>
@@ -11544,7 +11548,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="656" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>62</v>
       </c>
@@ -11558,7 +11562,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="657" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
         <v>63</v>
       </c>
@@ -11572,7 +11576,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="658" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
         <v>62</v>
       </c>
@@ -11586,7 +11590,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="659" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
         <v>63</v>
       </c>
@@ -11600,7 +11604,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="660" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="660" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
         <v>62</v>
       </c>
@@ -11614,7 +11618,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="661" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="661" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
         <v>63</v>
       </c>
@@ -11628,7 +11632,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="662" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="662" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
         <v>62</v>
       </c>
@@ -11642,7 +11646,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="663" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="663" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
         <v>63</v>
       </c>
@@ -11656,7 +11660,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="664" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
         <v>62</v>
       </c>
@@ -11670,7 +11674,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="665" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
         <v>63</v>
       </c>
@@ -11684,7 +11688,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="666" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="666" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>62</v>
       </c>
@@ -11698,7 +11702,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="667" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
         <v>63</v>
       </c>
@@ -11712,7 +11716,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="668" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="668" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
         <v>62</v>
       </c>
@@ -11726,7 +11730,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="669" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="669" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
         <v>63</v>
       </c>
@@ -11740,7 +11744,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="670" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="670" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
         <v>62</v>
       </c>
@@ -11754,7 +11758,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="671" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="671" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
         <v>63</v>
       </c>
@@ -11768,7 +11772,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="672" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="672" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
         <v>62</v>
       </c>
@@ -11782,7 +11786,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="673" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="673" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
         <v>63</v>
       </c>
@@ -11796,7 +11800,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="674" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="674" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>62</v>
       </c>
@@ -11810,7 +11814,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="675" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="675" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>63</v>
       </c>
@@ -11824,7 +11828,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="676" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="676" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
         <v>62</v>
       </c>
@@ -11838,7 +11842,7 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="677" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="677" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>63</v>
       </c>
@@ -11852,7 +11856,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="678" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="678" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
         <v>62</v>
       </c>
@@ -11866,7 +11870,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="679" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="679" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>63</v>
       </c>
@@ -11880,7 +11884,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="680" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="680" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>62</v>
       </c>
@@ -11894,7 +11898,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="681" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="681" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
         <v>63</v>
       </c>
@@ -11908,7 +11912,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="682" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="682" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>62</v>
       </c>
@@ -11922,7 +11926,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="683" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="683" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>63</v>
       </c>
@@ -11936,7 +11940,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="684" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="684" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>62</v>
       </c>
@@ -11950,7 +11954,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="685" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="685" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>63</v>
       </c>
@@ -11964,7 +11968,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="686" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="686" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>62</v>
       </c>
@@ -11978,7 +11982,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="687" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="687" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
         <v>63</v>
       </c>
@@ -11992,7 +11996,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="688" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="688" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>62</v>
       </c>
@@ -12006,7 +12010,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="689" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="689" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>63</v>
       </c>
@@ -12020,7 +12024,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="690" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="690" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>62</v>
       </c>
@@ -12034,7 +12038,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="691" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="691" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>63</v>
       </c>
@@ -12048,7 +12052,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="692" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="692" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>62</v>
       </c>
@@ -12062,7 +12066,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="693" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="693" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>63</v>
       </c>
@@ -12076,7 +12080,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="694" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="694" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>62</v>
       </c>
@@ -12090,7 +12094,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="695" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="695" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>63</v>
       </c>
@@ -12104,7 +12108,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="696" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="696" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>62</v>
       </c>
@@ -12118,7 +12122,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="697" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="697" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>63</v>
       </c>

--- a/VerveStacks_EST/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_Base_VS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6328A232-9BF1-47D6-A4D2-2A6223C6EB4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09036EF4-2F32-4328-A7E1-98B1B894457F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-10470" yWindow="10890" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="re_targets" sheetId="5" r:id="rId1"/>
@@ -1579,7 +1579,7 @@
     <col min="24" max="24" width="7.7109375" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="12" bestFit="1" customWidth="1"/>
@@ -2029,14 +2029,13 @@
       </c>
       <c r="AB15">
         <f>AE15*2.5</f>
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AC15">
         <v>3</v>
       </c>
       <c r="AE15" s="11">
-        <f>SUMIFS(historical_data_long!$D$3:$D$626,historical_data_long!$A$3:$A$626,Veda!$V15,historical_data_long!$C$3:$C$626,"GW",historical_data_long!$B$3:$B$626,2022)</f>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AF15" s="10" t="s">
         <v>86</v>

--- a/VerveStacks_EST/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09036EF4-2F32-4328-A7E1-98B1B894457F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0075BAC7-DE6D-4D3B-B3C5-5E44DB93A023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-10470" yWindow="10890" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2029,13 +2029,13 @@
       </c>
       <c r="AB15">
         <f>AE15*2.5</f>
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AC15">
         <v>3</v>
       </c>
       <c r="AE15" s="11">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="AF15" s="10" t="s">
         <v>86</v>

--- a/VerveStacks_EST/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_Base_VS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E6267EF-4852-44DC-85B7-781A4D12FE3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B419FC-9E4F-49CB-9361-F01A3CEC1A9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="re_targets" sheetId="5" r:id="rId1"/>
@@ -483,10 +483,10 @@
     <t>share_of_generation_pct</t>
   </si>
   <si>
-    <t>UC_T: UC_CAP~LO</t>
+    <t>~UC_T: UC_CAP~LO</t>
   </si>
   <si>
-    <t>UC_T: UC_CAP~UP</t>
+    <t>~UC_T: UC_CAP~UP</t>
   </si>
 </sst>
 </file>
@@ -981,14 +981,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9293F70F-DBAF-4231-9F91-306A64614683}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B9:L25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>91</v>
       </c>
@@ -1023,7 +1023,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="B11">
         <v>2030</v>
       </c>
@@ -1058,7 +1058,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="12" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="B12">
         <v>2030</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="B13">
         <v>2030</v>
       </c>
@@ -1128,7 +1128,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="14" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="B14">
         <v>2030</v>
       </c>
@@ -1163,7 +1163,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="15" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="B15">
         <v>2030</v>
       </c>
@@ -1198,7 +1198,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="16" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="B16">
         <v>2030</v>
       </c>
@@ -1233,7 +1233,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="17" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="B17">
         <v>2030</v>
       </c>
@@ -1268,7 +1268,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="18" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="B18">
         <v>2030</v>
       </c>
@@ -1303,7 +1303,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="19" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="B19">
         <v>2030</v>
       </c>
@@ -1338,7 +1338,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="20" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="B20">
         <v>2030</v>
       </c>
@@ -1373,7 +1373,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="21" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="B21">
         <v>2030</v>
       </c>
@@ -1408,7 +1408,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="22" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="B22">
         <v>2030</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="23" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="B23">
         <v>2030</v>
       </c>
@@ -1478,7 +1478,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="24" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="B24">
         <v>2030</v>
       </c>
@@ -1513,7 +1513,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="25" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="409.5" x14ac:dyDescent="0.35">
       <c r="B25">
         <v>2030</v>
       </c>
@@ -1557,44 +1557,44 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AL40"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="37" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7265625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="91" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5703125" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="35.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="4.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.54296875" customWidth="1"/>
+    <col min="6" max="6" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="35.26953125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="4.1796875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.7265625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.1796875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.7265625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="23.54296875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="12" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="28.7265625" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="12" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="10.54296875" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="12" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="11.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.35">
       <c r="AB1">
         <v>1.1000000000000001</v>
       </c>
@@ -1602,7 +1602,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.35">
       <c r="F2" s="6" t="s">
         <v>48</v>
       </c>
@@ -1619,7 +1619,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>0</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>46</v>
       </c>
@@ -1667,7 +1667,7 @@
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>85</v>
       </c>
@@ -1687,7 +1687,7 @@
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>0.28000000000000003</v>
       </c>
@@ -1723,7 +1723,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>81</v>
       </c>
@@ -1790,7 +1790,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>17</v>
       </c>
@@ -1868,7 +1868,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.35">
       <c r="F9" t="s">
         <v>9</v>
       </c>
@@ -1936,7 +1936,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:38" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:38" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F10" t="s">
         <v>86</v>
       </c>
@@ -1953,13 +1953,13 @@
         <v>0.30393385477435431</v>
       </c>
     </row>
-    <row r="11" spans="1:38" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:38" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>24</v>
       </c>
@@ -1967,7 +1967,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>25</v>
       </c>
@@ -2005,7 +2005,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>27</v>
       </c>
@@ -2042,27 +2042,27 @@
         <v>84</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.35">
       <c r="L16" s="7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
       <c r="L17" s="7" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
       <c r="L18" s="7" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>25</v>
       </c>
@@ -2082,7 +2082,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>30</v>
       </c>
@@ -2100,7 +2100,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>30</v>
       </c>
@@ -2118,7 +2118,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>30</v>
       </c>
@@ -2136,7 +2136,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
         <v>42</v>
       </c>
@@ -2150,7 +2150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
         <v>42</v>
       </c>
@@ -2164,7 +2164,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>47</v>
       </c>
@@ -2179,7 +2179,7 @@
         <v>co2captured</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>63</v>
       </c>
@@ -2190,7 +2190,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
         <v>65</v>
       </c>
@@ -2201,12 +2201,12 @@
         <v>64</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.35">
       <c r="E35" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
         <v>11</v>
       </c>
@@ -2223,7 +2223,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
         <v>37</v>
       </c>
@@ -2237,7 +2237,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="D38" t="s">
         <v>9</v>
       </c>
@@ -2245,7 +2245,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
         <v>39</v>
       </c>
@@ -2259,7 +2259,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="D40" t="s">
         <v>82</v>
       </c>
@@ -2278,26 +2278,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{320A1887-1B0C-44A8-9658-90FD86FEE0A5}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A9:J23"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.28515625" customWidth="1"/>
-    <col min="3" max="3" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.26953125" customWidth="1"/>
+    <col min="3" max="3" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.54296875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>88</v>
       </c>
@@ -2326,7 +2326,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>89</v>
       </c>
@@ -2355,17 +2355,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B18" s="9" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="8" t="s">
         <v>46</v>
       </c>
@@ -2391,7 +2391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -2421,7 +2421,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>10</v>
       </c>
@@ -2451,7 +2451,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -2481,7 +2481,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>17</v>
       </c>
@@ -2520,9 +2520,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC33DFE9-8C65-4A33-8FAE-96323628CE2A}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:D697"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>48</v>
       </c>
@@ -2536,7 +2536,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>53</v>
       </c>
@@ -2550,7 +2550,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -2564,7 +2564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -2578,7 +2578,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -2592,7 +2592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -2606,7 +2606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -2620,7 +2620,7 @@
         <v>7.9</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>53</v>
       </c>
@@ -2634,7 +2634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -2648,7 +2648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>86</v>
       </c>
@@ -2662,7 +2662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>53</v>
       </c>
@@ -2676,7 +2676,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -2690,7 +2690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -2704,7 +2704,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -2718,7 +2718,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -2732,7 +2732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -2746,7 +2746,7 @@
         <v>7.87</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>53</v>
       </c>
@@ -2760,7 +2760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>9</v>
       </c>
@@ -2774,7 +2774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>86</v>
       </c>
@@ -2788,7 +2788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>53</v>
       </c>
@@ -2802,7 +2802,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>5</v>
       </c>
@@ -2816,7 +2816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -2830,7 +2830,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -2844,7 +2844,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>17</v>
       </c>
@@ -2858,7 +2858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>21</v>
       </c>
@@ -2872,7 +2872,7 @@
         <v>7.97</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>53</v>
       </c>
@@ -2886,7 +2886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>9</v>
       </c>
@@ -2900,7 +2900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>86</v>
       </c>
@@ -2914,7 +2914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>53</v>
       </c>
@@ -2928,7 +2928,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>5</v>
       </c>
@@ -2942,7 +2942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>8</v>
       </c>
@@ -2956,7 +2956,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>6</v>
       </c>
@@ -2970,7 +2970,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>17</v>
       </c>
@@ -2984,7 +2984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>21</v>
       </c>
@@ -2998,7 +2998,7 @@
         <v>9.61</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>53</v>
       </c>
@@ -3012,7 +3012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>9</v>
       </c>
@@ -3026,7 +3026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>86</v>
       </c>
@@ -3040,7 +3040,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>53</v>
       </c>
@@ -3054,7 +3054,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>5</v>
       </c>
@@ -3068,7 +3068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>8</v>
       </c>
@@ -3082,7 +3082,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>6</v>
       </c>
@@ -3096,7 +3096,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>17</v>
       </c>
@@ -3110,7 +3110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>21</v>
       </c>
@@ -3124,7 +3124,7 @@
         <v>9.76</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>53</v>
       </c>
@@ -3138,7 +3138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>9</v>
       </c>
@@ -3152,7 +3152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>86</v>
       </c>
@@ -3166,7 +3166,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>53</v>
       </c>
@@ -3180,7 +3180,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>5</v>
       </c>
@@ -3194,7 +3194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>8</v>
       </c>
@@ -3208,7 +3208,7 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>6</v>
       </c>
@@ -3222,7 +3222,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>17</v>
       </c>
@@ -3236,7 +3236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>21</v>
       </c>
@@ -3250,7 +3250,7 @@
         <v>9.5500000000000007</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>53</v>
       </c>
@@ -3264,7 +3264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>9</v>
       </c>
@@ -3278,7 +3278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>86</v>
       </c>
@@ -3292,7 +3292,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>53</v>
       </c>
@@ -3306,7 +3306,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>5</v>
       </c>
@@ -3320,7 +3320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>8</v>
       </c>
@@ -3334,7 +3334,7 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>6</v>
       </c>
@@ -3348,7 +3348,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>17</v>
       </c>
@@ -3362,7 +3362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>21</v>
       </c>
@@ -3376,7 +3376,7 @@
         <v>9.06</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>53</v>
       </c>
@@ -3390,7 +3390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>9</v>
       </c>
@@ -3404,7 +3404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>86</v>
       </c>
@@ -3418,7 +3418,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>53</v>
       </c>
@@ -3432,7 +3432,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>5</v>
       </c>
@@ -3446,7 +3446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>8</v>
       </c>
@@ -3460,7 +3460,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>6</v>
       </c>
@@ -3474,7 +3474,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>17</v>
       </c>
@@ -3488,7 +3488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>21</v>
       </c>
@@ -3502,7 +3502,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>53</v>
       </c>
@@ -3516,7 +3516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>9</v>
       </c>
@@ -3530,7 +3530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>86</v>
       </c>
@@ -3544,7 +3544,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>53</v>
       </c>
@@ -3558,7 +3558,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>5</v>
       </c>
@@ -3572,7 +3572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>8</v>
       </c>
@@ -3586,7 +3586,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>6</v>
       </c>
@@ -3600,7 +3600,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>17</v>
       </c>
@@ -3614,7 +3614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>21</v>
       </c>
@@ -3628,7 +3628,7 @@
         <v>9.9600000000000009</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>53</v>
       </c>
@@ -3642,7 +3642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>9</v>
       </c>
@@ -3656,7 +3656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>86</v>
       </c>
@@ -3670,7 +3670,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>53</v>
       </c>
@@ -3684,7 +3684,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>5</v>
       </c>
@@ -3698,7 +3698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>8</v>
       </c>
@@ -3712,7 +3712,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>6</v>
       </c>
@@ -3726,7 +3726,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>17</v>
       </c>
@@ -3740,7 +3740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>21</v>
       </c>
@@ -3754,7 +3754,7 @@
         <v>8.1300000000000008</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>53</v>
       </c>
@@ -3768,7 +3768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>9</v>
       </c>
@@ -3782,7 +3782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>86</v>
       </c>
@@ -3796,7 +3796,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>53</v>
       </c>
@@ -3810,7 +3810,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>5</v>
       </c>
@@ -3824,7 +3824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>8</v>
       </c>
@@ -3838,7 +3838,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>6</v>
       </c>
@@ -3852,7 +3852,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>17</v>
       </c>
@@ -3866,7 +3866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>21</v>
       </c>
@@ -3880,7 +3880,7 @@
         <v>11.62</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>53</v>
       </c>
@@ -3894,7 +3894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>9</v>
       </c>
@@ -3908,7 +3908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>86</v>
       </c>
@@ -3922,7 +3922,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>53</v>
       </c>
@@ -3936,7 +3936,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>5</v>
       </c>
@@ -3950,7 +3950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>8</v>
       </c>
@@ -3964,7 +3964,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>6</v>
       </c>
@@ -3978,7 +3978,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>17</v>
       </c>
@@ -3992,7 +3992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>21</v>
       </c>
@@ -4006,7 +4006,7 @@
         <v>11.46</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>53</v>
       </c>
@@ -4020,7 +4020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>9</v>
       </c>
@@ -4034,7 +4034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>86</v>
       </c>
@@ -4048,7 +4048,7 @@
         <v>0.37</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>53</v>
       </c>
@@ -4062,7 +4062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>5</v>
       </c>
@@ -4076,7 +4076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>8</v>
       </c>
@@ -4090,7 +4090,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>6</v>
       </c>
@@ -4104,7 +4104,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>17</v>
       </c>
@@ -4118,7 +4118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>21</v>
       </c>
@@ -4132,7 +4132,7 @@
         <v>10.36</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>53</v>
       </c>
@@ -4146,7 +4146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>9</v>
       </c>
@@ -4160,7 +4160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>86</v>
       </c>
@@ -4174,7 +4174,7 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>53</v>
       </c>
@@ -4188,7 +4188,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>5</v>
       </c>
@@ -4202,7 +4202,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>8</v>
       </c>
@@ -4216,7 +4216,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>6</v>
       </c>
@@ -4230,7 +4230,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>17</v>
       </c>
@@ -4244,7 +4244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>21</v>
       </c>
@@ -4258,7 +4258,7 @@
         <v>11.95</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>53</v>
       </c>
@@ -4272,7 +4272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>9</v>
       </c>
@@ -4286,7 +4286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>86</v>
       </c>
@@ -4300,7 +4300,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>53</v>
       </c>
@@ -4314,7 +4314,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>5</v>
       </c>
@@ -4328,7 +4328,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>8</v>
       </c>
@@ -4342,7 +4342,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>6</v>
       </c>
@@ -4356,7 +4356,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>17</v>
       </c>
@@ -4370,7 +4370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>21</v>
       </c>
@@ -4384,7 +4384,7 @@
         <v>10.98</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>53</v>
       </c>
@@ -4398,7 +4398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>9</v>
       </c>
@@ -4412,7 +4412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>86</v>
       </c>
@@ -4426,7 +4426,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>53</v>
       </c>
@@ -4440,7 +4440,7 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>5</v>
       </c>
@@ -4454,7 +4454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>8</v>
       </c>
@@ -4468,7 +4468,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>6</v>
       </c>
@@ -4482,7 +4482,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>17</v>
       </c>
@@ -4496,7 +4496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>21</v>
       </c>
@@ -4510,7 +4510,7 @@
         <v>8.5299999999999994</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>53</v>
       </c>
@@ -4524,7 +4524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>9</v>
       </c>
@@ -4538,7 +4538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>86</v>
       </c>
@@ -4552,7 +4552,7 @@
         <v>0.71</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>53</v>
       </c>
@@ -4566,7 +4566,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>5</v>
       </c>
@@ -4580,7 +4580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>8</v>
       </c>
@@ -4594,7 +4594,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>6</v>
       </c>
@@ -4608,7 +4608,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>17</v>
       </c>
@@ -4622,7 +4622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>21</v>
       </c>
@@ -4636,7 +4636,7 @@
         <v>10.51</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>53</v>
       </c>
@@ -4650,7 +4650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>9</v>
       </c>
@@ -4664,7 +4664,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>86</v>
       </c>
@@ -4678,7 +4678,7 @@
         <v>0.59</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>53</v>
       </c>
@@ -4692,7 +4692,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>5</v>
       </c>
@@ -4706,7 +4706,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>8</v>
       </c>
@@ -4720,7 +4720,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>6</v>
       </c>
@@ -4734,7 +4734,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>17</v>
       </c>
@@ -4748,7 +4748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>21</v>
       </c>
@@ -4762,7 +4762,7 @@
         <v>11.22</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>53</v>
       </c>
@@ -4776,7 +4776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>9</v>
       </c>
@@ -4790,7 +4790,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>86</v>
       </c>
@@ -4804,7 +4804,7 @@
         <v>0.72</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>53</v>
       </c>
@@ -4818,7 +4818,7 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>5</v>
       </c>
@@ -4832,7 +4832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>8</v>
       </c>
@@ -4846,7 +4846,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>6</v>
       </c>
@@ -4860,7 +4860,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>17</v>
       </c>
@@ -4874,7 +4874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>21</v>
       </c>
@@ -4888,7 +4888,7 @@
         <v>10.32</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>53</v>
       </c>
@@ -4902,7 +4902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>9</v>
       </c>
@@ -4916,7 +4916,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>86</v>
       </c>
@@ -4930,7 +4930,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>53</v>
       </c>
@@ -4944,7 +4944,7 @@
         <v>1.36</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>5</v>
       </c>
@@ -4958,7 +4958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>8</v>
       </c>
@@ -4972,7 +4972,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>6</v>
       </c>
@@ -4986,7 +4986,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>17</v>
       </c>
@@ -5000,7 +5000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>21</v>
       </c>
@@ -5014,7 +5014,7 @@
         <v>5.43</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>53</v>
       </c>
@@ -5028,7 +5028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>9</v>
       </c>
@@ -5042,7 +5042,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>86</v>
       </c>
@@ -5056,7 +5056,7 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>53</v>
       </c>
@@ -5070,7 +5070,7 @@
         <v>1.85</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>5</v>
       </c>
@@ -5084,7 +5084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>8</v>
       </c>
@@ -5098,7 +5098,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>6</v>
       </c>
@@ -5112,7 +5112,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>17</v>
       </c>
@@ -5126,7 +5126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>21</v>
       </c>
@@ -5140,7 +5140,7 @@
         <v>3.08</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>53</v>
       </c>
@@ -5154,7 +5154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>9</v>
       </c>
@@ -5168,7 +5168,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>86</v>
       </c>
@@ -5182,7 +5182,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>53</v>
       </c>
@@ -5196,7 +5196,7 @@
         <v>1.77</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>5</v>
       </c>
@@ -5210,7 +5210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>8</v>
       </c>
@@ -5224,7 +5224,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>6</v>
       </c>
@@ -5238,7 +5238,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>17</v>
       </c>
@@ -5252,7 +5252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>21</v>
       </c>
@@ -5266,7 +5266,7 @@
         <v>4.28</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>53</v>
       </c>
@@ -5280,7 +5280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>9</v>
       </c>
@@ -5294,7 +5294,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>86</v>
       </c>
@@ -5308,7 +5308,7 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>53</v>
       </c>
@@ -5322,7 +5322,7 @@
         <v>1.57</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>5</v>
       </c>
@@ -5336,7 +5336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>8</v>
       </c>
@@ -5350,7 +5350,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>6</v>
       </c>
@@ -5364,7 +5364,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>17</v>
       </c>
@@ -5378,7 +5378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>21</v>
       </c>
@@ -5392,7 +5392,7 @@
         <v>6.02</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>53</v>
       </c>
@@ -5406,7 +5406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>9</v>
       </c>
@@ -5420,7 +5420,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>86</v>
       </c>
@@ -5434,7 +5434,7 @@
         <v>0.63</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>53</v>
       </c>
@@ -5448,7 +5448,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>5</v>
       </c>
@@ -5462,7 +5462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>8</v>
       </c>
@@ -5476,7 +5476,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>6</v>
       </c>
@@ -5490,7 +5490,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>17</v>
       </c>
@@ -5504,7 +5504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>21</v>
       </c>
@@ -5518,7 +5518,7 @@
         <v>3.56</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>53</v>
       </c>
@@ -5532,7 +5532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>9</v>
       </c>
@@ -5546,7 +5546,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>86</v>
       </c>
@@ -5560,7 +5560,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>53</v>
       </c>
@@ -5574,7 +5574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>5</v>
       </c>
@@ -5585,7 +5585,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>8</v>
       </c>
@@ -5599,7 +5599,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>6</v>
       </c>
@@ -5613,7 +5613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>17</v>
       </c>
@@ -5624,7 +5624,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>21</v>
       </c>
@@ -5638,7 +5638,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>53</v>
       </c>
@@ -5652,7 +5652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>9</v>
       </c>
@@ -5666,7 +5666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>86</v>
       </c>
@@ -5680,7 +5680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>53</v>
       </c>
@@ -5694,7 +5694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>5</v>
       </c>
@@ -5705,7 +5705,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>8</v>
       </c>
@@ -5719,7 +5719,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>6</v>
       </c>
@@ -5733,7 +5733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>17</v>
       </c>
@@ -5744,7 +5744,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>21</v>
       </c>
@@ -5758,7 +5758,7 @@
         <v>2.44</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>53</v>
       </c>
@@ -5772,7 +5772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>9</v>
       </c>
@@ -5786,7 +5786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>86</v>
       </c>
@@ -5800,7 +5800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>53</v>
       </c>
@@ -5814,7 +5814,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>5</v>
       </c>
@@ -5825,7 +5825,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>8</v>
       </c>
@@ -5839,7 +5839,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>6</v>
       </c>
@@ -5853,7 +5853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>17</v>
       </c>
@@ -5864,7 +5864,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>21</v>
       </c>
@@ -5878,7 +5878,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>53</v>
       </c>
@@ -5892,7 +5892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>9</v>
       </c>
@@ -5906,7 +5906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>86</v>
       </c>
@@ -5920,7 +5920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>53</v>
       </c>
@@ -5934,7 +5934,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>5</v>
       </c>
@@ -5945,7 +5945,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>8</v>
       </c>
@@ -5959,7 +5959,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>6</v>
       </c>
@@ -5973,7 +5973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>17</v>
       </c>
@@ -5984,7 +5984,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>21</v>
       </c>
@@ -5998,7 +5998,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>53</v>
       </c>
@@ -6012,7 +6012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>9</v>
       </c>
@@ -6026,7 +6026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>86</v>
       </c>
@@ -6040,7 +6040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>53</v>
       </c>
@@ -6054,7 +6054,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>5</v>
       </c>
@@ -6065,7 +6065,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>8</v>
       </c>
@@ -6079,7 +6079,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>6</v>
       </c>
@@ -6093,7 +6093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>17</v>
       </c>
@@ -6104,7 +6104,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>21</v>
       </c>
@@ -6118,7 +6118,7 @@
         <v>2.67</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>53</v>
       </c>
@@ -6132,7 +6132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>9</v>
       </c>
@@ -6146,7 +6146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>86</v>
       </c>
@@ -6160,7 +6160,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>53</v>
       </c>
@@ -6174,7 +6174,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>5</v>
       </c>
@@ -6185,7 +6185,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>8</v>
       </c>
@@ -6199,7 +6199,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>6</v>
       </c>
@@ -6213,7 +6213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>17</v>
       </c>
@@ -6224,7 +6224,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>21</v>
       </c>
@@ -6238,7 +6238,7 @@
         <v>2.5099999999999998</v>
       </c>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>53</v>
       </c>
@@ -6252,7 +6252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>9</v>
       </c>
@@ -6266,7 +6266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>86</v>
       </c>
@@ -6280,7 +6280,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>53</v>
       </c>
@@ -6294,7 +6294,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>5</v>
       </c>
@@ -6305,7 +6305,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>8</v>
       </c>
@@ -6319,7 +6319,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>6</v>
       </c>
@@ -6333,7 +6333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>17</v>
       </c>
@@ -6344,7 +6344,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>21</v>
       </c>
@@ -6358,7 +6358,7 @@
         <v>2.5099999999999998</v>
       </c>
     </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>53</v>
       </c>
@@ -6372,7 +6372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>9</v>
       </c>
@@ -6386,7 +6386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>86</v>
       </c>
@@ -6400,7 +6400,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>53</v>
       </c>
@@ -6414,7 +6414,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>5</v>
       </c>
@@ -6425,7 +6425,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>8</v>
       </c>
@@ -6439,7 +6439,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>6</v>
       </c>
@@ -6453,7 +6453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>17</v>
       </c>
@@ -6464,7 +6464,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>21</v>
       </c>
@@ -6478,7 +6478,7 @@
         <v>2.56</v>
       </c>
     </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>53</v>
       </c>
@@ -6492,7 +6492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>9</v>
       </c>
@@ -6506,7 +6506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>86</v>
       </c>
@@ -6520,7 +6520,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>53</v>
       </c>
@@ -6534,7 +6534,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>5</v>
       </c>
@@ -6545,7 +6545,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>8</v>
       </c>
@@ -6559,7 +6559,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>6</v>
       </c>
@@ -6573,7 +6573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>17</v>
       </c>
@@ -6584,7 +6584,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>21</v>
       </c>
@@ -6598,7 +6598,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>53</v>
       </c>
@@ -6612,7 +6612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>9</v>
       </c>
@@ -6626,7 +6626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>86</v>
       </c>
@@ -6640,7 +6640,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>53</v>
       </c>
@@ -6654,7 +6654,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>5</v>
       </c>
@@ -6665,7 +6665,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>8</v>
       </c>
@@ -6679,7 +6679,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>6</v>
       </c>
@@ -6693,7 +6693,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>17</v>
       </c>
@@ -6704,7 +6704,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>21</v>
       </c>
@@ -6718,7 +6718,7 @@
         <v>2.4900000000000002</v>
       </c>
     </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>53</v>
       </c>
@@ -6732,7 +6732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>9</v>
       </c>
@@ -6746,7 +6746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>86</v>
       </c>
@@ -6760,7 +6760,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>53</v>
       </c>
@@ -6774,7 +6774,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>5</v>
       </c>
@@ -6785,7 +6785,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>8</v>
       </c>
@@ -6799,7 +6799,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>6</v>
       </c>
@@ -6813,7 +6813,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>17</v>
       </c>
@@ -6824,7 +6824,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>21</v>
       </c>
@@ -6838,7 +6838,7 @@
         <v>2.4900000000000002</v>
       </c>
     </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>53</v>
       </c>
@@ -6852,7 +6852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>9</v>
       </c>
@@ -6866,7 +6866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>86</v>
       </c>
@@ -6880,7 +6880,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
         <v>53</v>
       </c>
@@ -6894,7 +6894,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>5</v>
       </c>
@@ -6905,7 +6905,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>8</v>
       </c>
@@ -6919,7 +6919,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>6</v>
       </c>
@@ -6933,7 +6933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>17</v>
       </c>
@@ -6944,7 +6944,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
         <v>21</v>
       </c>
@@ -6958,7 +6958,7 @@
         <v>2.4900000000000002</v>
       </c>
     </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
         <v>53</v>
       </c>
@@ -6972,7 +6972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>9</v>
       </c>
@@ -6986,7 +6986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
         <v>86</v>
       </c>
@@ -7000,7 +7000,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
         <v>53</v>
       </c>
@@ -7014,7 +7014,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>5</v>
       </c>
@@ -7025,7 +7025,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>8</v>
       </c>
@@ -7039,7 +7039,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>6</v>
       </c>
@@ -7053,7 +7053,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
         <v>17</v>
       </c>
@@ -7064,7 +7064,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
         <v>21</v>
       </c>
@@ -7078,7 +7078,7 @@
         <v>2.48</v>
       </c>
     </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
         <v>53</v>
       </c>
@@ -7092,7 +7092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
         <v>9</v>
       </c>
@@ -7106,7 +7106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
         <v>86</v>
       </c>
@@ -7120,7 +7120,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
         <v>53</v>
       </c>
@@ -7134,7 +7134,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
         <v>5</v>
       </c>
@@ -7145,7 +7145,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
         <v>8</v>
       </c>
@@ -7159,7 +7159,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
         <v>6</v>
       </c>
@@ -7173,7 +7173,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
         <v>17</v>
       </c>
@@ -7184,7 +7184,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
         <v>21</v>
       </c>
@@ -7198,7 +7198,7 @@
         <v>2.39</v>
       </c>
     </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
         <v>53</v>
       </c>
@@ -7212,7 +7212,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
         <v>9</v>
       </c>
@@ -7226,7 +7226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
         <v>86</v>
       </c>
@@ -7240,7 +7240,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
         <v>53</v>
       </c>
@@ -7254,7 +7254,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
         <v>5</v>
       </c>
@@ -7265,7 +7265,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
         <v>8</v>
       </c>
@@ -7279,7 +7279,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
         <v>6</v>
       </c>
@@ -7293,7 +7293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
         <v>17</v>
       </c>
@@ -7304,7 +7304,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
         <v>21</v>
       </c>
@@ -7318,7 +7318,7 @@
         <v>2.4700000000000002</v>
       </c>
     </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
         <v>53</v>
       </c>
@@ -7332,7 +7332,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
         <v>9</v>
       </c>
@@ -7346,7 +7346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
         <v>86</v>
       </c>
@@ -7360,7 +7360,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
         <v>53</v>
       </c>
@@ -7374,7 +7374,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
         <v>5</v>
       </c>
@@ -7385,7 +7385,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
         <v>8</v>
       </c>
@@ -7399,7 +7399,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
         <v>6</v>
       </c>
@@ -7413,7 +7413,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
         <v>17</v>
       </c>
@@ -7424,7 +7424,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
         <v>21</v>
       </c>
@@ -7438,7 +7438,7 @@
         <v>2.27</v>
       </c>
     </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
         <v>53</v>
       </c>
@@ -7452,7 +7452,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
         <v>9</v>
       </c>
@@ -7466,7 +7466,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
         <v>86</v>
       </c>
@@ -7480,7 +7480,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
         <v>53</v>
       </c>
@@ -7494,7 +7494,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
         <v>5</v>
       </c>
@@ -7505,7 +7505,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
         <v>8</v>
       </c>
@@ -7519,7 +7519,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
         <v>6</v>
       </c>
@@ -7533,7 +7533,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
         <v>17</v>
       </c>
@@ -7544,7 +7544,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
         <v>21</v>
       </c>
@@ -7558,7 +7558,7 @@
         <v>1.97</v>
       </c>
     </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
         <v>53</v>
       </c>
@@ -7572,7 +7572,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
         <v>9</v>
       </c>
@@ -7586,7 +7586,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
         <v>86</v>
       </c>
@@ -7600,7 +7600,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
         <v>53</v>
       </c>
@@ -7614,7 +7614,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
         <v>5</v>
       </c>
@@ -7625,7 +7625,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
         <v>8</v>
       </c>
@@ -7639,7 +7639,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
         <v>6</v>
       </c>
@@ -7653,7 +7653,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="375" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
         <v>17</v>
       </c>
@@ -7664,7 +7664,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="376" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
         <v>21</v>
       </c>
@@ -7678,7 +7678,7 @@
         <v>1.93</v>
       </c>
     </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
         <v>53</v>
       </c>
@@ -7692,7 +7692,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="378" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
         <v>9</v>
       </c>
@@ -7706,7 +7706,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
         <v>86</v>
       </c>
@@ -7720,7 +7720,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
         <v>53</v>
       </c>
@@ -7734,7 +7734,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="381" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
         <v>5</v>
       </c>
@@ -7745,7 +7745,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="382" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
         <v>8</v>
       </c>
@@ -7759,7 +7759,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="383" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
         <v>6</v>
       </c>
@@ -7773,7 +7773,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="384" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
         <v>17</v>
       </c>
@@ -7784,7 +7784,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
         <v>21</v>
       </c>
@@ -7798,7 +7798,7 @@
         <v>2.21</v>
       </c>
     </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
         <v>53</v>
       </c>
@@ -7812,7 +7812,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
         <v>9</v>
       </c>
@@ -7826,7 +7826,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
         <v>86</v>
       </c>
@@ -7840,7 +7840,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="389" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
         <v>53</v>
       </c>
@@ -7854,7 +7854,7 @@
         <v>0.19</v>
       </c>
     </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
         <v>5</v>
       </c>
@@ -7865,7 +7865,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
         <v>8</v>
       </c>
@@ -7879,7 +7879,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
         <v>6</v>
       </c>
@@ -7893,7 +7893,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
         <v>17</v>
       </c>
@@ -7904,7 +7904,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="394" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
         <v>21</v>
       </c>
@@ -7918,7 +7918,7 @@
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="395" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
         <v>53</v>
       </c>
@@ -7932,7 +7932,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="396" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
         <v>9</v>
       </c>
@@ -7946,7 +7946,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
         <v>86</v>
       </c>
@@ -7960,7 +7960,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
         <v>53</v>
       </c>
@@ -7974,7 +7974,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="399" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
         <v>5</v>
       </c>
@@ -7985,7 +7985,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
         <v>8</v>
       </c>
@@ -7999,7 +7999,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="401" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
         <v>6</v>
       </c>
@@ -8013,7 +8013,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="402" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
         <v>17</v>
       </c>
@@ -8024,7 +8024,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="403" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
         <v>21</v>
       </c>
@@ -8038,7 +8038,7 @@
         <v>1.91</v>
       </c>
     </row>
-    <row r="404" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
         <v>53</v>
       </c>
@@ -8052,7 +8052,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="405" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
         <v>9</v>
       </c>
@@ -8066,7 +8066,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="406" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
         <v>86</v>
       </c>
@@ -8080,7 +8080,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="407" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
         <v>53</v>
       </c>
@@ -8094,7 +8094,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="408" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
         <v>5</v>
       </c>
@@ -8105,7 +8105,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="409" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
         <v>8</v>
       </c>
@@ -8119,7 +8119,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="410" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
         <v>6</v>
       </c>
@@ -8133,7 +8133,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="411" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
         <v>17</v>
       </c>
@@ -8144,7 +8144,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="412" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
         <v>21</v>
       </c>
@@ -8158,7 +8158,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
         <v>53</v>
       </c>
@@ -8172,7 +8172,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="414" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
         <v>9</v>
       </c>
@@ -8186,7 +8186,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="415" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
         <v>86</v>
       </c>
@@ -8200,7 +8200,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="416" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
         <v>53</v>
       </c>
@@ -8214,7 +8214,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="417" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
         <v>5</v>
       </c>
@@ -8225,7 +8225,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="418" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
         <v>8</v>
       </c>
@@ -8239,7 +8239,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="419" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
         <v>6</v>
       </c>
@@ -8253,7 +8253,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="420" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
         <v>17</v>
       </c>
@@ -8264,7 +8264,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="421" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
         <v>21</v>
       </c>
@@ -8278,7 +8278,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="422" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
         <v>53</v>
       </c>
@@ -8292,7 +8292,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="423" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
         <v>9</v>
       </c>
@@ -8306,7 +8306,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="424" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
         <v>86</v>
       </c>
@@ -8320,7 +8320,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="425" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
         <v>53</v>
       </c>
@@ -8334,7 +8334,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="426" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
         <v>5</v>
       </c>
@@ -8345,7 +8345,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="427" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
         <v>8</v>
       </c>
@@ -8359,7 +8359,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="428" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
         <v>6</v>
       </c>
@@ -8373,7 +8373,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="429" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
         <v>17</v>
       </c>
@@ -8384,7 +8384,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="430" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
         <v>21</v>
       </c>
@@ -8398,7 +8398,7 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="431" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
         <v>53</v>
       </c>
@@ -8412,7 +8412,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="432" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
         <v>9</v>
       </c>
@@ -8426,7 +8426,7 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="433" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
         <v>86</v>
       </c>
@@ -8440,7 +8440,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="434" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
         <v>53</v>
       </c>
@@ -8454,7 +8454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="435" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
         <v>5</v>
       </c>
@@ -8468,7 +8468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="436" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
         <v>8</v>
       </c>
@@ -8482,7 +8482,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="437" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
         <v>6</v>
       </c>
@@ -8496,7 +8496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="438" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
         <v>17</v>
       </c>
@@ -8510,7 +8510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="439" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
         <v>21</v>
       </c>
@@ -8524,7 +8524,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="440" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
         <v>53</v>
       </c>
@@ -8538,7 +8538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="441" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
         <v>9</v>
       </c>
@@ -8552,7 +8552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="442" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
         <v>86</v>
       </c>
@@ -8566,7 +8566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="443" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
         <v>53</v>
       </c>
@@ -8580,7 +8580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="444" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
         <v>5</v>
       </c>
@@ -8594,7 +8594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="445" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
         <v>8</v>
       </c>
@@ -8608,7 +8608,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="446" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
         <v>6</v>
       </c>
@@ -8622,7 +8622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="447" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
         <v>17</v>
       </c>
@@ -8636,7 +8636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="448" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
         <v>21</v>
       </c>
@@ -8650,7 +8650,7 @@
         <v>5.18</v>
       </c>
     </row>
-    <row r="449" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
         <v>53</v>
       </c>
@@ -8664,7 +8664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="450" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
         <v>9</v>
       </c>
@@ -8678,7 +8678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="451" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
         <v>86</v>
       </c>
@@ -8692,7 +8692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="452" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
         <v>53</v>
       </c>
@@ -8706,7 +8706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="453" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
         <v>5</v>
       </c>
@@ -8720,7 +8720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="454" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
         <v>8</v>
       </c>
@@ -8734,7 +8734,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="455" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
         <v>6</v>
       </c>
@@ -8748,7 +8748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="456" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
         <v>17</v>
       </c>
@@ -8762,7 +8762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="457" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
         <v>21</v>
       </c>
@@ -8776,7 +8776,7 @@
         <v>5.24</v>
       </c>
     </row>
-    <row r="458" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
         <v>53</v>
       </c>
@@ -8790,7 +8790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="459" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
         <v>9</v>
       </c>
@@ -8804,7 +8804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="460" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
         <v>86</v>
       </c>
@@ -8818,7 +8818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="461" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
         <v>53</v>
       </c>
@@ -8832,7 +8832,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="462" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
         <v>5</v>
       </c>
@@ -8846,7 +8846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="463" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
         <v>8</v>
       </c>
@@ -8860,7 +8860,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="464" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
         <v>6</v>
       </c>
@@ -8874,7 +8874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="465" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
         <v>17</v>
       </c>
@@ -8888,7 +8888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="466" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
         <v>21</v>
       </c>
@@ -8902,7 +8902,7 @@
         <v>6.32</v>
       </c>
     </row>
-    <row r="467" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
         <v>53</v>
       </c>
@@ -8916,7 +8916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="468" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
         <v>9</v>
       </c>
@@ -8930,7 +8930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="469" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
         <v>86</v>
       </c>
@@ -8944,7 +8944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="470" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
         <v>53</v>
       </c>
@@ -8958,7 +8958,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="471" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
         <v>5</v>
       </c>
@@ -8972,7 +8972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="472" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
         <v>8</v>
       </c>
@@ -8986,7 +8986,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="473" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
         <v>6</v>
       </c>
@@ -9000,7 +9000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="474" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
         <v>17</v>
       </c>
@@ -9014,7 +9014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="475" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
         <v>21</v>
       </c>
@@ -9028,7 +9028,7 @@
         <v>6.42</v>
       </c>
     </row>
-    <row r="476" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
         <v>53</v>
       </c>
@@ -9042,7 +9042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="477" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
         <v>9</v>
       </c>
@@ -9056,7 +9056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="478" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
         <v>86</v>
       </c>
@@ -9070,7 +9070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="479" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
         <v>53</v>
       </c>
@@ -9084,7 +9084,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="480" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
         <v>5</v>
       </c>
@@ -9098,7 +9098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="481" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
         <v>8</v>
       </c>
@@ -9112,7 +9112,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="482" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
         <v>6</v>
       </c>
@@ -9126,7 +9126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="483" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
         <v>17</v>
       </c>
@@ -9140,7 +9140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="484" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
         <v>21</v>
       </c>
@@ -9154,7 +9154,7 @@
         <v>6.28</v>
       </c>
     </row>
-    <row r="485" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
         <v>53</v>
       </c>
@@ -9168,7 +9168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="486" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
         <v>9</v>
       </c>
@@ -9182,7 +9182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="487" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
         <v>86</v>
       </c>
@@ -9196,7 +9196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="488" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
         <v>53</v>
       </c>
@@ -9210,7 +9210,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="489" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
         <v>5</v>
       </c>
@@ -9224,7 +9224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="490" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
         <v>8</v>
       </c>
@@ -9238,7 +9238,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="491" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
         <v>6</v>
       </c>
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="492" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
         <v>17</v>
       </c>
@@ -9266,7 +9266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="493" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
         <v>21</v>
       </c>
@@ -9280,7 +9280,7 @@
         <v>5.96</v>
       </c>
     </row>
-    <row r="494" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
         <v>53</v>
       </c>
@@ -9294,7 +9294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="495" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
         <v>9</v>
       </c>
@@ -9308,7 +9308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="496" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
         <v>86</v>
       </c>
@@ -9322,7 +9322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="497" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
         <v>53</v>
       </c>
@@ -9336,7 +9336,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="498" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
         <v>5</v>
       </c>
@@ -9350,7 +9350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="499" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
         <v>8</v>
       </c>
@@ -9364,7 +9364,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="500" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
         <v>6</v>
       </c>
@@ -9378,7 +9378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="501" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
         <v>17</v>
       </c>
@@ -9392,7 +9392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="502" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
         <v>21</v>
       </c>
@@ -9406,7 +9406,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="503" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
         <v>53</v>
       </c>
@@ -9420,7 +9420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="504" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
         <v>9</v>
       </c>
@@ -9434,7 +9434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="505" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
         <v>86</v>
       </c>
@@ -9448,7 +9448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="506" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
         <v>53</v>
       </c>
@@ -9462,7 +9462,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="507" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
         <v>5</v>
       </c>
@@ -9476,7 +9476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="508" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
         <v>8</v>
       </c>
@@ -9490,7 +9490,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="509" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
         <v>6</v>
       </c>
@@ -9504,7 +9504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="510" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
         <v>17</v>
       </c>
@@ -9518,7 +9518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="511" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
         <v>21</v>
       </c>
@@ -9532,7 +9532,7 @@
         <v>6.55</v>
       </c>
     </row>
-    <row r="512" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
         <v>53</v>
       </c>
@@ -9546,7 +9546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="513" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
         <v>9</v>
       </c>
@@ -9560,7 +9560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="514" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
         <v>86</v>
       </c>
@@ -9574,7 +9574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="515" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
         <v>53</v>
       </c>
@@ -9588,7 +9588,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="516" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
         <v>5</v>
       </c>
@@ -9602,7 +9602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="517" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
         <v>8</v>
       </c>
@@ -9616,7 +9616,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="518" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
         <v>6</v>
       </c>
@@ -9630,7 +9630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="519" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
         <v>17</v>
       </c>
@@ -9644,7 +9644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="520" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
         <v>21</v>
       </c>
@@ -9658,7 +9658,7 @@
         <v>5.35</v>
       </c>
     </row>
-    <row r="521" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
         <v>53</v>
       </c>
@@ -9672,7 +9672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="522" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
         <v>9</v>
       </c>
@@ -9686,7 +9686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="523" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
         <v>86</v>
       </c>
@@ -9700,7 +9700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="524" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
         <v>53</v>
       </c>
@@ -9714,7 +9714,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="525" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
         <v>5</v>
       </c>
@@ -9728,7 +9728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="526" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
         <v>8</v>
       </c>
@@ -9742,7 +9742,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="527" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
         <v>6</v>
       </c>
@@ -9756,7 +9756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="528" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
         <v>17</v>
       </c>
@@ -9770,7 +9770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="529" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
         <v>21</v>
       </c>
@@ -9784,7 +9784,7 @@
         <v>7.65</v>
       </c>
     </row>
-    <row r="530" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
         <v>53</v>
       </c>
@@ -9798,7 +9798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="531" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
         <v>9</v>
       </c>
@@ -9812,7 +9812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="532" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
         <v>86</v>
       </c>
@@ -9826,7 +9826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="533" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
         <v>53</v>
       </c>
@@ -9840,7 +9840,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="534" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
         <v>5</v>
       </c>
@@ -9854,7 +9854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="535" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
         <v>8</v>
       </c>
@@ -9868,7 +9868,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="536" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
         <v>6</v>
       </c>
@@ -9882,7 +9882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="537" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
         <v>17</v>
       </c>
@@ -9896,7 +9896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="538" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
         <v>21</v>
       </c>
@@ -9910,7 +9910,7 @@
         <v>7.54</v>
       </c>
     </row>
-    <row r="539" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
         <v>53</v>
       </c>
@@ -9924,7 +9924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="540" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
         <v>9</v>
       </c>
@@ -9938,7 +9938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="541" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
         <v>86</v>
       </c>
@@ -9952,7 +9952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="542" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
         <v>53</v>
       </c>
@@ -9966,7 +9966,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="543" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
         <v>5</v>
       </c>
@@ -9980,7 +9980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="544" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
         <v>8</v>
       </c>
@@ -9994,7 +9994,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="545" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
         <v>6</v>
       </c>
@@ -10008,7 +10008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="546" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
         <v>17</v>
       </c>
@@ -10022,7 +10022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="547" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
         <v>21</v>
       </c>
@@ -10036,7 +10036,7 @@
         <v>6.82</v>
       </c>
     </row>
-    <row r="548" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
         <v>53</v>
       </c>
@@ -10050,7 +10050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="549" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
         <v>9</v>
       </c>
@@ -10064,7 +10064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="550" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
         <v>86</v>
       </c>
@@ -10078,7 +10078,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="551" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
         <v>53</v>
       </c>
@@ -10092,7 +10092,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="552" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
         <v>5</v>
       </c>
@@ -10106,7 +10106,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="553" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
         <v>8</v>
       </c>
@@ -10120,7 +10120,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="554" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
         <v>6</v>
       </c>
@@ -10134,7 +10134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="555" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
         <v>17</v>
       </c>
@@ -10148,7 +10148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="556" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
         <v>21</v>
       </c>
@@ -10162,7 +10162,7 @@
         <v>7.86</v>
       </c>
     </row>
-    <row r="557" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
         <v>53</v>
       </c>
@@ -10176,7 +10176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="558" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
         <v>9</v>
       </c>
@@ -10190,7 +10190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="559" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
         <v>86</v>
       </c>
@@ -10204,7 +10204,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="560" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
         <v>53</v>
       </c>
@@ -10218,7 +10218,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="561" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
         <v>5</v>
       </c>
@@ -10232,7 +10232,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="562" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
         <v>8</v>
       </c>
@@ -10246,7 +10246,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="563" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
         <v>6</v>
       </c>
@@ -10260,7 +10260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="564" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
         <v>17</v>
       </c>
@@ -10274,7 +10274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="565" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
         <v>21</v>
       </c>
@@ -10288,7 +10288,7 @@
         <v>7.22</v>
       </c>
     </row>
-    <row r="566" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
         <v>53</v>
       </c>
@@ -10302,7 +10302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="567" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
         <v>9</v>
       </c>
@@ -10316,7 +10316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="568" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
         <v>86</v>
       </c>
@@ -10330,7 +10330,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="569" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
         <v>53</v>
       </c>
@@ -10344,7 +10344,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="570" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
         <v>5</v>
       </c>
@@ -10358,7 +10358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="571" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
         <v>8</v>
       </c>
@@ -10372,7 +10372,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="572" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
         <v>6</v>
       </c>
@@ -10386,7 +10386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="573" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
         <v>17</v>
       </c>
@@ -10400,7 +10400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="574" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
         <v>21</v>
       </c>
@@ -10414,7 +10414,7 @@
         <v>5.61</v>
       </c>
     </row>
-    <row r="575" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
         <v>53</v>
       </c>
@@ -10428,7 +10428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="576" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
         <v>9</v>
       </c>
@@ -10442,7 +10442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="577" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
         <v>86</v>
       </c>
@@ -10456,7 +10456,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="578" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
         <v>53</v>
       </c>
@@ -10470,7 +10470,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="579" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
         <v>5</v>
       </c>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="580" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
         <v>8</v>
       </c>
@@ -10498,7 +10498,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="581" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
         <v>6</v>
       </c>
@@ -10512,7 +10512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="582" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
         <v>17</v>
       </c>
@@ -10526,7 +10526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="583" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
         <v>21</v>
       </c>
@@ -10540,7 +10540,7 @@
         <v>6.92</v>
       </c>
     </row>
-    <row r="584" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
         <v>53</v>
       </c>
@@ -10554,7 +10554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="585" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
         <v>9</v>
       </c>
@@ -10568,7 +10568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="586" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
         <v>86</v>
       </c>
@@ -10582,7 +10582,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="587" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
         <v>53</v>
       </c>
@@ -10596,7 +10596,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="588" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
         <v>5</v>
       </c>
@@ -10610,7 +10610,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="589" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
         <v>8</v>
       </c>
@@ -10624,7 +10624,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="590" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
         <v>6</v>
       </c>
@@ -10638,7 +10638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="591" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
         <v>17</v>
       </c>
@@ -10652,7 +10652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="592" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
         <v>21</v>
       </c>
@@ -10666,7 +10666,7 @@
         <v>7.38</v>
       </c>
     </row>
-    <row r="593" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
         <v>53</v>
       </c>
@@ -10680,7 +10680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="594" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
         <v>9</v>
       </c>
@@ -10694,7 +10694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="595" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
         <v>86</v>
       </c>
@@ -10708,7 +10708,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="596" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
         <v>53</v>
       </c>
@@ -10722,7 +10722,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="597" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
         <v>5</v>
       </c>
@@ -10736,7 +10736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="598" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
         <v>8</v>
       </c>
@@ -10750,7 +10750,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="599" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A599" t="s">
         <v>6</v>
       </c>
@@ -10764,7 +10764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="600" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A600" t="s">
         <v>17</v>
       </c>
@@ -10778,7 +10778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="601" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
         <v>21</v>
       </c>
@@ -10792,7 +10792,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="602" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A602" t="s">
         <v>53</v>
       </c>
@@ -10806,7 +10806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="603" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A603" t="s">
         <v>9</v>
       </c>
@@ -10820,7 +10820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="604" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A604" t="s">
         <v>86</v>
       </c>
@@ -10834,7 +10834,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="605" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
         <v>53</v>
       </c>
@@ -10848,7 +10848,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="606" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
         <v>5</v>
       </c>
@@ -10862,7 +10862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="607" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
         <v>8</v>
       </c>
@@ -10876,7 +10876,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="608" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
         <v>6</v>
       </c>
@@ -10890,7 +10890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="609" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
         <v>17</v>
       </c>
@@ -10904,7 +10904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="610" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A610" t="s">
         <v>21</v>
       </c>
@@ -10918,7 +10918,7 @@
         <v>3.57</v>
       </c>
     </row>
-    <row r="611" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
         <v>53</v>
       </c>
@@ -10932,7 +10932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="612" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A612" t="s">
         <v>9</v>
       </c>
@@ -10946,7 +10946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="613" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A613" t="s">
         <v>86</v>
       </c>
@@ -10960,7 +10960,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="614" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A614" t="s">
         <v>53</v>
       </c>
@@ -10974,7 +10974,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="615" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
         <v>5</v>
       </c>
@@ -10988,7 +10988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="616" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A616" t="s">
         <v>8</v>
       </c>
@@ -11002,7 +11002,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="617" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
         <v>6</v>
       </c>
@@ -11016,7 +11016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="618" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A618" t="s">
         <v>17</v>
       </c>
@@ -11030,7 +11030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="619" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A619" t="s">
         <v>21</v>
       </c>
@@ -11044,7 +11044,7 @@
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="620" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
         <v>53</v>
       </c>
@@ -11058,7 +11058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="621" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A621" t="s">
         <v>9</v>
       </c>
@@ -11072,7 +11072,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="622" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A622" t="s">
         <v>86</v>
       </c>
@@ -11086,7 +11086,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="623" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A623" t="s">
         <v>53</v>
       </c>
@@ -11100,7 +11100,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="624" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A624" t="s">
         <v>5</v>
       </c>
@@ -11114,7 +11114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="625" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A625" t="s">
         <v>8</v>
       </c>
@@ -11128,7 +11128,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="626" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A626" t="s">
         <v>6</v>
       </c>
@@ -11142,7 +11142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="627" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A627" t="s">
         <v>17</v>
       </c>
@@ -11156,7 +11156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="628" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A628" t="s">
         <v>21</v>
       </c>
@@ -11170,7 +11170,7 @@
         <v>2.82</v>
       </c>
     </row>
-    <row r="629" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A629" t="s">
         <v>53</v>
       </c>
@@ -11184,7 +11184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="630" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A630" t="s">
         <v>9</v>
       </c>
@@ -11198,7 +11198,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="631" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A631" t="s">
         <v>86</v>
       </c>
@@ -11212,7 +11212,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="632" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A632" t="s">
         <v>53</v>
       </c>
@@ -11226,7 +11226,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="633" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A633" t="s">
         <v>5</v>
       </c>
@@ -11240,7 +11240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="634" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A634" t="s">
         <v>8</v>
       </c>
@@ -11254,7 +11254,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="635" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A635" t="s">
         <v>6</v>
       </c>
@@ -11268,7 +11268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="636" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A636" t="s">
         <v>17</v>
       </c>
@@ -11282,7 +11282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="637" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A637" t="s">
         <v>21</v>
       </c>
@@ -11296,7 +11296,7 @@
         <v>3.96</v>
       </c>
     </row>
-    <row r="638" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A638" t="s">
         <v>53</v>
       </c>
@@ -11310,7 +11310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="639" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A639" t="s">
         <v>9</v>
       </c>
@@ -11324,7 +11324,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="640" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A640" t="s">
         <v>86</v>
       </c>
@@ -11338,7 +11338,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="641" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A641" t="s">
         <v>53</v>
       </c>
@@ -11352,7 +11352,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="642" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A642" t="s">
         <v>5</v>
       </c>
@@ -11366,7 +11366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="643" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A643" t="s">
         <v>8</v>
       </c>
@@ -11380,7 +11380,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="644" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A644" t="s">
         <v>6</v>
       </c>
@@ -11394,7 +11394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="645" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A645" t="s">
         <v>17</v>
       </c>
@@ -11408,7 +11408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="646" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A646" t="s">
         <v>21</v>
       </c>
@@ -11422,7 +11422,7 @@
         <v>2.34</v>
       </c>
     </row>
-    <row r="647" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A647" t="s">
         <v>53</v>
       </c>
@@ -11436,7 +11436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="648" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A648" t="s">
         <v>9</v>
       </c>
@@ -11450,7 +11450,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="649" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A649" t="s">
         <v>86</v>
       </c>
@@ -11464,7 +11464,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="650" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A650" t="s">
         <v>60</v>
       </c>
@@ -11478,7 +11478,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="651" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A651" t="s">
         <v>61</v>
       </c>
@@ -11492,7 +11492,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="652" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A652" t="s">
         <v>60</v>
       </c>
@@ -11506,7 +11506,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="653" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A653" t="s">
         <v>61</v>
       </c>
@@ -11520,7 +11520,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="654" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A654" t="s">
         <v>60</v>
       </c>
@@ -11534,7 +11534,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="655" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A655" t="s">
         <v>61</v>
       </c>
@@ -11548,7 +11548,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="656" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A656" t="s">
         <v>60</v>
       </c>
@@ -11562,7 +11562,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="657" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A657" t="s">
         <v>61</v>
       </c>
@@ -11576,7 +11576,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="658" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A658" t="s">
         <v>60</v>
       </c>
@@ -11590,7 +11590,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="659" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A659" t="s">
         <v>61</v>
       </c>
@@ -11604,7 +11604,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="660" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A660" t="s">
         <v>60</v>
       </c>
@@ -11618,7 +11618,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="661" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A661" t="s">
         <v>61</v>
       </c>
@@ -11632,7 +11632,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="662" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A662" t="s">
         <v>60</v>
       </c>
@@ -11646,7 +11646,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="663" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A663" t="s">
         <v>61</v>
       </c>
@@ -11660,7 +11660,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="664" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A664" t="s">
         <v>60</v>
       </c>
@@ -11674,7 +11674,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="665" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A665" t="s">
         <v>61</v>
       </c>
@@ -11688,7 +11688,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="666" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A666" t="s">
         <v>60</v>
       </c>
@@ -11702,7 +11702,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="667" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A667" t="s">
         <v>61</v>
       </c>
@@ -11716,7 +11716,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="668" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A668" t="s">
         <v>60</v>
       </c>
@@ -11730,7 +11730,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="669" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A669" t="s">
         <v>61</v>
       </c>
@@ -11744,7 +11744,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="670" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A670" t="s">
         <v>60</v>
       </c>
@@ -11758,7 +11758,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="671" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A671" t="s">
         <v>61</v>
       </c>
@@ -11772,7 +11772,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="672" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A672" t="s">
         <v>60</v>
       </c>
@@ -11786,7 +11786,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="673" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A673" t="s">
         <v>61</v>
       </c>
@@ -11800,7 +11800,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="674" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A674" t="s">
         <v>60</v>
       </c>
@@ -11814,7 +11814,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="675" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A675" t="s">
         <v>61</v>
       </c>
@@ -11828,7 +11828,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="676" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A676" t="s">
         <v>60</v>
       </c>
@@ -11842,7 +11842,7 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="677" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A677" t="s">
         <v>61</v>
       </c>
@@ -11856,7 +11856,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="678" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A678" t="s">
         <v>60</v>
       </c>
@@ -11870,7 +11870,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="679" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A679" t="s">
         <v>61</v>
       </c>
@@ -11884,7 +11884,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="680" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A680" t="s">
         <v>60</v>
       </c>
@@ -11898,7 +11898,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="681" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A681" t="s">
         <v>61</v>
       </c>
@@ -11912,7 +11912,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="682" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A682" t="s">
         <v>60</v>
       </c>
@@ -11926,7 +11926,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="683" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A683" t="s">
         <v>61</v>
       </c>
@@ -11940,7 +11940,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="684" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A684" t="s">
         <v>60</v>
       </c>
@@ -11954,7 +11954,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="685" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A685" t="s">
         <v>61</v>
       </c>
@@ -11968,7 +11968,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="686" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A686" t="s">
         <v>60</v>
       </c>
@@ -11982,7 +11982,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="687" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A687" t="s">
         <v>61</v>
       </c>
@@ -11996,7 +11996,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="688" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A688" t="s">
         <v>60</v>
       </c>
@@ -12010,7 +12010,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="689" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A689" t="s">
         <v>61</v>
       </c>
@@ -12024,7 +12024,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="690" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A690" t="s">
         <v>60</v>
       </c>
@@ -12038,7 +12038,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="691" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A691" t="s">
         <v>61</v>
       </c>
@@ -12052,7 +12052,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="692" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A692" t="s">
         <v>60</v>
       </c>
@@ -12066,7 +12066,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="693" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A693" t="s">
         <v>61</v>
       </c>
@@ -12080,7 +12080,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="694" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A694" t="s">
         <v>60</v>
       </c>
@@ -12094,7 +12094,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="695" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A695" t="s">
         <v>61</v>
       </c>
@@ -12108,7 +12108,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="696" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A696" t="s">
         <v>60</v>
       </c>
@@ -12122,7 +12122,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="697" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A697" t="s">
         <v>61</v>
       </c>

--- a/VerveStacks_EST/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0A7C904-378A-4D51-8ABC-BB3A1E2CA431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41CFED5B-F401-479A-8096-A76EC1D00873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-10470" yWindow="10890" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -235,6 +235,9 @@
   </si>
   <si>
     <t>Wind onshore</t>
+  </si>
+  <si>
+    <t>~UC_T: FX</t>
   </si>
   <si>
     <t>pset_pn</t>
@@ -484,9 +487,6 @@
   </si>
   <si>
     <t>~UC_T: UC_CAP~UP</t>
-  </si>
-  <si>
-    <t>UC_T: FX</t>
   </si>
 </sst>
 </file>
@@ -985,42 +985,42 @@
   <sheetData>
     <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
@@ -1028,34 +1028,34 @@
         <v>2030</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E11">
         <v>0.36699999999999999</v>
       </c>
       <c r="F11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I11" s="12">
         <v>45155</v>
       </c>
       <c r="J11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L11" s="13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
@@ -1063,34 +1063,34 @@
         <v>2030</v>
       </c>
       <c r="C12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E12">
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="F12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I12" s="12">
         <v>45155</v>
       </c>
       <c r="J12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L12" s="13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
@@ -1098,34 +1098,34 @@
         <v>2030</v>
       </c>
       <c r="C13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I13" s="12">
         <v>45155</v>
       </c>
       <c r="J13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
@@ -1133,34 +1133,34 @@
         <v>2030</v>
       </c>
       <c r="C14" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E14">
         <v>1.31</v>
       </c>
       <c r="F14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I14" s="12">
         <v>45155</v>
       </c>
       <c r="J14" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
@@ -1168,34 +1168,34 @@
         <v>2030</v>
       </c>
       <c r="C15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D15" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E15">
         <v>1.2</v>
       </c>
       <c r="F15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H15" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I15" s="12">
         <v>45155</v>
       </c>
       <c r="J15" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L15" s="13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
@@ -1203,34 +1203,34 @@
         <v>2030</v>
       </c>
       <c r="C16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E16">
         <v>1.54</v>
       </c>
       <c r="F16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H16" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I16" s="12">
         <v>45155</v>
       </c>
       <c r="J16" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L16" s="13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
@@ -1238,34 +1238,34 @@
         <v>2030</v>
       </c>
       <c r="C17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E17">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="F17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I17" s="12">
         <v>45155</v>
       </c>
       <c r="J17" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L17" s="13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
@@ -1273,34 +1273,34 @@
         <v>2030</v>
       </c>
       <c r="C18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D18" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E18">
         <v>3.7149999999999999</v>
       </c>
       <c r="F18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G18" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H18" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I18" s="12">
         <v>45155</v>
       </c>
       <c r="J18" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K18" s="13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L18" s="13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
@@ -1308,34 +1308,34 @@
         <v>2030</v>
       </c>
       <c r="C19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E19">
         <v>3.1240000000000001</v>
       </c>
       <c r="F19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G19" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H19" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I19" s="12">
         <v>45155</v>
       </c>
       <c r="J19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K19" s="13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L19" s="13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
@@ -1343,34 +1343,34 @@
         <v>2030</v>
       </c>
       <c r="C20" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D20" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E20">
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G20" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H20" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I20" s="12">
         <v>45155</v>
       </c>
       <c r="J20" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K20" s="13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L20" s="13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
@@ -1378,34 +1378,34 @@
         <v>2030</v>
       </c>
       <c r="C21" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E21">
         <v>16.376000000000001</v>
       </c>
       <c r="F21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H21" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I21" s="12">
         <v>45155</v>
       </c>
       <c r="J21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K21" s="13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L21" s="13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
@@ -1413,34 +1413,34 @@
         <v>2030</v>
       </c>
       <c r="C22" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D22" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E22">
         <v>0.26600000000000001</v>
       </c>
       <c r="F22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G22" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I22" s="12">
         <v>45155</v>
       </c>
       <c r="J22" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K22" s="13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L22" s="13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="23" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
@@ -1448,34 +1448,34 @@
         <v>2030</v>
       </c>
       <c r="C23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D23" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E23">
         <v>39.503999999999998</v>
       </c>
       <c r="F23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G23" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H23" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I23" s="12">
         <v>45155</v>
       </c>
       <c r="J23" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K23" s="13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L23" s="13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
@@ -1483,34 +1483,34 @@
         <v>2030</v>
       </c>
       <c r="C24" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D24" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E24">
         <v>33.22</v>
       </c>
       <c r="F24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G24" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H24" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I24" s="12">
         <v>45155</v>
       </c>
       <c r="J24" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K24" s="13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L24" s="13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="25" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
@@ -1518,34 +1518,34 @@
         <v>2030</v>
       </c>
       <c r="C25" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D25" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E25">
         <v>10.634</v>
       </c>
       <c r="F25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G25" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H25" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I25" s="12">
         <v>45155</v>
       </c>
       <c r="J25" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K25" s="13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L25" s="13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -1604,19 +1604,19 @@
     </row>
     <row r="2" spans="1:38" x14ac:dyDescent="0.25">
       <c r="F2" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:38" x14ac:dyDescent="0.25">
@@ -1624,7 +1624,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G3" s="3">
         <v>0.22831050228310504</v>
@@ -1644,7 +1644,7 @@
     </row>
     <row r="4" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B4" t="s">
         <v>2</v>
@@ -1669,10 +1669,10 @@
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D5" s="4"/>
       <c r="F5" t="s">
@@ -1692,7 +1692,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
         <v>7</v>
@@ -1717,15 +1717,15 @@
         <v>0.68557077625570773</v>
       </c>
       <c r="U6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AF6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:38" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
@@ -1938,7 +1938,7 @@
     </row>
     <row r="10" spans="1:38" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G10" s="3">
         <v>0.11415525114155252</v>
@@ -1964,7 +1964,7 @@
         <v>24</v>
       </c>
       <c r="U13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:38" x14ac:dyDescent="0.25">
@@ -2017,10 +2017,10 @@
         <v>Hydropower - large-scale unit,Solar photovoltaics - Large scale unit,Wind offshore,Wind onshore</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="U15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="V15" t="s">
         <v>17</v>
@@ -2039,7 +2039,7 @@
         <v>0</v>
       </c>
       <c r="AF15" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:38" x14ac:dyDescent="0.25">
@@ -2138,13 +2138,13 @@
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C25" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D25" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -2152,13 +2152,13 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C26" t="s">
+        <v>45</v>
+      </c>
+      <c r="D26" t="s">
         <v>44</v>
-      </c>
-      <c r="D26" t="s">
-        <v>43</v>
       </c>
       <c r="E26">
         <v>-1</v>
@@ -2166,10 +2166,10 @@
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E27">
         <v>0.03</v>
@@ -2181,29 +2181,29 @@
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E28">
         <v>50</v>
       </c>
       <c r="G28" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E29">
         <v>8.76</v>
       </c>
       <c r="G29" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.25">
       <c r="E35" t="s">
-        <v>117</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.25">
@@ -2211,7 +2211,7 @@
         <v>11</v>
       </c>
       <c r="C36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D36" t="s">
         <v>2</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C37" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E37">
         <v>1</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C39" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -2261,7 +2261,7 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.25">
       <c r="D40" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E40">
         <v>-1</v>
@@ -2294,41 +2294,41 @@
   <sheetData>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C11">
         <v>0.5</v>
@@ -2362,24 +2362,24 @@
     </row>
     <row r="18" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>2</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F19" s="8">
         <v>2025</v>
@@ -2404,7 +2404,7 @@
         <v>solar</v>
       </c>
       <c r="D20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -2434,7 +2434,7 @@
         <v>wind*</v>
       </c>
       <c r="D21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -2464,7 +2464,7 @@
         <v>hydro</v>
       </c>
       <c r="D22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -2494,7 +2494,7 @@
         <v>nuclear</v>
       </c>
       <c r="D23" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -2524,27 +2524,27 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B2">
         <v>2000</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D2">
         <v>0.01</v>
@@ -2558,7 +2558,7 @@
         <v>2000</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -2572,7 +2572,7 @@
         <v>2000</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D4">
         <v>0.6</v>
@@ -2586,7 +2586,7 @@
         <v>2000</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -2600,7 +2600,7 @@
         <v>2000</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -2614,7 +2614,7 @@
         <v>2000</v>
       </c>
       <c r="C7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D7">
         <v>7.9</v>
@@ -2622,13 +2622,13 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B8">
         <v>2000</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -2642,7 +2642,7 @@
         <v>2000</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -2650,13 +2650,13 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B10">
         <v>2000</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -2664,13 +2664,13 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B11">
         <v>2001</v>
       </c>
       <c r="C11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D11">
         <v>0.01</v>
@@ -2684,7 +2684,7 @@
         <v>2001</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -2698,7 +2698,7 @@
         <v>2001</v>
       </c>
       <c r="C13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D13">
         <v>0.6</v>
@@ -2712,7 +2712,7 @@
         <v>2001</v>
       </c>
       <c r="C14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14">
         <v>0.01</v>
@@ -2726,7 +2726,7 @@
         <v>2001</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -2740,7 +2740,7 @@
         <v>2001</v>
       </c>
       <c r="C16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D16">
         <v>7.87</v>
@@ -2748,13 +2748,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B17">
         <v>2001</v>
       </c>
       <c r="C17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -2768,7 +2768,7 @@
         <v>2001</v>
       </c>
       <c r="C18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -2776,13 +2776,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B19">
         <v>2001</v>
       </c>
       <c r="C19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -2790,13 +2790,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B20">
         <v>2002</v>
       </c>
       <c r="C20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D20">
         <v>0.02</v>
@@ -2810,7 +2810,7 @@
         <v>2002</v>
       </c>
       <c r="C21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -2824,7 +2824,7 @@
         <v>2002</v>
       </c>
       <c r="C22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D22">
         <v>0.53</v>
@@ -2838,7 +2838,7 @@
         <v>2002</v>
       </c>
       <c r="C23" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D23">
         <v>0.01</v>
@@ -2852,7 +2852,7 @@
         <v>2002</v>
       </c>
       <c r="C24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -2866,7 +2866,7 @@
         <v>2002</v>
       </c>
       <c r="C25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D25">
         <v>7.97</v>
@@ -2874,13 +2874,13 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B26">
         <v>2002</v>
       </c>
       <c r="C26" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -2894,7 +2894,7 @@
         <v>2002</v>
       </c>
       <c r="C27" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -2902,13 +2902,13 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B28">
         <v>2002</v>
       </c>
       <c r="C28" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -2916,13 +2916,13 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B29">
         <v>2003</v>
       </c>
       <c r="C29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D29">
         <v>0.03</v>
@@ -2936,7 +2936,7 @@
         <v>2003</v>
       </c>
       <c r="C30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -2950,7 +2950,7 @@
         <v>2003</v>
       </c>
       <c r="C31" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D31">
         <v>0.5</v>
@@ -2964,7 +2964,7 @@
         <v>2003</v>
       </c>
       <c r="C32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D32">
         <v>0.01</v>
@@ -2978,7 +2978,7 @@
         <v>2003</v>
       </c>
       <c r="C33" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -2992,7 +2992,7 @@
         <v>2003</v>
       </c>
       <c r="C34" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D34">
         <v>9.61</v>
@@ -3000,13 +3000,13 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B35">
         <v>2003</v>
       </c>
       <c r="C35" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -3020,7 +3020,7 @@
         <v>2003</v>
       </c>
       <c r="C36" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -3028,13 +3028,13 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B37">
         <v>2003</v>
       </c>
       <c r="C37" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D37">
         <v>0.01</v>
@@ -3042,13 +3042,13 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B38">
         <v>2004</v>
       </c>
       <c r="C38" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D38">
         <v>0.03</v>
@@ -3062,7 +3062,7 @@
         <v>2004</v>
       </c>
       <c r="C39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -3076,7 +3076,7 @@
         <v>2004</v>
       </c>
       <c r="C40" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D40">
         <v>0.49</v>
@@ -3090,7 +3090,7 @@
         <v>2004</v>
       </c>
       <c r="C41" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D41">
         <v>0.02</v>
@@ -3104,7 +3104,7 @@
         <v>2004</v>
       </c>
       <c r="C42" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -3118,7 +3118,7 @@
         <v>2004</v>
       </c>
       <c r="C43" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D43">
         <v>9.76</v>
@@ -3126,13 +3126,13 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B44">
         <v>2004</v>
       </c>
       <c r="C44" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -3146,7 +3146,7 @@
         <v>2004</v>
       </c>
       <c r="C45" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -3154,13 +3154,13 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B46">
         <v>2004</v>
       </c>
       <c r="C46" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D46">
         <v>0.01</v>
@@ -3168,13 +3168,13 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B47">
         <v>2005</v>
       </c>
       <c r="C47" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D47">
         <v>0.04</v>
@@ -3188,7 +3188,7 @@
         <v>2005</v>
       </c>
       <c r="C48" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -3202,7 +3202,7 @@
         <v>2005</v>
       </c>
       <c r="C49" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D49">
         <v>0.54</v>
@@ -3216,7 +3216,7 @@
         <v>2005</v>
       </c>
       <c r="C50" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D50">
         <v>0.02</v>
@@ -3230,7 +3230,7 @@
         <v>2005</v>
       </c>
       <c r="C51" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -3244,7 +3244,7 @@
         <v>2005</v>
       </c>
       <c r="C52" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D52">
         <v>9.5500000000000007</v>
@@ -3252,13 +3252,13 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B53">
         <v>2005</v>
       </c>
       <c r="C53" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -3272,7 +3272,7 @@
         <v>2005</v>
       </c>
       <c r="C54" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -3280,13 +3280,13 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B55">
         <v>2005</v>
       </c>
       <c r="C55" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D55">
         <v>0.05</v>
@@ -3294,13 +3294,13 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B56">
         <v>2006</v>
       </c>
       <c r="C56" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D56">
         <v>0.04</v>
@@ -3314,7 +3314,7 @@
         <v>2006</v>
       </c>
       <c r="C57" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>2006</v>
       </c>
       <c r="C58" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D58">
         <v>0.54</v>
@@ -3342,7 +3342,7 @@
         <v>2006</v>
       </c>
       <c r="C59" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D59">
         <v>0.01</v>
@@ -3356,7 +3356,7 @@
         <v>2006</v>
       </c>
       <c r="C60" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -3370,7 +3370,7 @@
         <v>2006</v>
       </c>
       <c r="C61" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D61">
         <v>9.06</v>
@@ -3378,13 +3378,13 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B62">
         <v>2006</v>
       </c>
       <c r="C62" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -3398,7 +3398,7 @@
         <v>2006</v>
       </c>
       <c r="C63" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -3406,13 +3406,13 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B64">
         <v>2006</v>
       </c>
       <c r="C64" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D64">
         <v>0.08</v>
@@ -3420,13 +3420,13 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B65">
         <v>2007</v>
       </c>
       <c r="C65" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D65">
         <v>0.03</v>
@@ -3440,7 +3440,7 @@
         <v>2007</v>
       </c>
       <c r="C66" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -3454,7 +3454,7 @@
         <v>2007</v>
       </c>
       <c r="C67" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D67">
         <v>0.34</v>
@@ -3468,7 +3468,7 @@
         <v>2007</v>
       </c>
       <c r="C68" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D68">
         <v>0.02</v>
@@ -3482,7 +3482,7 @@
         <v>2007</v>
       </c>
       <c r="C69" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -3496,7 +3496,7 @@
         <v>2007</v>
       </c>
       <c r="C70" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D70">
         <v>11.7</v>
@@ -3504,13 +3504,13 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B71">
         <v>2007</v>
       </c>
       <c r="C71" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -3524,7 +3524,7 @@
         <v>2007</v>
       </c>
       <c r="C72" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -3532,13 +3532,13 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B73">
         <v>2007</v>
       </c>
       <c r="C73" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D73">
         <v>0.09</v>
@@ -3546,13 +3546,13 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B74">
         <v>2008</v>
       </c>
       <c r="C74" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D74">
         <v>0.04</v>
@@ -3566,7 +3566,7 @@
         <v>2008</v>
       </c>
       <c r="C75" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -3580,7 +3580,7 @@
         <v>2008</v>
       </c>
       <c r="C76" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D76">
         <v>0.42</v>
@@ -3594,7 +3594,7 @@
         <v>2008</v>
       </c>
       <c r="C77" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D77">
         <v>0.03</v>
@@ -3608,7 +3608,7 @@
         <v>2008</v>
       </c>
       <c r="C78" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -3622,7 +3622,7 @@
         <v>2008</v>
       </c>
       <c r="C79" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D79">
         <v>9.9600000000000009</v>
@@ -3630,13 +3630,13 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B80">
         <v>2008</v>
       </c>
       <c r="C80" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -3650,7 +3650,7 @@
         <v>2008</v>
       </c>
       <c r="C81" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -3658,13 +3658,13 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B82">
         <v>2008</v>
       </c>
       <c r="C82" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D82">
         <v>0.13</v>
@@ -3672,13 +3672,13 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B83">
         <v>2009</v>
       </c>
       <c r="C83" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D83">
         <v>0.31</v>
@@ -3692,7 +3692,7 @@
         <v>2009</v>
       </c>
       <c r="C84" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -3706,7 +3706,7 @@
         <v>2009</v>
       </c>
       <c r="C85" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D85">
         <v>0.11</v>
@@ -3720,7 +3720,7 @@
         <v>2009</v>
       </c>
       <c r="C86" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D86">
         <v>0.03</v>
@@ -3734,7 +3734,7 @@
         <v>2009</v>
       </c>
       <c r="C87" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -3748,7 +3748,7 @@
         <v>2009</v>
       </c>
       <c r="C88" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D88">
         <v>8.1300000000000008</v>
@@ -3756,13 +3756,13 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B89">
         <v>2009</v>
       </c>
       <c r="C89" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -3776,7 +3776,7 @@
         <v>2009</v>
       </c>
       <c r="C90" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -3784,13 +3784,13 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B91">
         <v>2009</v>
       </c>
       <c r="C91" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D91">
         <v>0.2</v>
@@ -3798,13 +3798,13 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B92">
         <v>2010</v>
       </c>
       <c r="C92" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D92">
         <v>0.74</v>
@@ -3818,7 +3818,7 @@
         <v>2010</v>
       </c>
       <c r="C93" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -3832,7 +3832,7 @@
         <v>2010</v>
       </c>
       <c r="C94" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D94">
         <v>0.3</v>
@@ -3846,7 +3846,7 @@
         <v>2010</v>
       </c>
       <c r="C95" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D95">
         <v>0.03</v>
@@ -3860,7 +3860,7 @@
         <v>2010</v>
       </c>
       <c r="C96" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -3874,7 +3874,7 @@
         <v>2010</v>
       </c>
       <c r="C97" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D97">
         <v>11.62</v>
@@ -3882,13 +3882,13 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B98">
         <v>2010</v>
       </c>
       <c r="C98" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D98">
         <v>0</v>
@@ -3902,7 +3902,7 @@
         <v>2010</v>
       </c>
       <c r="C99" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D99">
         <v>0</v>
@@ -3910,13 +3910,13 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B100">
         <v>2010</v>
       </c>
       <c r="C100" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D100">
         <v>0.28000000000000003</v>
@@ -3924,13 +3924,13 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B101">
         <v>2011</v>
       </c>
       <c r="C101" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D101">
         <v>0.78</v>
@@ -3944,7 +3944,7 @@
         <v>2011</v>
       </c>
       <c r="C102" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -3958,7 +3958,7 @@
         <v>2011</v>
       </c>
       <c r="C103" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D103">
         <v>0.25</v>
@@ -3972,7 +3972,7 @@
         <v>2011</v>
       </c>
       <c r="C104" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D104">
         <v>0.03</v>
@@ -3986,7 +3986,7 @@
         <v>2011</v>
       </c>
       <c r="C105" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D105">
         <v>0</v>
@@ -4000,7 +4000,7 @@
         <v>2011</v>
       </c>
       <c r="C106" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D106">
         <v>11.46</v>
@@ -4008,13 +4008,13 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B107">
         <v>2011</v>
       </c>
       <c r="C107" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D107">
         <v>0</v>
@@ -4028,7 +4028,7 @@
         <v>2011</v>
       </c>
       <c r="C108" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D108">
         <v>0</v>
@@ -4036,13 +4036,13 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B109">
         <v>2011</v>
       </c>
       <c r="C109" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D109">
         <v>0.37</v>
@@ -4050,13 +4050,13 @@
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B110">
         <v>2012</v>
       </c>
       <c r="C110" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D110">
         <v>1</v>
@@ -4070,7 +4070,7 @@
         <v>2012</v>
       </c>
       <c r="C111" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D111">
         <v>0</v>
@@ -4084,7 +4084,7 @@
         <v>2012</v>
       </c>
       <c r="C112" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D112">
         <v>0.13</v>
@@ -4098,7 +4098,7 @@
         <v>2012</v>
       </c>
       <c r="C113" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D113">
         <v>0.04</v>
@@ -4112,7 +4112,7 @@
         <v>2012</v>
       </c>
       <c r="C114" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D114">
         <v>0</v>
@@ -4126,7 +4126,7 @@
         <v>2012</v>
       </c>
       <c r="C115" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D115">
         <v>10.36</v>
@@ -4134,13 +4134,13 @@
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B116">
         <v>2012</v>
       </c>
       <c r="C116" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D116">
         <v>0</v>
@@ -4154,7 +4154,7 @@
         <v>2012</v>
       </c>
       <c r="C117" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D117">
         <v>0</v>
@@ -4162,13 +4162,13 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B118">
         <v>2012</v>
       </c>
       <c r="C118" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D118">
         <v>0.43</v>
@@ -4176,13 +4176,13 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B119">
         <v>2013</v>
       </c>
       <c r="C119" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D119">
         <v>0.67</v>
@@ -4196,7 +4196,7 @@
         <v>2013</v>
       </c>
       <c r="C120" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D120">
         <v>0.01</v>
@@ -4210,7 +4210,7 @@
         <v>2013</v>
       </c>
       <c r="C121" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D121">
         <v>0.09</v>
@@ -4224,7 +4224,7 @@
         <v>2013</v>
       </c>
       <c r="C122" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D122">
         <v>0.03</v>
@@ -4238,7 +4238,7 @@
         <v>2013</v>
       </c>
       <c r="C123" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D123">
         <v>0</v>
@@ -4252,7 +4252,7 @@
         <v>2013</v>
       </c>
       <c r="C124" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D124">
         <v>11.95</v>
@@ -4260,13 +4260,13 @@
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B125">
         <v>2013</v>
       </c>
       <c r="C125" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D125">
         <v>0</v>
@@ -4280,7 +4280,7 @@
         <v>2013</v>
       </c>
       <c r="C126" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D126">
         <v>0</v>
@@ -4288,13 +4288,13 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B127">
         <v>2013</v>
       </c>
       <c r="C127" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D127">
         <v>0.53</v>
@@ -4302,13 +4302,13 @@
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B128">
         <v>2014</v>
       </c>
       <c r="C128" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D128">
         <v>0.76</v>
@@ -4322,7 +4322,7 @@
         <v>2014</v>
       </c>
       <c r="C129" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D129">
         <v>0.01</v>
@@ -4336,7 +4336,7 @@
         <v>2014</v>
       </c>
       <c r="C130" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D130">
         <v>7.0000000000000007E-2</v>
@@ -4350,7 +4350,7 @@
         <v>2014</v>
       </c>
       <c r="C131" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D131">
         <v>0.03</v>
@@ -4364,7 +4364,7 @@
         <v>2014</v>
       </c>
       <c r="C132" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D132">
         <v>0</v>
@@ -4378,7 +4378,7 @@
         <v>2014</v>
       </c>
       <c r="C133" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D133">
         <v>10.98</v>
@@ -4386,13 +4386,13 @@
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B134">
         <v>2014</v>
       </c>
       <c r="C134" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D134">
         <v>0</v>
@@ -4406,7 +4406,7 @@
         <v>2014</v>
       </c>
       <c r="C135" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D135">
         <v>0</v>
@@ -4414,13 +4414,13 @@
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B136">
         <v>2014</v>
       </c>
       <c r="C136" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D136">
         <v>0.6</v>
@@ -4428,13 +4428,13 @@
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B137">
         <v>2015</v>
       </c>
       <c r="C137" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D137">
         <v>0.82</v>
@@ -4448,7 +4448,7 @@
         <v>2015</v>
       </c>
       <c r="C138" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D138">
         <v>0</v>
@@ -4462,7 +4462,7 @@
         <v>2015</v>
       </c>
       <c r="C139" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D139">
         <v>0.06</v>
@@ -4476,7 +4476,7 @@
         <v>2015</v>
       </c>
       <c r="C140" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D140">
         <v>0.03</v>
@@ -4490,7 +4490,7 @@
         <v>2015</v>
       </c>
       <c r="C141" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D141">
         <v>0</v>
@@ -4504,7 +4504,7 @@
         <v>2015</v>
       </c>
       <c r="C142" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D142">
         <v>8.5299999999999994</v>
@@ -4512,13 +4512,13 @@
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B143">
         <v>2015</v>
       </c>
       <c r="C143" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D143">
         <v>0</v>
@@ -4532,7 +4532,7 @@
         <v>2015</v>
       </c>
       <c r="C144" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D144">
         <v>0</v>
@@ -4540,13 +4540,13 @@
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B145">
         <v>2015</v>
       </c>
       <c r="C145" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D145">
         <v>0.71</v>
@@ -4554,13 +4554,13 @@
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B146">
         <v>2016</v>
       </c>
       <c r="C146" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D146">
         <v>0.95</v>
@@ -4574,7 +4574,7 @@
         <v>2016</v>
       </c>
       <c r="C147" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D147">
         <v>0</v>
@@ -4588,7 +4588,7 @@
         <v>2016</v>
       </c>
       <c r="C148" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D148">
         <v>7.0000000000000007E-2</v>
@@ -4602,7 +4602,7 @@
         <v>2016</v>
       </c>
       <c r="C149" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D149">
         <v>0.04</v>
@@ -4616,7 +4616,7 @@
         <v>2016</v>
       </c>
       <c r="C150" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D150">
         <v>0</v>
@@ -4630,7 +4630,7 @@
         <v>2016</v>
       </c>
       <c r="C151" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D151">
         <v>10.51</v>
@@ -4638,13 +4638,13 @@
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B152">
         <v>2016</v>
       </c>
       <c r="C152" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D152">
         <v>0</v>
@@ -4658,7 +4658,7 @@
         <v>2016</v>
       </c>
       <c r="C153" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D153">
         <v>0.01</v>
@@ -4666,13 +4666,13 @@
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B154">
         <v>2016</v>
       </c>
       <c r="C154" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D154">
         <v>0.59</v>
@@ -4680,13 +4680,13 @@
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B155">
         <v>2017</v>
       </c>
       <c r="C155" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D155">
         <v>1.1000000000000001</v>
@@ -4700,7 +4700,7 @@
         <v>2017</v>
       </c>
       <c r="C156" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D156">
         <v>0.02</v>
@@ -4714,7 +4714,7 @@
         <v>2017</v>
       </c>
       <c r="C157" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D157">
         <v>0.06</v>
@@ -4728,7 +4728,7 @@
         <v>2017</v>
       </c>
       <c r="C158" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D158">
         <v>0.03</v>
@@ -4742,7 +4742,7 @@
         <v>2017</v>
       </c>
       <c r="C159" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D159">
         <v>0</v>
@@ -4756,7 +4756,7 @@
         <v>2017</v>
       </c>
       <c r="C160" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D160">
         <v>11.22</v>
@@ -4764,13 +4764,13 @@
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B161">
         <v>2017</v>
       </c>
       <c r="C161" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D161">
         <v>0</v>
@@ -4784,7 +4784,7 @@
         <v>2017</v>
       </c>
       <c r="C162" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D162">
         <v>0.01</v>
@@ -4792,13 +4792,13 @@
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B163">
         <v>2017</v>
       </c>
       <c r="C163" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D163">
         <v>0.72</v>
@@ -4806,13 +4806,13 @@
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B164">
         <v>2018</v>
       </c>
       <c r="C164" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D164">
         <v>1.31</v>
@@ -4826,7 +4826,7 @@
         <v>2018</v>
       </c>
       <c r="C165" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D165">
         <v>0</v>
@@ -4840,7 +4840,7 @@
         <v>2018</v>
       </c>
       <c r="C166" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D166">
         <v>0.06</v>
@@ -4854,7 +4854,7 @@
         <v>2018</v>
       </c>
       <c r="C167" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D167">
         <v>0.01</v>
@@ -4868,7 +4868,7 @@
         <v>2018</v>
       </c>
       <c r="C168" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D168">
         <v>0</v>
@@ -4882,7 +4882,7 @@
         <v>2018</v>
       </c>
       <c r="C169" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D169">
         <v>10.32</v>
@@ -4890,13 +4890,13 @@
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B170">
         <v>2018</v>
       </c>
       <c r="C170" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D170">
         <v>0</v>
@@ -4910,7 +4910,7 @@
         <v>2018</v>
       </c>
       <c r="C171" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D171">
         <v>0.03</v>
@@ -4918,13 +4918,13 @@
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B172">
         <v>2018</v>
       </c>
       <c r="C172" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D172">
         <v>0.64</v>
@@ -4932,13 +4932,13 @@
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B173">
         <v>2019</v>
       </c>
       <c r="C173" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D173">
         <v>1.36</v>
@@ -4952,7 +4952,7 @@
         <v>2019</v>
       </c>
       <c r="C174" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D174">
         <v>0</v>
@@ -4966,7 +4966,7 @@
         <v>2019</v>
       </c>
       <c r="C175" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D175">
         <v>0.04</v>
@@ -4980,7 +4980,7 @@
         <v>2019</v>
       </c>
       <c r="C176" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D176">
         <v>0.02</v>
@@ -4994,7 +4994,7 @@
         <v>2019</v>
       </c>
       <c r="C177" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D177">
         <v>0</v>
@@ -5008,7 +5008,7 @@
         <v>2019</v>
       </c>
       <c r="C178" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D178">
         <v>5.43</v>
@@ -5016,13 +5016,13 @@
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B179">
         <v>2019</v>
       </c>
       <c r="C179" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D179">
         <v>0</v>
@@ -5036,7 +5036,7 @@
         <v>2019</v>
       </c>
       <c r="C180" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D180">
         <v>7.0000000000000007E-2</v>
@@ -5044,13 +5044,13 @@
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B181">
         <v>2019</v>
       </c>
       <c r="C181" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D181">
         <v>0.69</v>
@@ -5058,13 +5058,13 @@
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B182">
         <v>2020</v>
       </c>
       <c r="C182" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D182">
         <v>1.85</v>
@@ -5078,7 +5078,7 @@
         <v>2020</v>
       </c>
       <c r="C183" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D183">
         <v>0</v>
@@ -5092,7 +5092,7 @@
         <v>2020</v>
       </c>
       <c r="C184" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D184">
         <v>0.03</v>
@@ -5106,7 +5106,7 @@
         <v>2020</v>
       </c>
       <c r="C185" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D185">
         <v>0.03</v>
@@ -5120,7 +5120,7 @@
         <v>2020</v>
       </c>
       <c r="C186" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D186">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>2020</v>
       </c>
       <c r="C187" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D187">
         <v>3.08</v>
@@ -5142,13 +5142,13 @@
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B188">
         <v>2020</v>
       </c>
       <c r="C188" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D188">
         <v>0</v>
@@ -5162,7 +5162,7 @@
         <v>2020</v>
       </c>
       <c r="C189" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D189">
         <v>0.25</v>
@@ -5170,13 +5170,13 @@
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B190">
         <v>2020</v>
       </c>
       <c r="C190" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D190">
         <v>0.84</v>
@@ -5184,13 +5184,13 @@
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B191">
         <v>2021</v>
       </c>
       <c r="C191" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D191">
         <v>1.77</v>
@@ -5204,7 +5204,7 @@
         <v>2021</v>
       </c>
       <c r="C192" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D192">
         <v>0</v>
@@ -5218,7 +5218,7 @@
         <v>2021</v>
       </c>
       <c r="C193" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D193">
         <v>0.04</v>
@@ -5232,7 +5232,7 @@
         <v>2021</v>
       </c>
       <c r="C194" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D194">
         <v>0.02</v>
@@ -5246,7 +5246,7 @@
         <v>2021</v>
       </c>
       <c r="C195" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D195">
         <v>0</v>
@@ -5260,7 +5260,7 @@
         <v>2021</v>
       </c>
       <c r="C196" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D196">
         <v>4.28</v>
@@ -5268,13 +5268,13 @@
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B197">
         <v>2021</v>
       </c>
       <c r="C197" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D197">
         <v>0</v>
@@ -5288,7 +5288,7 @@
         <v>2021</v>
       </c>
       <c r="C198" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D198">
         <v>0.35</v>
@@ -5296,13 +5296,13 @@
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B199">
         <v>2021</v>
       </c>
       <c r="C199" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D199">
         <v>0.73</v>
@@ -5310,13 +5310,13 @@
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B200">
         <v>2022</v>
       </c>
       <c r="C200" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D200">
         <v>1.57</v>
@@ -5330,7 +5330,7 @@
         <v>2022</v>
       </c>
       <c r="C201" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D201">
         <v>0</v>
@@ -5344,7 +5344,7 @@
         <v>2022</v>
       </c>
       <c r="C202" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D202">
         <v>0.06</v>
@@ -5358,7 +5358,7 @@
         <v>2022</v>
       </c>
       <c r="C203" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D203">
         <v>0.02</v>
@@ -5372,7 +5372,7 @@
         <v>2022</v>
       </c>
       <c r="C204" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D204">
         <v>0</v>
@@ -5386,7 +5386,7 @@
         <v>2022</v>
       </c>
       <c r="C205" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D205">
         <v>6.02</v>
@@ -5394,13 +5394,13 @@
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B206">
         <v>2022</v>
       </c>
       <c r="C206" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D206">
         <v>0</v>
@@ -5414,7 +5414,7 @@
         <v>2022</v>
       </c>
       <c r="C207" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D207">
         <v>0.6</v>
@@ -5422,13 +5422,13 @@
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B208">
         <v>2022</v>
       </c>
       <c r="C208" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D208">
         <v>0.63</v>
@@ -5436,13 +5436,13 @@
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B209">
         <v>2023</v>
       </c>
       <c r="C209" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D209">
         <v>1.33</v>
@@ -5456,7 +5456,7 @@
         <v>2023</v>
       </c>
       <c r="C210" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D210">
         <v>0</v>
@@ -5470,7 +5470,7 @@
         <v>2023</v>
       </c>
       <c r="C211" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D211">
         <v>0.05</v>
@@ -5484,7 +5484,7 @@
         <v>2023</v>
       </c>
       <c r="C212" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D212">
         <v>0.02</v>
@@ -5498,7 +5498,7 @@
         <v>2023</v>
       </c>
       <c r="C213" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D213">
         <v>0</v>
@@ -5512,7 +5512,7 @@
         <v>2023</v>
       </c>
       <c r="C214" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D214">
         <v>3.56</v>
@@ -5520,13 +5520,13 @@
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B215">
         <v>2023</v>
       </c>
       <c r="C215" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D215">
         <v>0</v>
@@ -5540,7 +5540,7 @@
         <v>2023</v>
       </c>
       <c r="C216" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D216">
         <v>0.77</v>
@@ -5548,13 +5548,13 @@
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B217">
         <v>2023</v>
       </c>
       <c r="C217" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D217">
         <v>0.75</v>
@@ -5562,13 +5562,13 @@
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B218">
         <v>2000</v>
       </c>
       <c r="C218" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D218">
         <v>0</v>
@@ -5582,7 +5582,7 @@
         <v>2000</v>
       </c>
       <c r="C219" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.25">
@@ -5593,7 +5593,7 @@
         <v>2000</v>
       </c>
       <c r="C220" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D220">
         <v>0.21</v>
@@ -5607,7 +5607,7 @@
         <v>2000</v>
       </c>
       <c r="C221" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D221">
         <v>0</v>
@@ -5621,7 +5621,7 @@
         <v>2000</v>
       </c>
       <c r="C222" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.25">
@@ -5632,7 +5632,7 @@
         <v>2000</v>
       </c>
       <c r="C223" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D223">
         <v>2.8</v>
@@ -5640,13 +5640,13 @@
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B224">
         <v>2000</v>
       </c>
       <c r="C224" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D224">
         <v>0</v>
@@ -5660,7 +5660,7 @@
         <v>2000</v>
       </c>
       <c r="C225" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D225">
         <v>0</v>
@@ -5668,13 +5668,13 @@
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B226">
         <v>2000</v>
       </c>
       <c r="C226" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D226">
         <v>0</v>
@@ -5682,13 +5682,13 @@
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B227">
         <v>2001</v>
       </c>
       <c r="C227" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D227">
         <v>0</v>
@@ -5702,7 +5702,7 @@
         <v>2001</v>
       </c>
       <c r="C228" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.25">
@@ -5713,7 +5713,7 @@
         <v>2001</v>
       </c>
       <c r="C229" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D229">
         <v>0.21</v>
@@ -5727,7 +5727,7 @@
         <v>2001</v>
       </c>
       <c r="C230" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D230">
         <v>0</v>
@@ -5741,7 +5741,7 @@
         <v>2001</v>
       </c>
       <c r="C231" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.25">
@@ -5752,7 +5752,7 @@
         <v>2001</v>
       </c>
       <c r="C232" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D232">
         <v>2.44</v>
@@ -5760,13 +5760,13 @@
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B233">
         <v>2001</v>
       </c>
       <c r="C233" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D233">
         <v>0</v>
@@ -5780,7 +5780,7 @@
         <v>2001</v>
       </c>
       <c r="C234" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D234">
         <v>0</v>
@@ -5788,13 +5788,13 @@
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B235">
         <v>2001</v>
       </c>
       <c r="C235" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D235">
         <v>0</v>
@@ -5802,13 +5802,13 @@
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B236">
         <v>2002</v>
       </c>
       <c r="C236" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D236">
         <v>0.01</v>
@@ -5822,7 +5822,7 @@
         <v>2002</v>
       </c>
       <c r="C237" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.25">
@@ -5833,7 +5833,7 @@
         <v>2002</v>
       </c>
       <c r="C238" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D238">
         <v>0.21</v>
@@ -5847,7 +5847,7 @@
         <v>2002</v>
       </c>
       <c r="C239" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D239">
         <v>0</v>
@@ -5861,7 +5861,7 @@
         <v>2002</v>
       </c>
       <c r="C240" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.25">
@@ -5872,7 +5872,7 @@
         <v>2002</v>
       </c>
       <c r="C241" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D241">
         <v>2.4</v>
@@ -5880,13 +5880,13 @@
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B242">
         <v>2002</v>
       </c>
       <c r="C242" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D242">
         <v>0</v>
@@ -5900,7 +5900,7 @@
         <v>2002</v>
       </c>
       <c r="C243" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D243">
         <v>0</v>
@@ -5908,13 +5908,13 @@
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B244">
         <v>2002</v>
       </c>
       <c r="C244" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D244">
         <v>0</v>
@@ -5922,13 +5922,13 @@
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B245">
         <v>2003</v>
       </c>
       <c r="C245" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D245">
         <v>0.01</v>
@@ -5942,7 +5942,7 @@
         <v>2003</v>
       </c>
       <c r="C246" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.25">
@@ -5953,7 +5953,7 @@
         <v>2003</v>
       </c>
       <c r="C247" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D247">
         <v>0.21</v>
@@ -5967,7 +5967,7 @@
         <v>2003</v>
       </c>
       <c r="C248" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D248">
         <v>0</v>
@@ -5981,7 +5981,7 @@
         <v>2003</v>
       </c>
       <c r="C249" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.25">
@@ -5992,7 +5992,7 @@
         <v>2003</v>
       </c>
       <c r="C250" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D250">
         <v>2.4</v>
@@ -6000,13 +6000,13 @@
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B251">
         <v>2003</v>
       </c>
       <c r="C251" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D251">
         <v>0</v>
@@ -6020,7 +6020,7 @@
         <v>2003</v>
       </c>
       <c r="C252" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D252">
         <v>0</v>
@@ -6028,13 +6028,13 @@
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B253">
         <v>2003</v>
       </c>
       <c r="C253" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D253">
         <v>0</v>
@@ -6042,13 +6042,13 @@
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B254">
         <v>2004</v>
       </c>
       <c r="C254" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D254">
         <v>0.01</v>
@@ -6062,7 +6062,7 @@
         <v>2004</v>
       </c>
       <c r="C255" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.25">
@@ -6073,7 +6073,7 @@
         <v>2004</v>
       </c>
       <c r="C256" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D256">
         <v>0.21</v>
@@ -6087,7 +6087,7 @@
         <v>2004</v>
       </c>
       <c r="C257" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D257">
         <v>0</v>
@@ -6101,7 +6101,7 @@
         <v>2004</v>
       </c>
       <c r="C258" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.25">
@@ -6112,7 +6112,7 @@
         <v>2004</v>
       </c>
       <c r="C259" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D259">
         <v>2.67</v>
@@ -6120,13 +6120,13 @@
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B260">
         <v>2004</v>
       </c>
       <c r="C260" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D260">
         <v>0</v>
@@ -6140,7 +6140,7 @@
         <v>2004</v>
       </c>
       <c r="C261" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D261">
         <v>0</v>
@@ -6148,13 +6148,13 @@
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B262">
         <v>2004</v>
       </c>
       <c r="C262" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D262">
         <v>0.01</v>
@@ -6162,13 +6162,13 @@
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B263">
         <v>2005</v>
       </c>
       <c r="C263" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D263">
         <v>0.01</v>
@@ -6182,7 +6182,7 @@
         <v>2005</v>
       </c>
       <c r="C264" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.25">
@@ -6193,7 +6193,7 @@
         <v>2005</v>
       </c>
       <c r="C265" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D265">
         <v>0.21</v>
@@ -6207,7 +6207,7 @@
         <v>2005</v>
       </c>
       <c r="C266" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D266">
         <v>0</v>
@@ -6221,7 +6221,7 @@
         <v>2005</v>
       </c>
       <c r="C267" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
@@ -6232,7 +6232,7 @@
         <v>2005</v>
       </c>
       <c r="C268" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D268">
         <v>2.5099999999999998</v>
@@ -6240,13 +6240,13 @@
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B269">
         <v>2005</v>
       </c>
       <c r="C269" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D269">
         <v>0</v>
@@ -6260,7 +6260,7 @@
         <v>2005</v>
       </c>
       <c r="C270" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D270">
         <v>0</v>
@@ -6268,13 +6268,13 @@
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B271">
         <v>2005</v>
       </c>
       <c r="C271" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D271">
         <v>0.03</v>
@@ -6282,13 +6282,13 @@
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B272">
         <v>2006</v>
       </c>
       <c r="C272" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D272">
         <v>0.01</v>
@@ -6302,7 +6302,7 @@
         <v>2006</v>
       </c>
       <c r="C273" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
@@ -6313,7 +6313,7 @@
         <v>2006</v>
       </c>
       <c r="C274" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D274">
         <v>0.21</v>
@@ -6327,7 +6327,7 @@
         <v>2006</v>
       </c>
       <c r="C275" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D275">
         <v>0</v>
@@ -6341,7 +6341,7 @@
         <v>2006</v>
       </c>
       <c r="C276" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
@@ -6352,7 +6352,7 @@
         <v>2006</v>
       </c>
       <c r="C277" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D277">
         <v>2.5099999999999998</v>
@@ -6360,13 +6360,13 @@
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B278">
         <v>2006</v>
       </c>
       <c r="C278" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D278">
         <v>0</v>
@@ -6380,7 +6380,7 @@
         <v>2006</v>
       </c>
       <c r="C279" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D279">
         <v>0</v>
@@ -6388,13 +6388,13 @@
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B280">
         <v>2006</v>
       </c>
       <c r="C280" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D280">
         <v>0.03</v>
@@ -6402,13 +6402,13 @@
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B281">
         <v>2007</v>
       </c>
       <c r="C281" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D281">
         <v>0.01</v>
@@ -6422,7 +6422,7 @@
         <v>2007</v>
       </c>
       <c r="C282" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
@@ -6433,7 +6433,7 @@
         <v>2007</v>
       </c>
       <c r="C283" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D283">
         <v>0.21</v>
@@ -6447,7 +6447,7 @@
         <v>2007</v>
       </c>
       <c r="C284" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D284">
         <v>0</v>
@@ -6461,7 +6461,7 @@
         <v>2007</v>
       </c>
       <c r="C285" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.25">
@@ -6472,7 +6472,7 @@
         <v>2007</v>
       </c>
       <c r="C286" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D286">
         <v>2.56</v>
@@ -6480,13 +6480,13 @@
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B287">
         <v>2007</v>
       </c>
       <c r="C287" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D287">
         <v>0</v>
@@ -6500,7 +6500,7 @@
         <v>2007</v>
       </c>
       <c r="C288" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D288">
         <v>0</v>
@@ -6508,13 +6508,13 @@
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B289">
         <v>2007</v>
       </c>
       <c r="C289" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D289">
         <v>0.05</v>
@@ -6522,13 +6522,13 @@
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B290">
         <v>2008</v>
       </c>
       <c r="C290" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D290">
         <v>0.01</v>
@@ -6542,7 +6542,7 @@
         <v>2008</v>
       </c>
       <c r="C291" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.25">
@@ -6553,7 +6553,7 @@
         <v>2008</v>
       </c>
       <c r="C292" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D292">
         <v>0.21</v>
@@ -6567,7 +6567,7 @@
         <v>2008</v>
       </c>
       <c r="C293" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D293">
         <v>0</v>
@@ -6581,7 +6581,7 @@
         <v>2008</v>
       </c>
       <c r="C294" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.25">
@@ -6592,7 +6592,7 @@
         <v>2008</v>
       </c>
       <c r="C295" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D295">
         <v>2.6</v>
@@ -6600,13 +6600,13 @@
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B296">
         <v>2008</v>
       </c>
       <c r="C296" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D296">
         <v>0</v>
@@ -6620,7 +6620,7 @@
         <v>2008</v>
       </c>
       <c r="C297" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D297">
         <v>0</v>
@@ -6628,13 +6628,13 @@
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B298">
         <v>2008</v>
       </c>
       <c r="C298" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D298">
         <v>0.08</v>
@@ -6642,13 +6642,13 @@
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B299">
         <v>2009</v>
       </c>
       <c r="C299" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D299">
         <v>0.06</v>
@@ -6662,7 +6662,7 @@
         <v>2009</v>
       </c>
       <c r="C300" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.25">
@@ -6673,7 +6673,7 @@
         <v>2009</v>
       </c>
       <c r="C301" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D301">
         <v>0.21</v>
@@ -6687,7 +6687,7 @@
         <v>2009</v>
       </c>
       <c r="C302" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D302">
         <v>0.01</v>
@@ -6701,7 +6701,7 @@
         <v>2009</v>
       </c>
       <c r="C303" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.25">
@@ -6712,7 +6712,7 @@
         <v>2009</v>
       </c>
       <c r="C304" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D304">
         <v>2.4900000000000002</v>
@@ -6720,13 +6720,13 @@
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B305">
         <v>2009</v>
       </c>
       <c r="C305" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D305">
         <v>0</v>
@@ -6740,7 +6740,7 @@
         <v>2009</v>
       </c>
       <c r="C306" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D306">
         <v>0</v>
@@ -6748,13 +6748,13 @@
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B307">
         <v>2009</v>
       </c>
       <c r="C307" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D307">
         <v>0.1</v>
@@ -6762,13 +6762,13 @@
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B308">
         <v>2010</v>
       </c>
       <c r="C308" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D308">
         <v>0.14000000000000001</v>
@@ -6782,7 +6782,7 @@
         <v>2010</v>
       </c>
       <c r="C309" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.25">
@@ -6793,7 +6793,7 @@
         <v>2010</v>
       </c>
       <c r="C310" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D310">
         <v>0.21</v>
@@ -6807,7 +6807,7 @@
         <v>2010</v>
       </c>
       <c r="C311" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D311">
         <v>0.01</v>
@@ -6821,7 +6821,7 @@
         <v>2010</v>
       </c>
       <c r="C312" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.25">
@@ -6832,7 +6832,7 @@
         <v>2010</v>
       </c>
       <c r="C313" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D313">
         <v>2.4900000000000002</v>
@@ -6840,13 +6840,13 @@
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B314">
         <v>2010</v>
       </c>
       <c r="C314" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D314">
         <v>0</v>
@@ -6860,7 +6860,7 @@
         <v>2010</v>
       </c>
       <c r="C315" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D315">
         <v>0</v>
@@ -6868,13 +6868,13 @@
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B316">
         <v>2010</v>
       </c>
       <c r="C316" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D316">
         <v>0.11</v>
@@ -6882,13 +6882,13 @@
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B317">
         <v>2011</v>
       </c>
       <c r="C317" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D317">
         <v>0.15</v>
@@ -6902,7 +6902,7 @@
         <v>2011</v>
       </c>
       <c r="C318" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.25">
@@ -6913,7 +6913,7 @@
         <v>2011</v>
       </c>
       <c r="C319" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D319">
         <v>0.21</v>
@@ -6927,7 +6927,7 @@
         <v>2011</v>
       </c>
       <c r="C320" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D320">
         <v>0</v>
@@ -6941,7 +6941,7 @@
         <v>2011</v>
       </c>
       <c r="C321" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.25">
@@ -6952,7 +6952,7 @@
         <v>2011</v>
       </c>
       <c r="C322" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D322">
         <v>2.4900000000000002</v>
@@ -6960,13 +6960,13 @@
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B323">
         <v>2011</v>
       </c>
       <c r="C323" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D323">
         <v>0</v>
@@ -6980,7 +6980,7 @@
         <v>2011</v>
       </c>
       <c r="C324" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D324">
         <v>0</v>
@@ -6988,13 +6988,13 @@
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B325">
         <v>2011</v>
       </c>
       <c r="C325" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D325">
         <v>0.18</v>
@@ -7002,13 +7002,13 @@
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B326">
         <v>2012</v>
       </c>
       <c r="C326" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D326">
         <v>0.17</v>
@@ -7022,7 +7022,7 @@
         <v>2012</v>
       </c>
       <c r="C327" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.25">
@@ -7033,7 +7033,7 @@
         <v>2012</v>
       </c>
       <c r="C328" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D328">
         <v>0.21</v>
@@ -7047,7 +7047,7 @@
         <v>2012</v>
       </c>
       <c r="C329" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D329">
         <v>0.01</v>
@@ -7061,7 +7061,7 @@
         <v>2012</v>
       </c>
       <c r="C330" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.25">
@@ -7072,7 +7072,7 @@
         <v>2012</v>
       </c>
       <c r="C331" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D331">
         <v>2.48</v>
@@ -7080,13 +7080,13 @@
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B332">
         <v>2012</v>
       </c>
       <c r="C332" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D332">
         <v>0</v>
@@ -7100,7 +7100,7 @@
         <v>2012</v>
       </c>
       <c r="C333" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D333">
         <v>0</v>
@@ -7108,13 +7108,13 @@
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B334">
         <v>2012</v>
       </c>
       <c r="C334" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D334">
         <v>0.27</v>
@@ -7122,13 +7122,13 @@
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B335">
         <v>2013</v>
       </c>
       <c r="C335" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D335">
         <v>0.16</v>
@@ -7142,7 +7142,7 @@
         <v>2013</v>
       </c>
       <c r="C336" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.25">
@@ -7153,7 +7153,7 @@
         <v>2013</v>
       </c>
       <c r="C337" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D337">
         <v>0.42</v>
@@ -7167,7 +7167,7 @@
         <v>2013</v>
       </c>
       <c r="C338" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D338">
         <v>0.01</v>
@@ -7181,7 +7181,7 @@
         <v>2013</v>
       </c>
       <c r="C339" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.25">
@@ -7192,7 +7192,7 @@
         <v>2013</v>
       </c>
       <c r="C340" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D340">
         <v>2.39</v>
@@ -7200,13 +7200,13 @@
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B341">
         <v>2013</v>
       </c>
       <c r="C341" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D341">
         <v>0.1</v>
@@ -7220,7 +7220,7 @@
         <v>2013</v>
       </c>
       <c r="C342" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D342">
         <v>0</v>
@@ -7228,13 +7228,13 @@
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B343">
         <v>2013</v>
       </c>
       <c r="C343" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D343">
         <v>0.25</v>
@@ -7242,13 +7242,13 @@
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B344">
         <v>2014</v>
       </c>
       <c r="C344" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D344">
         <v>0.17</v>
@@ -7262,7 +7262,7 @@
         <v>2014</v>
       </c>
       <c r="C345" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.25">
@@ -7273,7 +7273,7 @@
         <v>2014</v>
       </c>
       <c r="C346" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D346">
         <v>0.42</v>
@@ -7287,7 +7287,7 @@
         <v>2014</v>
       </c>
       <c r="C347" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D347">
         <v>0</v>
@@ -7301,7 +7301,7 @@
         <v>2014</v>
       </c>
       <c r="C348" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.25">
@@ -7312,7 +7312,7 @@
         <v>2014</v>
       </c>
       <c r="C349" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D349">
         <v>2.4700000000000002</v>
@@ -7320,13 +7320,13 @@
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B350">
         <v>2014</v>
       </c>
       <c r="C350" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D350">
         <v>0.1</v>
@@ -7340,7 +7340,7 @@
         <v>2014</v>
       </c>
       <c r="C351" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D351">
         <v>0</v>
@@ -7348,13 +7348,13 @@
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B352">
         <v>2014</v>
       </c>
       <c r="C352" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D352">
         <v>0.28000000000000003</v>
@@ -7362,13 +7362,13 @@
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B353">
         <v>2015</v>
       </c>
       <c r="C353" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D353">
         <v>0.18</v>
@@ -7382,7 +7382,7 @@
         <v>2015</v>
       </c>
       <c r="C354" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.25">
@@ -7393,7 +7393,7 @@
         <v>2015</v>
       </c>
       <c r="C355" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D355">
         <v>0.42</v>
@@ -7407,7 +7407,7 @@
         <v>2015</v>
       </c>
       <c r="C356" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D356">
         <v>0.01</v>
@@ -7421,7 +7421,7 @@
         <v>2015</v>
       </c>
       <c r="C357" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.25">
@@ -7432,7 +7432,7 @@
         <v>2015</v>
       </c>
       <c r="C358" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D358">
         <v>2.27</v>
@@ -7440,13 +7440,13 @@
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B359">
         <v>2015</v>
       </c>
       <c r="C359" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D359">
         <v>0.1</v>
@@ -7460,7 +7460,7 @@
         <v>2015</v>
       </c>
       <c r="C360" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D360">
         <v>0.01</v>
@@ -7468,13 +7468,13 @@
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B361">
         <v>2015</v>
       </c>
       <c r="C361" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D361">
         <v>0.3</v>
@@ -7482,13 +7482,13 @@
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B362">
         <v>2016</v>
       </c>
       <c r="C362" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D362">
         <v>0.18</v>
@@ -7502,7 +7502,7 @@
         <v>2016</v>
       </c>
       <c r="C363" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.25">
@@ -7513,7 +7513,7 @@
         <v>2016</v>
       </c>
       <c r="C364" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D364">
         <v>0.42</v>
@@ -7527,7 +7527,7 @@
         <v>2016</v>
       </c>
       <c r="C365" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D365">
         <v>0.01</v>
@@ -7541,7 +7541,7 @@
         <v>2016</v>
       </c>
       <c r="C366" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.25">
@@ -7552,7 +7552,7 @@
         <v>2016</v>
       </c>
       <c r="C367" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D367">
         <v>1.97</v>
@@ -7560,13 +7560,13 @@
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B368">
         <v>2016</v>
       </c>
       <c r="C368" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D368">
         <v>0.1</v>
@@ -7580,7 +7580,7 @@
         <v>2016</v>
       </c>
       <c r="C369" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D369">
         <v>0.01</v>
@@ -7588,13 +7588,13 @@
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B370">
         <v>2016</v>
       </c>
       <c r="C370" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D370">
         <v>0.31</v>
@@ -7602,13 +7602,13 @@
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B371">
         <v>2017</v>
       </c>
       <c r="C371" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D371">
         <v>0.18</v>
@@ -7622,7 +7622,7 @@
         <v>2017</v>
       </c>
       <c r="C372" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.25">
@@ -7633,7 +7633,7 @@
         <v>2017</v>
       </c>
       <c r="C373" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D373">
         <v>0.42</v>
@@ -7647,7 +7647,7 @@
         <v>2017</v>
       </c>
       <c r="C374" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D374">
         <v>0.01</v>
@@ -7661,7 +7661,7 @@
         <v>2017</v>
       </c>
       <c r="C375" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.25">
@@ -7672,7 +7672,7 @@
         <v>2017</v>
       </c>
       <c r="C376" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D376">
         <v>1.93</v>
@@ -7680,13 +7680,13 @@
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B377">
         <v>2017</v>
       </c>
       <c r="C377" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D377">
         <v>0.1</v>
@@ -7700,7 +7700,7 @@
         <v>2017</v>
       </c>
       <c r="C378" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D378">
         <v>0.01</v>
@@ -7708,13 +7708,13 @@
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B379">
         <v>2017</v>
       </c>
       <c r="C379" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D379">
         <v>0.31</v>
@@ -7722,13 +7722,13 @@
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B380">
         <v>2018</v>
       </c>
       <c r="C380" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D380">
         <v>0.17</v>
@@ -7742,7 +7742,7 @@
         <v>2018</v>
       </c>
       <c r="C381" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.25">
@@ -7753,7 +7753,7 @@
         <v>2018</v>
       </c>
       <c r="C382" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D382">
         <v>0.42</v>
@@ -7767,7 +7767,7 @@
         <v>2018</v>
       </c>
       <c r="C383" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D383">
         <v>0.01</v>
@@ -7781,7 +7781,7 @@
         <v>2018</v>
       </c>
       <c r="C384" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.25">
@@ -7792,7 +7792,7 @@
         <v>2018</v>
       </c>
       <c r="C385" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D385">
         <v>2.21</v>
@@ -7800,13 +7800,13 @@
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B386">
         <v>2018</v>
       </c>
       <c r="C386" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D386">
         <v>0.09</v>
@@ -7820,7 +7820,7 @@
         <v>2018</v>
       </c>
       <c r="C387" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D387">
         <v>0.03</v>
@@ -7828,13 +7828,13 @@
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B388">
         <v>2018</v>
       </c>
       <c r="C388" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D388">
         <v>0.31</v>
@@ -7842,13 +7842,13 @@
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B389">
         <v>2019</v>
       </c>
       <c r="C389" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D389">
         <v>0.19</v>
@@ -7862,7 +7862,7 @@
         <v>2019</v>
       </c>
       <c r="C390" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.25">
@@ -7873,7 +7873,7 @@
         <v>2019</v>
       </c>
       <c r="C391" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D391">
         <v>0.42</v>
@@ -7887,7 +7887,7 @@
         <v>2019</v>
       </c>
       <c r="C392" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D392">
         <v>0.01</v>
@@ -7901,7 +7901,7 @@
         <v>2019</v>
       </c>
       <c r="C393" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.25">
@@ -7912,7 +7912,7 @@
         <v>2019</v>
       </c>
       <c r="C394" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D394">
         <v>2.0299999999999998</v>
@@ -7920,13 +7920,13 @@
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B395">
         <v>2019</v>
       </c>
       <c r="C395" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D395">
         <v>0.09</v>
@@ -7940,7 +7940,7 @@
         <v>2019</v>
       </c>
       <c r="C396" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D396">
         <v>0.12</v>
@@ -7948,13 +7948,13 @@
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B397">
         <v>2019</v>
       </c>
       <c r="C397" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D397">
         <v>0.32</v>
@@ -7962,13 +7962,13 @@
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B398">
         <v>2020</v>
       </c>
       <c r="C398" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D398">
         <v>0.21</v>
@@ -7982,7 +7982,7 @@
         <v>2020</v>
       </c>
       <c r="C399" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.25">
@@ -7993,7 +7993,7 @@
         <v>2020</v>
       </c>
       <c r="C400" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D400">
         <v>0.42</v>
@@ -8007,7 +8007,7 @@
         <v>2020</v>
       </c>
       <c r="C401" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D401">
         <v>0.01</v>
@@ -8021,7 +8021,7 @@
         <v>2020</v>
       </c>
       <c r="C402" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.25">
@@ -8032,7 +8032,7 @@
         <v>2020</v>
       </c>
       <c r="C403" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D403">
         <v>1.91</v>
@@ -8040,13 +8040,13 @@
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B404">
         <v>2020</v>
       </c>
       <c r="C404" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D404">
         <v>0.09</v>
@@ -8060,7 +8060,7 @@
         <v>2020</v>
       </c>
       <c r="C405" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D405">
         <v>0.21</v>
@@ -8068,13 +8068,13 @@
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B406">
         <v>2020</v>
       </c>
       <c r="C406" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D406">
         <v>0.32</v>
@@ -8082,13 +8082,13 @@
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B407">
         <v>2021</v>
       </c>
       <c r="C407" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D407">
         <v>0.21</v>
@@ -8102,7 +8102,7 @@
         <v>2021</v>
       </c>
       <c r="C408" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.25">
@@ -8113,7 +8113,7 @@
         <v>2021</v>
       </c>
       <c r="C409" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D409">
         <v>0.42</v>
@@ -8127,7 +8127,7 @@
         <v>2021</v>
       </c>
       <c r="C410" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D410">
         <v>0.01</v>
@@ -8141,7 +8141,7 @@
         <v>2021</v>
       </c>
       <c r="C411" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.25">
@@ -8152,7 +8152,7 @@
         <v>2021</v>
       </c>
       <c r="C412" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D412">
         <v>1.4</v>
@@ -8160,13 +8160,13 @@
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B413">
         <v>2021</v>
       </c>
       <c r="C413" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D413">
         <v>0.09</v>
@@ -8180,7 +8180,7 @@
         <v>2021</v>
       </c>
       <c r="C414" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D414">
         <v>0.39</v>
@@ -8188,13 +8188,13 @@
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B415">
         <v>2021</v>
       </c>
       <c r="C415" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D415">
         <v>0.31</v>
@@ -8202,13 +8202,13 @@
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B416">
         <v>2022</v>
       </c>
       <c r="C416" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D416">
         <v>0.21</v>
@@ -8222,7 +8222,7 @@
         <v>2022</v>
       </c>
       <c r="C417" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.25">
@@ -8233,7 +8233,7 @@
         <v>2022</v>
       </c>
       <c r="C418" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D418">
         <v>0.42</v>
@@ -8247,7 +8247,7 @@
         <v>2022</v>
       </c>
       <c r="C419" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D419">
         <v>0.01</v>
@@ -8261,7 +8261,7 @@
         <v>2022</v>
       </c>
       <c r="C420" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.25">
@@ -8272,7 +8272,7 @@
         <v>2022</v>
       </c>
       <c r="C421" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D421">
         <v>1.4</v>
@@ -8280,13 +8280,13 @@
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B422">
         <v>2022</v>
       </c>
       <c r="C422" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D422">
         <v>0.09</v>
@@ -8300,7 +8300,7 @@
         <v>2022</v>
       </c>
       <c r="C423" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D423">
         <v>0.52</v>
@@ -8308,13 +8308,13 @@
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B424">
         <v>2022</v>
       </c>
       <c r="C424" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D424">
         <v>0.32</v>
@@ -8322,13 +8322,13 @@
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B425">
         <v>2023</v>
       </c>
       <c r="C425" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D425">
         <v>0.21</v>
@@ -8342,7 +8342,7 @@
         <v>2023</v>
       </c>
       <c r="C426" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.25">
@@ -8353,7 +8353,7 @@
         <v>2023</v>
       </c>
       <c r="C427" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D427">
         <v>0.42</v>
@@ -8367,7 +8367,7 @@
         <v>2023</v>
       </c>
       <c r="C428" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D428">
         <v>0.01</v>
@@ -8381,7 +8381,7 @@
         <v>2023</v>
       </c>
       <c r="C429" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.25">
@@ -8392,7 +8392,7 @@
         <v>2023</v>
       </c>
       <c r="C430" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D430">
         <v>1.31</v>
@@ -8400,13 +8400,13 @@
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B431">
         <v>2023</v>
       </c>
       <c r="C431" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D431">
         <v>0.09</v>
@@ -8420,7 +8420,7 @@
         <v>2023</v>
       </c>
       <c r="C432" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D432">
         <v>0.69</v>
@@ -8428,13 +8428,13 @@
     </row>
     <row r="433" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B433">
         <v>2023</v>
       </c>
       <c r="C433" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D433">
         <v>0.41</v>
@@ -8442,13 +8442,13 @@
     </row>
     <row r="434" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B434">
         <v>2000</v>
       </c>
       <c r="C434" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D434">
         <v>0</v>
@@ -8462,7 +8462,7 @@
         <v>2000</v>
       </c>
       <c r="C435" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D435">
         <v>0</v>
@@ -8476,7 +8476,7 @@
         <v>2000</v>
       </c>
       <c r="C436" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D436">
         <v>0.2</v>
@@ -8490,7 +8490,7 @@
         <v>2000</v>
       </c>
       <c r="C437" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D437">
         <v>0</v>
@@ -8504,7 +8504,7 @@
         <v>2000</v>
       </c>
       <c r="C438" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D438">
         <v>0</v>
@@ -8518,7 +8518,7 @@
         <v>2000</v>
       </c>
       <c r="C439" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D439">
         <v>5.2</v>
@@ -8526,13 +8526,13 @@
     </row>
     <row r="440" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B440">
         <v>2000</v>
       </c>
       <c r="C440" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D440">
         <v>0</v>
@@ -8546,7 +8546,7 @@
         <v>2000</v>
       </c>
       <c r="C441" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D441">
         <v>0</v>
@@ -8554,13 +8554,13 @@
     </row>
     <row r="442" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B442">
         <v>2000</v>
       </c>
       <c r="C442" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D442">
         <v>0</v>
@@ -8568,13 +8568,13 @@
     </row>
     <row r="443" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B443">
         <v>2001</v>
       </c>
       <c r="C443" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D443">
         <v>0</v>
@@ -8588,7 +8588,7 @@
         <v>2001</v>
       </c>
       <c r="C444" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D444">
         <v>0</v>
@@ -8602,7 +8602,7 @@
         <v>2001</v>
       </c>
       <c r="C445" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D445">
         <v>0.2</v>
@@ -8616,7 +8616,7 @@
         <v>2001</v>
       </c>
       <c r="C446" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D446">
         <v>0</v>
@@ -8630,7 +8630,7 @@
         <v>2001</v>
       </c>
       <c r="C447" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D447">
         <v>0</v>
@@ -8644,7 +8644,7 @@
         <v>2001</v>
       </c>
       <c r="C448" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D448">
         <v>5.18</v>
@@ -8652,13 +8652,13 @@
     </row>
     <row r="449" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B449">
         <v>2001</v>
       </c>
       <c r="C449" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D449">
         <v>0</v>
@@ -8672,7 +8672,7 @@
         <v>2001</v>
       </c>
       <c r="C450" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D450">
         <v>0</v>
@@ -8680,13 +8680,13 @@
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B451">
         <v>2001</v>
       </c>
       <c r="C451" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D451">
         <v>0</v>
@@ -8694,13 +8694,13 @@
     </row>
     <row r="452" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B452">
         <v>2002</v>
       </c>
       <c r="C452" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D452">
         <v>0</v>
@@ -8714,7 +8714,7 @@
         <v>2002</v>
       </c>
       <c r="C453" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D453">
         <v>0</v>
@@ -8728,7 +8728,7 @@
         <v>2002</v>
       </c>
       <c r="C454" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D454">
         <v>0.17</v>
@@ -8742,7 +8742,7 @@
         <v>2002</v>
       </c>
       <c r="C455" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D455">
         <v>0</v>
@@ -8756,7 +8756,7 @@
         <v>2002</v>
       </c>
       <c r="C456" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D456">
         <v>0</v>
@@ -8770,7 +8770,7 @@
         <v>2002</v>
       </c>
       <c r="C457" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D457">
         <v>5.24</v>
@@ -8778,13 +8778,13 @@
     </row>
     <row r="458" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B458">
         <v>2002</v>
       </c>
       <c r="C458" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D458">
         <v>0</v>
@@ -8798,7 +8798,7 @@
         <v>2002</v>
       </c>
       <c r="C459" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D459">
         <v>0</v>
@@ -8806,13 +8806,13 @@
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B460">
         <v>2002</v>
       </c>
       <c r="C460" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D460">
         <v>0</v>
@@ -8820,13 +8820,13 @@
     </row>
     <row r="461" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B461">
         <v>2003</v>
       </c>
       <c r="C461" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D461">
         <v>0.01</v>
@@ -8840,7 +8840,7 @@
         <v>2003</v>
       </c>
       <c r="C462" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D462">
         <v>0</v>
@@ -8854,7 +8854,7 @@
         <v>2003</v>
       </c>
       <c r="C463" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D463">
         <v>0.16</v>
@@ -8868,7 +8868,7 @@
         <v>2003</v>
       </c>
       <c r="C464" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D464">
         <v>0</v>
@@ -8882,7 +8882,7 @@
         <v>2003</v>
       </c>
       <c r="C465" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D465">
         <v>0</v>
@@ -8896,7 +8896,7 @@
         <v>2003</v>
       </c>
       <c r="C466" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D466">
         <v>6.32</v>
@@ -8904,13 +8904,13 @@
     </row>
     <row r="467" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B467">
         <v>2003</v>
       </c>
       <c r="C467" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D467">
         <v>0</v>
@@ -8924,7 +8924,7 @@
         <v>2003</v>
       </c>
       <c r="C468" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D468">
         <v>0</v>
@@ -8932,13 +8932,13 @@
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B469">
         <v>2003</v>
       </c>
       <c r="C469" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D469">
         <v>0</v>
@@ -8946,13 +8946,13 @@
     </row>
     <row r="470" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B470">
         <v>2004</v>
       </c>
       <c r="C470" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D470">
         <v>0.01</v>
@@ -8966,7 +8966,7 @@
         <v>2004</v>
       </c>
       <c r="C471" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D471">
         <v>0</v>
@@ -8980,7 +8980,7 @@
         <v>2004</v>
       </c>
       <c r="C472" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D472">
         <v>0.16</v>
@@ -8994,7 +8994,7 @@
         <v>2004</v>
       </c>
       <c r="C473" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D473">
         <v>0</v>
@@ -9008,7 +9008,7 @@
         <v>2004</v>
       </c>
       <c r="C474" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D474">
         <v>0</v>
@@ -9022,7 +9022,7 @@
         <v>2004</v>
       </c>
       <c r="C475" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D475">
         <v>6.42</v>
@@ -9030,13 +9030,13 @@
     </row>
     <row r="476" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B476">
         <v>2004</v>
       </c>
       <c r="C476" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D476">
         <v>0</v>
@@ -9050,7 +9050,7 @@
         <v>2004</v>
       </c>
       <c r="C477" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D477">
         <v>0</v>
@@ -9058,13 +9058,13 @@
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B478">
         <v>2004</v>
       </c>
       <c r="C478" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D478">
         <v>0</v>
@@ -9072,13 +9072,13 @@
     </row>
     <row r="479" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B479">
         <v>2005</v>
       </c>
       <c r="C479" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D479">
         <v>0.01</v>
@@ -9092,7 +9092,7 @@
         <v>2005</v>
       </c>
       <c r="C480" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D480">
         <v>0</v>
@@ -9106,7 +9106,7 @@
         <v>2005</v>
       </c>
       <c r="C481" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D481">
         <v>0.18</v>
@@ -9120,7 +9120,7 @@
         <v>2005</v>
       </c>
       <c r="C482" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D482">
         <v>0</v>
@@ -9134,7 +9134,7 @@
         <v>2005</v>
       </c>
       <c r="C483" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D483">
         <v>0</v>
@@ -9148,7 +9148,7 @@
         <v>2005</v>
       </c>
       <c r="C484" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D484">
         <v>6.28</v>
@@ -9156,13 +9156,13 @@
     </row>
     <row r="485" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B485">
         <v>2005</v>
       </c>
       <c r="C485" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D485">
         <v>0</v>
@@ -9176,7 +9176,7 @@
         <v>2005</v>
       </c>
       <c r="C486" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D486">
         <v>0</v>
@@ -9184,13 +9184,13 @@
     </row>
     <row r="487" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B487">
         <v>2005</v>
       </c>
       <c r="C487" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D487">
         <v>0</v>
@@ -9198,13 +9198,13 @@
     </row>
     <row r="488" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B488">
         <v>2006</v>
       </c>
       <c r="C488" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D488">
         <v>0.01</v>
@@ -9218,7 +9218,7 @@
         <v>2006</v>
       </c>
       <c r="C489" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D489">
         <v>0</v>
@@ -9232,7 +9232,7 @@
         <v>2006</v>
       </c>
       <c r="C490" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D490">
         <v>0.18</v>
@@ -9246,7 +9246,7 @@
         <v>2006</v>
       </c>
       <c r="C491" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D491">
         <v>0</v>
@@ -9260,7 +9260,7 @@
         <v>2006</v>
       </c>
       <c r="C492" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D492">
         <v>0</v>
@@ -9274,7 +9274,7 @@
         <v>2006</v>
       </c>
       <c r="C493" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D493">
         <v>5.96</v>
@@ -9282,13 +9282,13 @@
     </row>
     <row r="494" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B494">
         <v>2006</v>
       </c>
       <c r="C494" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D494">
         <v>0</v>
@@ -9302,7 +9302,7 @@
         <v>2006</v>
       </c>
       <c r="C495" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D495">
         <v>0</v>
@@ -9310,13 +9310,13 @@
     </row>
     <row r="496" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B496">
         <v>2006</v>
       </c>
       <c r="C496" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D496">
         <v>0</v>
@@ -9324,13 +9324,13 @@
     </row>
     <row r="497" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B497">
         <v>2007</v>
       </c>
       <c r="C497" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D497">
         <v>0.01</v>
@@ -9344,7 +9344,7 @@
         <v>2007</v>
       </c>
       <c r="C498" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D498">
         <v>0</v>
@@ -9358,7 +9358,7 @@
         <v>2007</v>
       </c>
       <c r="C499" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D499">
         <v>0.11</v>
@@ -9372,7 +9372,7 @@
         <v>2007</v>
       </c>
       <c r="C500" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D500">
         <v>0</v>
@@ -9386,7 +9386,7 @@
         <v>2007</v>
       </c>
       <c r="C501" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D501">
         <v>0</v>
@@ -9400,7 +9400,7 @@
         <v>2007</v>
       </c>
       <c r="C502" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D502">
         <v>7.7</v>
@@ -9408,13 +9408,13 @@
     </row>
     <row r="503" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B503">
         <v>2007</v>
       </c>
       <c r="C503" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D503">
         <v>0</v>
@@ -9428,7 +9428,7 @@
         <v>2007</v>
       </c>
       <c r="C504" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D504">
         <v>0</v>
@@ -9436,13 +9436,13 @@
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B505">
         <v>2007</v>
       </c>
       <c r="C505" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D505">
         <v>0</v>
@@ -9450,13 +9450,13 @@
     </row>
     <row r="506" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B506">
         <v>2008</v>
       </c>
       <c r="C506" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D506">
         <v>0.01</v>
@@ -9470,7 +9470,7 @@
         <v>2008</v>
       </c>
       <c r="C507" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D507">
         <v>0</v>
@@ -9484,7 +9484,7 @@
         <v>2008</v>
       </c>
       <c r="C508" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D508">
         <v>0.14000000000000001</v>
@@ -9498,7 +9498,7 @@
         <v>2008</v>
       </c>
       <c r="C509" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D509">
         <v>0</v>
@@ -9512,7 +9512,7 @@
         <v>2008</v>
       </c>
       <c r="C510" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D510">
         <v>0</v>
@@ -9526,7 +9526,7 @@
         <v>2008</v>
       </c>
       <c r="C511" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D511">
         <v>6.55</v>
@@ -9534,13 +9534,13 @@
     </row>
     <row r="512" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B512">
         <v>2008</v>
       </c>
       <c r="C512" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D512">
         <v>0</v>
@@ -9554,7 +9554,7 @@
         <v>2008</v>
       </c>
       <c r="C513" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D513">
         <v>0</v>
@@ -9562,13 +9562,13 @@
     </row>
     <row r="514" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B514">
         <v>2008</v>
       </c>
       <c r="C514" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D514">
         <v>0</v>
@@ -9576,13 +9576,13 @@
     </row>
     <row r="515" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B515">
         <v>2009</v>
       </c>
       <c r="C515" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D515">
         <v>7.0000000000000007E-2</v>
@@ -9596,7 +9596,7 @@
         <v>2009</v>
       </c>
       <c r="C516" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D516">
         <v>0</v>
@@ -9610,7 +9610,7 @@
         <v>2009</v>
       </c>
       <c r="C517" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D517">
         <v>0.04</v>
@@ -9624,7 +9624,7 @@
         <v>2009</v>
       </c>
       <c r="C518" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D518">
         <v>0</v>
@@ -9638,7 +9638,7 @@
         <v>2009</v>
       </c>
       <c r="C519" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D519">
         <v>0</v>
@@ -9652,7 +9652,7 @@
         <v>2009</v>
       </c>
       <c r="C520" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D520">
         <v>5.35</v>
@@ -9660,13 +9660,13 @@
     </row>
     <row r="521" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B521">
         <v>2009</v>
       </c>
       <c r="C521" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D521">
         <v>0</v>
@@ -9680,7 +9680,7 @@
         <v>2009</v>
       </c>
       <c r="C522" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D522">
         <v>0</v>
@@ -9688,13 +9688,13 @@
     </row>
     <row r="523" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B523">
         <v>2009</v>
       </c>
       <c r="C523" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D523">
         <v>0</v>
@@ -9702,13 +9702,13 @@
     </row>
     <row r="524" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B524">
         <v>2010</v>
       </c>
       <c r="C524" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D524">
         <v>0.16</v>
@@ -9722,7 +9722,7 @@
         <v>2010</v>
       </c>
       <c r="C525" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D525">
         <v>0</v>
@@ -9736,7 +9736,7 @@
         <v>2010</v>
       </c>
       <c r="C526" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D526">
         <v>0.1</v>
@@ -9750,7 +9750,7 @@
         <v>2010</v>
       </c>
       <c r="C527" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D527">
         <v>0</v>
@@ -9764,7 +9764,7 @@
         <v>2010</v>
       </c>
       <c r="C528" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D528">
         <v>0</v>
@@ -9778,7 +9778,7 @@
         <v>2010</v>
       </c>
       <c r="C529" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D529">
         <v>7.65</v>
@@ -9786,13 +9786,13 @@
     </row>
     <row r="530" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B530">
         <v>2010</v>
       </c>
       <c r="C530" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D530">
         <v>0</v>
@@ -9806,7 +9806,7 @@
         <v>2010</v>
       </c>
       <c r="C531" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D531">
         <v>0</v>
@@ -9814,13 +9814,13 @@
     </row>
     <row r="532" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B532">
         <v>2010</v>
       </c>
       <c r="C532" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D532">
         <v>0</v>
@@ -9828,13 +9828,13 @@
     </row>
     <row r="533" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B533">
         <v>2011</v>
       </c>
       <c r="C533" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D533">
         <v>0.17</v>
@@ -9848,7 +9848,7 @@
         <v>2011</v>
       </c>
       <c r="C534" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D534">
         <v>0</v>
@@ -9862,7 +9862,7 @@
         <v>2011</v>
       </c>
       <c r="C535" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D535">
         <v>0.08</v>
@@ -9876,7 +9876,7 @@
         <v>2011</v>
       </c>
       <c r="C536" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D536">
         <v>0</v>
@@ -9890,7 +9890,7 @@
         <v>2011</v>
       </c>
       <c r="C537" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D537">
         <v>0</v>
@@ -9904,7 +9904,7 @@
         <v>2011</v>
       </c>
       <c r="C538" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D538">
         <v>7.54</v>
@@ -9912,13 +9912,13 @@
     </row>
     <row r="539" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B539">
         <v>2011</v>
       </c>
       <c r="C539" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D539">
         <v>0</v>
@@ -9932,7 +9932,7 @@
         <v>2011</v>
       </c>
       <c r="C540" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D540">
         <v>0</v>
@@ -9940,13 +9940,13 @@
     </row>
     <row r="541" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B541">
         <v>2011</v>
       </c>
       <c r="C541" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D541">
         <v>0</v>
@@ -9954,13 +9954,13 @@
     </row>
     <row r="542" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B542">
         <v>2012</v>
       </c>
       <c r="C542" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D542">
         <v>0.22</v>
@@ -9974,7 +9974,7 @@
         <v>2012</v>
       </c>
       <c r="C543" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D543">
         <v>0</v>
@@ -9988,7 +9988,7 @@
         <v>2012</v>
       </c>
       <c r="C544" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D544">
         <v>0.04</v>
@@ -10002,7 +10002,7 @@
         <v>2012</v>
       </c>
       <c r="C545" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D545">
         <v>0</v>
@@ -10016,7 +10016,7 @@
         <v>2012</v>
       </c>
       <c r="C546" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D546">
         <v>0</v>
@@ -10030,7 +10030,7 @@
         <v>2012</v>
       </c>
       <c r="C547" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D547">
         <v>6.82</v>
@@ -10038,13 +10038,13 @@
     </row>
     <row r="548" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B548">
         <v>2012</v>
       </c>
       <c r="C548" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D548">
         <v>0</v>
@@ -10058,7 +10058,7 @@
         <v>2012</v>
       </c>
       <c r="C549" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D549">
         <v>0</v>
@@ -10066,13 +10066,13 @@
     </row>
     <row r="550" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B550">
         <v>2012</v>
       </c>
       <c r="C550" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D550">
         <v>0.01</v>
@@ -10080,13 +10080,13 @@
     </row>
     <row r="551" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B551">
         <v>2013</v>
       </c>
       <c r="C551" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D551">
         <v>0.14000000000000001</v>
@@ -10100,7 +10100,7 @@
         <v>2013</v>
       </c>
       <c r="C552" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D552">
         <v>0.01</v>
@@ -10114,7 +10114,7 @@
         <v>2013</v>
       </c>
       <c r="C553" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D553">
         <v>0.03</v>
@@ -10128,7 +10128,7 @@
         <v>2013</v>
       </c>
       <c r="C554" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D554">
         <v>0</v>
@@ -10142,7 +10142,7 @@
         <v>2013</v>
       </c>
       <c r="C555" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D555">
         <v>0</v>
@@ -10156,7 +10156,7 @@
         <v>2013</v>
       </c>
       <c r="C556" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D556">
         <v>7.86</v>
@@ -10164,13 +10164,13 @@
     </row>
     <row r="557" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B557">
         <v>2013</v>
       </c>
       <c r="C557" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D557">
         <v>0</v>
@@ -10184,7 +10184,7 @@
         <v>2013</v>
       </c>
       <c r="C558" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D558">
         <v>0</v>
@@ -10192,13 +10192,13 @@
     </row>
     <row r="559" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B559">
         <v>2013</v>
       </c>
       <c r="C559" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D559">
         <v>0.01</v>
@@ -10206,13 +10206,13 @@
     </row>
     <row r="560" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B560">
         <v>2014</v>
       </c>
       <c r="C560" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D560">
         <v>0.16</v>
@@ -10226,7 +10226,7 @@
         <v>2014</v>
       </c>
       <c r="C561" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D561">
         <v>0.01</v>
@@ -10240,7 +10240,7 @@
         <v>2014</v>
       </c>
       <c r="C562" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D562">
         <v>0.02</v>
@@ -10254,7 +10254,7 @@
         <v>2014</v>
       </c>
       <c r="C563" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D563">
         <v>0</v>
@@ -10268,7 +10268,7 @@
         <v>2014</v>
       </c>
       <c r="C564" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D564">
         <v>0</v>
@@ -10282,7 +10282,7 @@
         <v>2014</v>
       </c>
       <c r="C565" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D565">
         <v>7.22</v>
@@ -10290,13 +10290,13 @@
     </row>
     <row r="566" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B566">
         <v>2014</v>
       </c>
       <c r="C566" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D566">
         <v>0</v>
@@ -10310,7 +10310,7 @@
         <v>2014</v>
       </c>
       <c r="C567" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D567">
         <v>0</v>
@@ -10318,13 +10318,13 @@
     </row>
     <row r="568" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B568">
         <v>2014</v>
       </c>
       <c r="C568" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D568">
         <v>0.01</v>
@@ -10332,13 +10332,13 @@
     </row>
     <row r="569" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B569">
         <v>2015</v>
       </c>
       <c r="C569" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D569">
         <v>0.18</v>
@@ -10352,7 +10352,7 @@
         <v>2015</v>
       </c>
       <c r="C570" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D570">
         <v>0</v>
@@ -10366,7 +10366,7 @@
         <v>2015</v>
       </c>
       <c r="C571" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D571">
         <v>0.02</v>
@@ -10380,7 +10380,7 @@
         <v>2015</v>
       </c>
       <c r="C572" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D572">
         <v>0</v>
@@ -10394,7 +10394,7 @@
         <v>2015</v>
       </c>
       <c r="C573" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D573">
         <v>0</v>
@@ -10408,7 +10408,7 @@
         <v>2015</v>
       </c>
       <c r="C574" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D574">
         <v>5.61</v>
@@ -10416,13 +10416,13 @@
     </row>
     <row r="575" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B575">
         <v>2015</v>
       </c>
       <c r="C575" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D575">
         <v>0</v>
@@ -10436,7 +10436,7 @@
         <v>2015</v>
       </c>
       <c r="C576" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D576">
         <v>0</v>
@@ -10444,13 +10444,13 @@
     </row>
     <row r="577" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B577">
         <v>2015</v>
       </c>
       <c r="C577" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D577">
         <v>0.01</v>
@@ -10458,13 +10458,13 @@
     </row>
     <row r="578" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B578">
         <v>2016</v>
       </c>
       <c r="C578" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D578">
         <v>0.21</v>
@@ -10478,7 +10478,7 @@
         <v>2016</v>
       </c>
       <c r="C579" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D579">
         <v>0</v>
@@ -10492,7 +10492,7 @@
         <v>2016</v>
       </c>
       <c r="C580" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D580">
         <v>0.02</v>
@@ -10506,7 +10506,7 @@
         <v>2016</v>
       </c>
       <c r="C581" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D581">
         <v>0</v>
@@ -10520,7 +10520,7 @@
         <v>2016</v>
       </c>
       <c r="C582" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D582">
         <v>0</v>
@@ -10534,7 +10534,7 @@
         <v>2016</v>
       </c>
       <c r="C583" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D583">
         <v>6.92</v>
@@ -10542,13 +10542,13 @@
     </row>
     <row r="584" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B584">
         <v>2016</v>
       </c>
       <c r="C584" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D584">
         <v>0</v>
@@ -10562,7 +10562,7 @@
         <v>2016</v>
       </c>
       <c r="C585" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D585">
         <v>0</v>
@@ -10570,13 +10570,13 @@
     </row>
     <row r="586" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B586">
         <v>2016</v>
       </c>
       <c r="C586" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D586">
         <v>0.01</v>
@@ -10584,13 +10584,13 @@
     </row>
     <row r="587" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B587">
         <v>2017</v>
       </c>
       <c r="C587" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D587">
         <v>0.24</v>
@@ -10604,7 +10604,7 @@
         <v>2017</v>
       </c>
       <c r="C588" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D588">
         <v>0.02</v>
@@ -10618,7 +10618,7 @@
         <v>2017</v>
       </c>
       <c r="C589" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D589">
         <v>0.02</v>
@@ -10632,7 +10632,7 @@
         <v>2017</v>
       </c>
       <c r="C590" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D590">
         <v>0</v>
@@ -10646,7 +10646,7 @@
         <v>2017</v>
       </c>
       <c r="C591" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D591">
         <v>0</v>
@@ -10660,7 +10660,7 @@
         <v>2017</v>
       </c>
       <c r="C592" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D592">
         <v>7.38</v>
@@ -10668,13 +10668,13 @@
     </row>
     <row r="593" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B593">
         <v>2017</v>
       </c>
       <c r="C593" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D593">
         <v>0</v>
@@ -10688,7 +10688,7 @@
         <v>2017</v>
       </c>
       <c r="C594" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D594">
         <v>0</v>
@@ -10696,13 +10696,13 @@
     </row>
     <row r="595" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B595">
         <v>2017</v>
       </c>
       <c r="C595" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D595">
         <v>0.01</v>
@@ -10710,13 +10710,13 @@
     </row>
     <row r="596" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B596">
         <v>2018</v>
       </c>
       <c r="C596" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D596">
         <v>0.28000000000000003</v>
@@ -10730,7 +10730,7 @@
         <v>2018</v>
       </c>
       <c r="C597" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D597">
         <v>0</v>
@@ -10744,7 +10744,7 @@
         <v>2018</v>
       </c>
       <c r="C598" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D598">
         <v>0.02</v>
@@ -10758,7 +10758,7 @@
         <v>2018</v>
       </c>
       <c r="C599" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D599">
         <v>0</v>
@@ -10772,7 +10772,7 @@
         <v>2018</v>
       </c>
       <c r="C600" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D600">
         <v>0</v>
@@ -10786,7 +10786,7 @@
         <v>2018</v>
       </c>
       <c r="C601" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D601">
         <v>6.79</v>
@@ -10794,13 +10794,13 @@
     </row>
     <row r="602" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B602">
         <v>2018</v>
       </c>
       <c r="C602" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D602">
         <v>0</v>
@@ -10814,7 +10814,7 @@
         <v>2018</v>
       </c>
       <c r="C603" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D603">
         <v>0</v>
@@ -10822,13 +10822,13 @@
     </row>
     <row r="604" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B604">
         <v>2018</v>
       </c>
       <c r="C604" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D604">
         <v>0.01</v>
@@ -10836,13 +10836,13 @@
     </row>
     <row r="605" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B605">
         <v>2019</v>
       </c>
       <c r="C605" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D605">
         <v>0.28999999999999998</v>
@@ -10856,7 +10856,7 @@
         <v>2019</v>
       </c>
       <c r="C606" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D606">
         <v>0</v>
@@ -10870,7 +10870,7 @@
         <v>2019</v>
       </c>
       <c r="C607" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D607">
         <v>0.01</v>
@@ -10884,7 +10884,7 @@
         <v>2019</v>
       </c>
       <c r="C608" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D608">
         <v>0</v>
@@ -10898,7 +10898,7 @@
         <v>2019</v>
       </c>
       <c r="C609" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D609">
         <v>0</v>
@@ -10912,7 +10912,7 @@
         <v>2019</v>
       </c>
       <c r="C610" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D610">
         <v>3.57</v>
@@ -10920,13 +10920,13 @@
     </row>
     <row r="611" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B611">
         <v>2019</v>
       </c>
       <c r="C611" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D611">
         <v>0</v>
@@ -10940,7 +10940,7 @@
         <v>2019</v>
       </c>
       <c r="C612" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D612">
         <v>0</v>
@@ -10948,13 +10948,13 @@
     </row>
     <row r="613" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B613">
         <v>2019</v>
       </c>
       <c r="C613" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D613">
         <v>0.01</v>
@@ -10962,13 +10962,13 @@
     </row>
     <row r="614" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B614">
         <v>2020</v>
       </c>
       <c r="C614" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D614">
         <v>0.4</v>
@@ -10982,7 +10982,7 @@
         <v>2020</v>
       </c>
       <c r="C615" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D615">
         <v>0</v>
@@ -10996,7 +10996,7 @@
         <v>2020</v>
       </c>
       <c r="C616" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D616">
         <v>0.01</v>
@@ -11010,7 +11010,7 @@
         <v>2020</v>
       </c>
       <c r="C617" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D617">
         <v>0</v>
@@ -11024,7 +11024,7 @@
         <v>2020</v>
       </c>
       <c r="C618" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D618">
         <v>0</v>
@@ -11038,7 +11038,7 @@
         <v>2020</v>
       </c>
       <c r="C619" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D619">
         <v>2.0299999999999998</v>
@@ -11046,13 +11046,13 @@
     </row>
     <row r="620" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B620">
         <v>2020</v>
       </c>
       <c r="C620" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D620">
         <v>0</v>
@@ -11066,7 +11066,7 @@
         <v>2020</v>
       </c>
       <c r="C621" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D621">
         <v>0.01</v>
@@ -11074,13 +11074,13 @@
     </row>
     <row r="622" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B622">
         <v>2020</v>
       </c>
       <c r="C622" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D622">
         <v>0.01</v>
@@ -11088,13 +11088,13 @@
     </row>
     <row r="623" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B623">
         <v>2021</v>
       </c>
       <c r="C623" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D623">
         <v>0.38</v>
@@ -11108,7 +11108,7 @@
         <v>2021</v>
       </c>
       <c r="C624" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D624">
         <v>0</v>
@@ -11122,7 +11122,7 @@
         <v>2021</v>
       </c>
       <c r="C625" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D625">
         <v>0.01</v>
@@ -11136,7 +11136,7 @@
         <v>2021</v>
       </c>
       <c r="C626" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D626">
         <v>0</v>
@@ -11150,7 +11150,7 @@
         <v>2021</v>
       </c>
       <c r="C627" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D627">
         <v>0</v>
@@ -11164,7 +11164,7 @@
         <v>2021</v>
       </c>
       <c r="C628" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D628">
         <v>2.82</v>
@@ -11172,13 +11172,13 @@
     </row>
     <row r="629" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B629">
         <v>2021</v>
       </c>
       <c r="C629" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D629">
         <v>0</v>
@@ -11192,7 +11192,7 @@
         <v>2021</v>
       </c>
       <c r="C630" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D630">
         <v>0.02</v>
@@ -11200,13 +11200,13 @@
     </row>
     <row r="631" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B631">
         <v>2021</v>
       </c>
       <c r="C631" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D631">
         <v>0.01</v>
@@ -11214,13 +11214,13 @@
     </row>
     <row r="632" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B632">
         <v>2022</v>
       </c>
       <c r="C632" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D632">
         <v>0.34</v>
@@ -11234,7 +11234,7 @@
         <v>2022</v>
       </c>
       <c r="C633" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D633">
         <v>0</v>
@@ -11248,7 +11248,7 @@
         <v>2022</v>
       </c>
       <c r="C634" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D634">
         <v>0.02</v>
@@ -11262,7 +11262,7 @@
         <v>2022</v>
       </c>
       <c r="C635" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D635">
         <v>0</v>
@@ -11276,7 +11276,7 @@
         <v>2022</v>
       </c>
       <c r="C636" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D636">
         <v>0</v>
@@ -11290,7 +11290,7 @@
         <v>2022</v>
       </c>
       <c r="C637" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D637">
         <v>3.96</v>
@@ -11298,13 +11298,13 @@
     </row>
     <row r="638" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B638">
         <v>2022</v>
       </c>
       <c r="C638" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D638">
         <v>0</v>
@@ -11318,7 +11318,7 @@
         <v>2022</v>
       </c>
       <c r="C639" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D639">
         <v>0.03</v>
@@ -11326,13 +11326,13 @@
     </row>
     <row r="640" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B640">
         <v>2022</v>
       </c>
       <c r="C640" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D640">
         <v>0.01</v>
@@ -11340,13 +11340,13 @@
     </row>
     <row r="641" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B641">
         <v>2023</v>
       </c>
       <c r="C641" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D641">
         <v>0.28999999999999998</v>
@@ -11360,7 +11360,7 @@
         <v>2023</v>
       </c>
       <c r="C642" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D642">
         <v>0</v>
@@ -11374,7 +11374,7 @@
         <v>2023</v>
       </c>
       <c r="C643" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D643">
         <v>0.02</v>
@@ -11388,7 +11388,7 @@
         <v>2023</v>
       </c>
       <c r="C644" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D644">
         <v>0</v>
@@ -11402,7 +11402,7 @@
         <v>2023</v>
       </c>
       <c r="C645" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D645">
         <v>0</v>
@@ -11416,7 +11416,7 @@
         <v>2023</v>
       </c>
       <c r="C646" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D646">
         <v>2.34</v>
@@ -11424,13 +11424,13 @@
     </row>
     <row r="647" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B647">
         <v>2023</v>
       </c>
       <c r="C647" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D647">
         <v>0</v>
@@ -11444,7 +11444,7 @@
         <v>2023</v>
       </c>
       <c r="C648" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D648">
         <v>0.04</v>
@@ -11452,13 +11452,13 @@
     </row>
     <row r="649" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B649">
         <v>2023</v>
       </c>
       <c r="C649" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D649">
         <v>0.01</v>
@@ -11466,13 +11466,13 @@
     </row>
     <row r="650" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B650">
         <v>2000</v>
       </c>
       <c r="C650" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D650">
         <v>1.3</v>
@@ -11480,13 +11480,13 @@
     </row>
     <row r="651" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B651">
         <v>2000</v>
       </c>
       <c r="C651" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D651">
         <v>0.4</v>
@@ -11494,13 +11494,13 @@
     </row>
     <row r="652" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B652">
         <v>2001</v>
       </c>
       <c r="C652" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D652">
         <v>1.1000000000000001</v>
@@ -11508,13 +11508,13 @@
     </row>
     <row r="653" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B653">
         <v>2001</v>
       </c>
       <c r="C653" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D653">
         <v>0.5</v>
@@ -11522,13 +11522,13 @@
     </row>
     <row r="654" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B654">
         <v>2002</v>
       </c>
       <c r="C654" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D654">
         <v>1.1000000000000001</v>
@@ -11536,13 +11536,13 @@
     </row>
     <row r="655" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B655">
         <v>2002</v>
       </c>
       <c r="C655" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D655">
         <v>0.4</v>
@@ -11550,13 +11550,13 @@
     </row>
     <row r="656" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B656">
         <v>2003</v>
       </c>
       <c r="C656" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D656">
         <v>2</v>
@@ -11564,13 +11564,13 @@
     </row>
     <row r="657" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B657">
         <v>2003</v>
       </c>
       <c r="C657" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D657">
         <v>0.1</v>
@@ -11578,13 +11578,13 @@
     </row>
     <row r="658" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B658">
         <v>2004</v>
       </c>
       <c r="C658" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D658">
         <v>2.1</v>
@@ -11592,13 +11592,13 @@
     </row>
     <row r="659" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B659">
         <v>2004</v>
       </c>
       <c r="C659" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D659">
         <v>0.3</v>
@@ -11606,13 +11606,13 @@
     </row>
     <row r="660" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B660">
         <v>2005</v>
       </c>
       <c r="C660" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D660">
         <v>2</v>
@@ -11620,13 +11620,13 @@
     </row>
     <row r="661" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B661">
         <v>2005</v>
       </c>
       <c r="C661" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D661">
         <v>0.3</v>
@@ -11634,13 +11634,13 @@
     </row>
     <row r="662" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B662">
         <v>2006</v>
       </c>
       <c r="C662" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D662">
         <v>1</v>
@@ -11648,13 +11648,13 @@
     </row>
     <row r="663" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B663">
         <v>2006</v>
       </c>
       <c r="C663" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D663">
         <v>0.3</v>
@@ -11662,13 +11662,13 @@
     </row>
     <row r="664" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B664">
         <v>2007</v>
       </c>
       <c r="C664" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D664">
         <v>2.8</v>
@@ -11676,13 +11676,13 @@
     </row>
     <row r="665" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B665">
         <v>2007</v>
       </c>
       <c r="C665" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D665">
         <v>0.3</v>
@@ -11690,13 +11690,13 @@
     </row>
     <row r="666" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B666">
         <v>2008</v>
       </c>
       <c r="C666" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D666">
         <v>2.2999999999999998</v>
@@ -11704,13 +11704,13 @@
     </row>
     <row r="667" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B667">
         <v>2008</v>
       </c>
       <c r="C667" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D667">
         <v>1.4</v>
@@ -11718,13 +11718,13 @@
     </row>
     <row r="668" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B668">
         <v>2009</v>
       </c>
       <c r="C668" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D668">
         <v>2.9</v>
@@ -11732,13 +11732,13 @@
     </row>
     <row r="669" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B669">
         <v>2009</v>
       </c>
       <c r="C669" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D669">
         <v>3</v>
@@ -11746,13 +11746,13 @@
     </row>
     <row r="670" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B670">
         <v>2010</v>
       </c>
       <c r="C670" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D670">
         <v>4.4000000000000004</v>
@@ -11760,13 +11760,13 @@
     </row>
     <row r="671" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B671">
         <v>2010</v>
       </c>
       <c r="C671" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D671">
         <v>1.1000000000000001</v>
@@ -11774,13 +11774,13 @@
     </row>
     <row r="672" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B672">
         <v>2011</v>
       </c>
       <c r="C672" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D672">
         <v>5.3</v>
@@ -11788,13 +11788,13 @@
     </row>
     <row r="673" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B673">
         <v>2011</v>
       </c>
       <c r="C673" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D673">
         <v>1.7</v>
@@ -11802,13 +11802,13 @@
     </row>
     <row r="674" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B674">
         <v>2012</v>
       </c>
       <c r="C674" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D674">
         <v>5</v>
@@ -11816,13 +11816,13 @@
     </row>
     <row r="675" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B675">
         <v>2012</v>
       </c>
       <c r="C675" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D675">
         <v>2.7</v>
@@ -11830,13 +11830,13 @@
     </row>
     <row r="676" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B676">
         <v>2013</v>
       </c>
       <c r="C676" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D676">
         <v>6.3</v>
@@ -11844,13 +11844,13 @@
     </row>
     <row r="677" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B677">
         <v>2013</v>
       </c>
       <c r="C677" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D677">
         <v>2.7</v>
@@ -11858,13 +11858,13 @@
     </row>
     <row r="678" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B678">
         <v>2014</v>
       </c>
       <c r="C678" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D678">
         <v>6.5</v>
@@ -11872,13 +11872,13 @@
     </row>
     <row r="679" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B679">
         <v>2014</v>
       </c>
       <c r="C679" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D679">
         <v>3.7</v>
@@ -11886,13 +11886,13 @@
     </row>
     <row r="680" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B680">
         <v>2015</v>
       </c>
       <c r="C680" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D680">
         <v>6.4</v>
@@ -11900,13 +11900,13 @@
     </row>
     <row r="681" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B681">
         <v>2015</v>
       </c>
       <c r="C681" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D681">
         <v>5.5</v>
@@ -11914,13 +11914,13 @@
     </row>
     <row r="682" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B682">
         <v>2016</v>
       </c>
       <c r="C682" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D682">
         <v>5.6</v>
@@ -11928,13 +11928,13 @@
     </row>
     <row r="683" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B683">
         <v>2016</v>
       </c>
       <c r="C683" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D683">
         <v>3.6</v>
@@ -11942,13 +11942,13 @@
     </row>
     <row r="684" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B684">
         <v>2017</v>
       </c>
       <c r="C684" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D684">
         <v>5</v>
@@ -11956,13 +11956,13 @@
     </row>
     <row r="685" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B685">
         <v>2017</v>
       </c>
       <c r="C685" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D685">
         <v>2.2999999999999998</v>
@@ -11970,13 +11970,13 @@
     </row>
     <row r="686" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B686">
         <v>2018</v>
       </c>
       <c r="C686" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D686">
         <v>5</v>
@@ -11984,13 +11984,13 @@
     </row>
     <row r="687" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B687">
         <v>2018</v>
       </c>
       <c r="C687" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D687">
         <v>3.1</v>
@@ -11998,13 +11998,13 @@
     </row>
     <row r="688" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B688">
         <v>2019</v>
       </c>
       <c r="C688" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D688">
         <v>2.7</v>
@@ -12012,13 +12012,13 @@
     </row>
     <row r="689" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B689">
         <v>2019</v>
       </c>
       <c r="C689" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D689">
         <v>4.9000000000000004</v>
@@ -12026,13 +12026,13 @@
     </row>
     <row r="690" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B690">
         <v>2020</v>
       </c>
       <c r="C690" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D690">
         <v>3.7</v>
@@ -12040,13 +12040,13 @@
     </row>
     <row r="691" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B691">
         <v>2020</v>
       </c>
       <c r="C691" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D691">
         <v>7.4</v>
@@ -12054,13 +12054,13 @@
     </row>
     <row r="692" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B692">
         <v>2021</v>
       </c>
       <c r="C692" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D692">
         <v>4.7</v>
@@ -12068,13 +12068,13 @@
     </row>
     <row r="693" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B693">
         <v>2021</v>
       </c>
       <c r="C693" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D693">
         <v>7.3</v>
@@ -12082,13 +12082,13 @@
     </row>
     <row r="694" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B694">
         <v>2022</v>
       </c>
       <c r="C694" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D694">
         <v>6.2</v>
@@ -12096,13 +12096,13 @@
     </row>
     <row r="695" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B695">
         <v>2022</v>
       </c>
       <c r="C695" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D695">
         <v>7.2</v>
@@ -12110,13 +12110,13 @@
     </row>
     <row r="696" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B696">
         <v>2023</v>
       </c>
       <c r="C696" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D696">
         <v>4.4000000000000004</v>
@@ -12124,13 +12124,13 @@
     </row>
     <row r="697" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B697">
         <v>2023</v>
       </c>
       <c r="C697" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D697">
         <v>7.7</v>
